--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://robocip20-my.sharepoint.com/personal/endo_tatsuya_robocip_or_jp/Documents/ドキュメント/_repos/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F179486-39F2-4EE0-8364-DB41D2151382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="-5580" windowWidth="38385" windowHeight="41970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67215" yWindow="-6930" windowWidth="32385" windowHeight="46050" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -44,10 +44,21 @@
     <definedName name="カテゴリ" localSheetId="7">[1]shortcut設定!$F$13:$F$37</definedName>
     <definedName name="カテゴリ">shortcut設定!$F$13:$F$37</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -9474,6 +9485,7 @@
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="setting"/>
+      <sheetName val="MyExcelAddin"/>
     </sheetNames>
     <definedNames>
       <definedName name="getdirpath"/>
@@ -9481,15 +9493,16 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9527,7 +9540,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9633,7 +9646,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9775,7 +9788,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15103,9 +15116,9 @@
       <c r="D16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="26" t="str">
-        <f>[2]!getdirpath(C16)</f>
-        <v>C:\prg_exe\AiperEditex</v>
+      <c r="E16" s="26" t="e">
+        <f ca="1">[2]!getdirpath(C16)</f>
+        <v>#NAME?</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>149</v>
@@ -15151,7 +15164,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T16" s="13" t="str">
+      <c r="T16" s="13" t="e">
         <f ca="1">IF(
   AND($A16&lt;&gt;"",$I16="○"),
   (
@@ -15165,7 +15178,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\121_Doc_Analyze" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\121_Doc_Analyze\AiperEditex（OfficeファイルGrep）.lnk" "C:\prg_exe\AiperEditex\AiperEditex.exe" "" "C:\prg_exe\AiperEditex"</v>
+        <v>#NAME?</v>
       </c>
       <c r="U16" s="9" t="str">
         <f ca="1">IFERROR(
@@ -31662,9 +31675,9 @@
       <c r="D85" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E85" s="26" t="str">
-        <f>[2]!getdirpath(C85)</f>
-        <v>C:\prg_exe\Rapture</v>
+      <c r="E85" s="26" t="e">
+        <f ca="1">[2]!getdirpath(C85)</f>
+        <v>#NAME?</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>149</v>
@@ -31710,7 +31723,7 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="T85" s="13" t="str">
+      <c r="T85" s="13" t="e">
         <f ca="1">IF(
   AND($A85&lt;&gt;"",$I85="○"),
   (
@@ -31724,7 +31737,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\Rapture（スクリーンショット）.lnk" "C:\prg_exe\Rapture\rapture.exe" "" "C:\prg_exe\Rapture"</v>
+        <v>#NAME?</v>
       </c>
       <c r="U85" s="9" t="str">
         <f ca="1">IFERROR(
@@ -67633,9 +67646,9 @@
       <c r="H12" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="I12" s="1" t="str">
-        <f>IF($F12="○","mkdir """&amp;[2]!getdirpath($H12)&amp;"""","")</f>
-        <v>mkdir "%USERPROFILE%\_repos"</v>
+      <c r="I12" s="1" t="e">
+        <f ca="1">IF($F12="○","mkdir """&amp;[2]!getdirpath($H12)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J12" s="1" t="str">
         <f>IF(
@@ -67694,9 +67707,9 @@
       <c r="H13" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="I13" s="1" t="str">
-        <f>IF($F13="○","mkdir """&amp;[2]!getdirpath($H13)&amp;"""","")</f>
-        <v>mkdir "%USERPROFILE%\_repos"</v>
+      <c r="I13" s="1" t="e">
+        <f ca="1">IF($F13="○","mkdir """&amp;[2]!getdirpath($H13)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J13" s="1" t="str">
         <f>IF(
@@ -67746,9 +67759,9 @@
       <c r="H14" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="I14" s="1" t="str">
-        <f>IF($F14="○","mkdir """&amp;[2]!getdirpath($H14)&amp;"""","")</f>
-        <v>mkdir "%USERPROFILE%\_repos"</v>
+      <c r="I14" s="1" t="e">
+        <f ca="1">IF($F14="○","mkdir """&amp;[2]!getdirpath($H14)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J14" s="1" t="str">
         <f>IF(
@@ -67798,9 +67811,9 @@
       <c r="H15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="1" t="str">
-        <f>IF($F15="○","mkdir """&amp;[2]!getdirpath($H15)&amp;"""","")</f>
-        <v>mkdir "%USERPROFILE%\_root"</v>
+      <c r="I15" s="1" t="e">
+        <f ca="1">IF($F15="○","mkdir """&amp;[2]!getdirpath($H15)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J15" s="1" t="str">
         <f>IF(
@@ -67859,9 +67872,9 @@
       <c r="H16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="1" t="str">
-        <f>IF($F16="○","mkdir """&amp;[2]!getdirpath($H16)&amp;"""","")</f>
-        <v>mkdir "%USERPROFILE%"</v>
+      <c r="I16" s="1" t="e">
+        <f ca="1">IF($F16="○","mkdir """&amp;[2]!getdirpath($H16)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J16" s="1" t="str">
         <f>IF(
@@ -67920,9 +67933,9 @@
       <c r="H17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I17" s="1" t="str">
-        <f>IF($F17="○","mkdir """&amp;[2]!getdirpath($H17)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\excel"</v>
+      <c r="I17" s="1" t="e">
+        <f ca="1">IF($F17="○","mkdir """&amp;[2]!getdirpath($H17)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J17" s="1" t="str">
         <f>IF(
@@ -68026,9 +68039,9 @@
       <c r="H19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="1" t="str">
-        <f>IF($F19="○","mkdir """&amp;[2]!getdirpath($H19)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\outlook"</v>
+      <c r="I19" s="1" t="e">
+        <f ca="1">IF($F19="○","mkdir """&amp;[2]!getdirpath($H19)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J19" s="1" t="str">
         <f>IF(
@@ -68079,12 +68092,12 @@
       <c r="H20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I20" s="1" t="str">
-        <f>IF($F20="○","mkdir """&amp;[2]!getdirpath($H20)&amp;"""","")</f>
-        <v>mkdir "C:\other\template"</v>
-      </c>
-      <c r="J20" s="1" t="str">
-        <f>IF(
+      <c r="I20" s="1" t="e">
+        <f ca="1">IF($F20="○","mkdir """&amp;[2]!getdirpath($H20)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J20" s="1" t="e">
+        <f ca="1">IF(
   $F20="○",
   IF(
     $E20="file",
@@ -68093,7 +68106,7 @@
   ),
   ""
 )</f>
-        <v>copy "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68132,9 +68145,9 @@
       <c r="H21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="1" t="str">
-        <f>IF($F21="○","mkdir """&amp;[2]!getdirpath($H21)&amp;"""","")</f>
-        <v>mkdir "C:\codes"</v>
+      <c r="I21" s="1" t="e">
+        <f ca="1">IF($F21="○","mkdir """&amp;[2]!getdirpath($H21)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J21" s="1" t="str">
         <f>IF(
@@ -68185,9 +68198,9 @@
       <c r="H22" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="I22" s="1" t="str">
-        <f>IF($F22="○","mkdir """&amp;[2]!getdirpath($H22)&amp;"""","")</f>
-        <v>mkdir "C:\codes"</v>
+      <c r="I22" s="1" t="e">
+        <f ca="1">IF($F22="○","mkdir """&amp;[2]!getdirpath($H22)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J22" s="1" t="str">
         <f>IF(
@@ -68238,12 +68251,12 @@
       <c r="H23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I23" s="1" t="str">
-        <f>IF($F23="○","mkdir """&amp;[2]!getdirpath($H23)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim"</v>
-      </c>
-      <c r="J23" s="1" t="str">
-        <f>IF(
+      <c r="I23" s="1" t="e">
+        <f ca="1">IF($F23="○","mkdir """&amp;[2]!getdirpath($H23)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J23" s="1" t="e">
+        <f ca="1">IF(
   $F23="○",
   IF(
     $E23="file",
@@ -68252,7 +68265,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K23" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68291,12 +68304,12 @@
       <c r="H24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="1" t="str">
-        <f>IF($F24="○","mkdir """&amp;[2]!getdirpath($H24)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim"</v>
-      </c>
-      <c r="J24" s="1" t="str">
-        <f>IF(
+      <c r="I24" s="1" t="e">
+        <f ca="1">IF($F24="○","mkdir """&amp;[2]!getdirpath($H24)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J24" s="1" t="e">
+        <f ca="1">IF(
   $F24="○",
   IF(
     $E24="file",
@@ -68305,7 +68318,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_vimrc" "C:\codes\vim"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K24" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68344,12 +68357,12 @@
       <c r="H25" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="I25" s="1" t="str">
-        <f>IF($F25="○","mkdir """&amp;[2]!getdirpath($H25)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
-      </c>
-      <c r="J25" s="1" t="str">
-        <f>IF(
+      <c r="I25" s="1" t="e">
+        <f ca="1">IF($F25="○","mkdir """&amp;[2]!getdirpath($H25)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J25" s="1" t="e">
+        <f ca="1">IF(
   $F25="○",
   IF(
     $E25="file",
@@ -68358,7 +68371,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K25" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68397,12 +68410,12 @@
       <c r="H26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="1" t="str">
-        <f>IF($F26="○","mkdir """&amp;[2]!getdirpath($H26)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
-      </c>
-      <c r="J26" s="1" t="str">
-        <f>IF(
+      <c r="I26" s="1" t="e">
+        <f ca="1">IF($F26="○","mkdir """&amp;[2]!getdirpath($H26)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J26" s="1" t="e">
+        <f ca="1">IF(
   $F26="○",
   IF(
     $E26="file",
@@ -68411,7 +68424,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68450,12 +68463,12 @@
       <c r="H27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I27" s="1" t="str">
-        <f>IF($F27="○","mkdir """&amp;[2]!getdirpath($H27)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx"</v>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f>IF(
+      <c r="I27" s="1" t="e">
+        <f ca="1">IF($F27="○","mkdir """&amp;[2]!getdirpath($H27)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J27" s="1" t="e">
+        <f ca="1">IF(
   $F27="○",
   IF(
     $E27="file",
@@ -68464,7 +68477,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K27" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68503,12 +68516,12 @@
       <c r="H28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="1" t="str">
-        <f>IF($F28="○","mkdir """&amp;[2]!getdirpath($H28)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
-      </c>
-      <c r="J28" s="1" t="str">
-        <f>IF(
+      <c r="I28" s="1" t="e">
+        <f ca="1">IF($F28="○","mkdir """&amp;[2]!getdirpath($H28)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J28" s="1" t="e">
+        <f ca="1">IF(
   $F28="○",
   IF(
     $E28="file",
@@ -68517,7 +68530,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K28" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68556,12 +68569,12 @@
       <c r="H29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="1" t="str">
-        <f>IF($F29="○","mkdir """&amp;[2]!getdirpath($H29)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
-      </c>
-      <c r="J29" s="1" t="str">
-        <f>IF(
+      <c r="I29" s="1" t="e">
+        <f ca="1">IF($F29="○","mkdir """&amp;[2]!getdirpath($H29)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J29" s="1" t="e">
+        <f ca="1">IF(
   $F29="○",
   IF(
     $E29="file",
@@ -68570,7 +68583,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68609,12 +68622,12 @@
       <c r="H30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I30" s="1" t="str">
-        <f>IF($F30="○","mkdir """&amp;[2]!getdirpath($H30)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
-      </c>
-      <c r="J30" s="1" t="str">
-        <f>IF(
+      <c r="I30" s="1" t="e">
+        <f ca="1">IF($F30="○","mkdir """&amp;[2]!getdirpath($H30)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J30" s="1" t="e">
+        <f ca="1">IF(
   $F30="○",
   IF(
     $E30="file",
@@ -68623,7 +68636,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68662,12 +68675,12 @@
       <c r="H31" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I31" s="1" t="str">
-        <f>IF($F31="○","mkdir """&amp;[2]!getdirpath($H31)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vscode"</v>
-      </c>
-      <c r="J31" s="1" t="str">
-        <f>IF(
+      <c r="I31" s="1" t="e">
+        <f ca="1">IF($F31="○","mkdir """&amp;[2]!getdirpath($H31)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J31" s="1" t="e">
+        <f ca="1">IF(
   $F31="○",
   IF(
     $E31="file",
@@ -68676,7 +68689,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K31" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68715,12 +68728,12 @@
       <c r="H32" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I32" s="1" t="str">
-        <f>IF($F32="○","mkdir """&amp;[2]!getdirpath($H32)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vscode"</v>
-      </c>
-      <c r="J32" s="1" t="str">
-        <f>IF(
+      <c r="I32" s="1" t="e">
+        <f ca="1">IF($F32="○","mkdir """&amp;[2]!getdirpath($H32)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J32" s="1" t="e">
+        <f ca="1">IF(
   $F32="○",
   IF(
     $E32="file",
@@ -68729,7 +68742,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K32" s="1" t="str">
         <f t="shared" si="1"/>
@@ -68768,12 +68781,12 @@
       <c r="H33" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="I33" s="1" t="str">
-        <f>IF($F33="○","mkdir """&amp;[2]!getdirpath($H33)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vscode"</v>
-      </c>
-      <c r="J33" s="1" t="str">
-        <f>IF(
+      <c r="I33" s="1" t="e">
+        <f ca="1">IF($F33="○","mkdir """&amp;[2]!getdirpath($H33)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J33" s="1" t="e">
+        <f ca="1">IF(
   $F33="○",
   IF(
     $E33="file",
@@ -68782,7 +68795,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K33" s="1" t="str">
         <f t="shared" ref="K33:K38" si="2">IF(F33="○","rename """&amp;G33&amp;""" """&amp;RIGHT(G33,LEN(G33)-FIND("●",SUBSTITUTE(G33,"\","●",LEN(G33)-LEN(SUBSTITUTE(G33,"\","")))))&amp;"_bak""","")</f>
@@ -68829,12 +68842,12 @@
       <c r="H34" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="I34" s="1" t="str">
-        <f>IF($F34="○","mkdir """&amp;[2]!getdirpath($H34)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vbs\tools\x-finder"</v>
-      </c>
-      <c r="J34" s="1" t="str">
-        <f>IF(
+      <c r="I34" s="1" t="e">
+        <f ca="1">IF($F34="○","mkdir """&amp;[2]!getdirpath($H34)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J34" s="1" t="e">
+        <f ca="1">IF(
   $F34="○",
   IF(
     $E34="file",
@@ -68843,7 +68856,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K34" s="1" t="str">
         <f t="shared" si="2"/>
@@ -68882,12 +68895,12 @@
       <c r="H35" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="I35" s="1" t="str">
-        <f>IF($F35="○","mkdir """&amp;[2]!getdirpath($H35)&amp;"""","")</f>
-        <v>mkdir "C:\codes\bat\tools\x-finder"</v>
-      </c>
-      <c r="J35" s="1" t="str">
-        <f>IF(
+      <c r="I35" s="1" t="e">
+        <f ca="1">IF($F35="○","mkdir """&amp;[2]!getdirpath($H35)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J35" s="1" t="e">
+        <f ca="1">IF(
   $F35="○",
   IF(
     $E35="file",
@@ -68896,7 +68909,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K35" s="1" t="str">
         <f t="shared" si="2"/>
@@ -68935,12 +68948,12 @@
       <c r="H36" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I36" s="1" t="str">
-        <f>IF($F36="○","mkdir """&amp;[2]!getdirpath($H36)&amp;"""","")</f>
-        <v>mkdir "C:\codes\winterm"</v>
-      </c>
-      <c r="J36" s="1" t="str">
-        <f>IF(
+      <c r="I36" s="1" t="e">
+        <f ca="1">IF($F36="○","mkdir """&amp;[2]!getdirpath($H36)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J36" s="1" t="e">
+        <f ca="1">IF(
   $F36="○",
   IF(
     $E36="file",
@@ -68949,7 +68962,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K36" s="1" t="str">
         <f t="shared" si="2"/>
@@ -68988,12 +69001,12 @@
       <c r="H37" s="6" t="s">
         <v>1146</v>
       </c>
-      <c r="I37" s="1" t="str">
-        <f>IF($F37="○","mkdir """&amp;[2]!getdirpath($H37)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_alluser"</v>
-      </c>
-      <c r="J37" s="1" t="str">
-        <f>IF(
+      <c r="I37" s="1" t="e">
+        <f ca="1">IF($F37="○","mkdir """&amp;[2]!getdirpath($H37)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J37" s="1" t="e">
+        <f ca="1">IF(
   $F37="○",
   IF(
     $E37="file",
@@ -69002,7 +69015,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="2"/>
@@ -69041,12 +69054,12 @@
       <c r="H38" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="I38" s="1" t="str">
-        <f>IF($F38="○","mkdir """&amp;[2]!getdirpath($H38)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_myuser"</v>
-      </c>
-      <c r="J38" s="1" t="str">
-        <f>IF(
+      <c r="I38" s="1" t="e">
+        <f ca="1">IF($F38="○","mkdir """&amp;[2]!getdirpath($H38)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J38" s="1" t="e">
+        <f ca="1">IF(
   $F38="○",
   IF(
     $E38="file",
@@ -69055,7 +69068,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="2"/>
@@ -69094,12 +69107,12 @@
       <c r="H39" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="I39" s="1" t="str">
-        <f>IF($F39="○","mkdir """&amp;[2]!getdirpath($H39)&amp;"""","")</f>
-        <v>mkdir "C:\codes\wezterm"</v>
-      </c>
-      <c r="J39" s="1" t="str">
-        <f>IF(
+      <c r="I39" s="1" t="e">
+        <f ca="1">IF($F39="○","mkdir """&amp;[2]!getdirpath($H39)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J39" s="1" t="e">
+        <f ca="1">IF(
   $F39="○",
   IF(
     $E39="file",
@@ -69108,7 +69121,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K39" s="1" t="str">
         <f t="shared" ref="K39" si="4">IF(F39="○","rename """&amp;G39&amp;""" """&amp;RIGHT(G39,LEN(G39)-FIND("●",SUBSTITUTE(G39,"\","●",LEN(G39)-LEN(SUBSTITUTE(G39,"\","")))))&amp;"_bak""","")</f>
@@ -69155,9 +69168,9 @@
       <c r="H40" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="I40" s="1" t="str">
-        <f>IF($F40="○","mkdir """&amp;[2]!getdirpath($H40)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\HNXgrep"</v>
+      <c r="I40" s="1" t="e">
+        <f ca="1">IF($F40="○","mkdir """&amp;[2]!getdirpath($H40)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J40" s="1" t="str">
         <f>IF(
@@ -69208,9 +69221,9 @@
       <c r="H41" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="I41" s="1" t="str">
-        <f>IF($F41="○","mkdir """&amp;[2]!getdirpath($H41)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Icaros"</v>
+      <c r="I41" s="1" t="e">
+        <f ca="1">IF($F41="○","mkdir """&amp;[2]!getdirpath($H41)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J41" s="1" t="str">
         <f>IF(
@@ -69261,9 +69274,9 @@
       <c r="H42" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="I42" s="1" t="str">
-        <f>IF($F42="○","mkdir """&amp;[2]!getdirpath($H42)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\EasyShot"</v>
+      <c r="I42" s="1" t="e">
+        <f ca="1">IF($F42="○","mkdir """&amp;[2]!getdirpath($H42)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J42" s="1" t="str">
         <f>IF(
@@ -69314,9 +69327,9 @@
       <c r="H43" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="I43" s="1" t="str">
-        <f>IF($F43="○","mkdir """&amp;[2]!getdirpath($H43)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\DeInput"</v>
+      <c r="I43" s="1" t="e">
+        <f ca="1">IF($F43="○","mkdir """&amp;[2]!getdirpath($H43)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J43" s="1" t="str">
         <f>IF(
@@ -69367,9 +69380,9 @@
       <c r="H44" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="I44" s="1" t="str">
-        <f>IF($F44="○","mkdir """&amp;[2]!getdirpath($H44)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\MP3Tag"</v>
+      <c r="I44" s="1" t="e">
+        <f ca="1">IF($F44="○","mkdir """&amp;[2]!getdirpath($H44)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J44" s="1" t="str">
         <f>IF(
@@ -69473,9 +69486,9 @@
       <c r="H46" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="I46" s="1" t="str">
-        <f>IF($F46="○","mkdir """&amp;[2]!getdirpath($H46)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Audacity"</v>
+      <c r="I46" s="1" t="e">
+        <f ca="1">IF($F46="○","mkdir """&amp;[2]!getdirpath($H46)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J46" s="1" t="str">
         <f>IF(
@@ -69526,9 +69539,9 @@
       <c r="H47" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="I47" s="1" t="str">
-        <f>IF($F47="○","mkdir """&amp;[2]!getdirpath($H47)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Subversion"</v>
+      <c r="I47" s="1" t="e">
+        <f ca="1">IF($F47="○","mkdir """&amp;[2]!getdirpath($H47)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J47" s="1" t="str">
         <f>IF(
@@ -69579,9 +69592,9 @@
       <c r="H48" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="I48" s="1" t="str">
-        <f>IF($F48="○","mkdir """&amp;[2]!getdirpath($H48)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseGit"</v>
+      <c r="I48" s="1" t="e">
+        <f ca="1">IF($F48="○","mkdir """&amp;[2]!getdirpath($H48)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J48" s="1" t="str">
         <f>IF(
@@ -69632,9 +69645,9 @@
       <c r="H49" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="I49" s="1" t="str">
-        <f>IF($F49="○","mkdir """&amp;[2]!getdirpath($H49)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseSVN"</v>
+      <c r="I49" s="1" t="e">
+        <f ca="1">IF($F49="○","mkdir """&amp;[2]!getdirpath($H49)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J49" s="1" t="str">
         <f>IF(
@@ -69685,9 +69698,9 @@
       <c r="H50" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="I50" s="1" t="str">
-        <f>IF($F50="○","mkdir """&amp;[2]!getdirpath($H50)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Anki2"</v>
+      <c r="I50" s="1" t="e">
+        <f ca="1">IF($F50="○","mkdir """&amp;[2]!getdirpath($H50)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J50" s="1" t="str">
         <f>IF(
@@ -69746,9 +69759,9 @@
       <c r="H51" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="I51" s="1" t="str">
-        <f>IF($F51="○","mkdir """&amp;[2]!getdirpath($H51)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+      <c r="I51" s="1" t="e">
+        <f ca="1">IF($F51="○","mkdir """&amp;[2]!getdirpath($H51)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J51" s="1" t="str">
         <f>IF(
@@ -69799,9 +69812,9 @@
       <c r="H52" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="I52" s="1" t="str">
-        <f>IF($F52="○","mkdir """&amp;[2]!getdirpath($H52)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+      <c r="I52" s="1" t="e">
+        <f ca="1">IF($F52="○","mkdir """&amp;[2]!getdirpath($H52)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J52" s="1" t="str">
         <f>IF(
@@ -69982,12 +69995,12 @@
       <c r="H55" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="I55" s="1" t="str">
-        <f>IF($F55="○","mkdir """&amp;[2]!getdirpath($H55)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
-      </c>
-      <c r="J55" s="1" t="str">
-        <f>IF(
+      <c r="I55" s="1" t="e">
+        <f ca="1">IF($F55="○","mkdir """&amp;[2]!getdirpath($H55)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J55" s="1" t="e">
+        <f ca="1">IF(
   $F55="○",
   IF(
     $E55="file",
@@ -69996,7 +70009,7 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K55" s="1" t="str">
         <f t="shared" ref="K55" si="7">IF(F55="○","rename """&amp;G55&amp;""" """&amp;RIGHT(G55,LEN(G55)-FIND("●",SUBSTITUTE(G55,"\","●",LEN(G55)-LEN(SUBSTITUTE(G55,"\","")))))&amp;"_bak""","")</f>
@@ -70043,9 +70056,9 @@
       <c r="H56" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="I56" s="1" t="str">
-        <f>IF($F56="○","mkdir """&amp;[2]!getdirpath($H56)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+      <c r="I56" s="1" t="e">
+        <f ca="1">IF($F56="○","mkdir """&amp;[2]!getdirpath($H56)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J56" s="1" t="str">
         <f>IF(
@@ -70096,12 +70109,12 @@
       <c r="H57" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="I57" s="1" t="str">
-        <f>IF($F57="○","mkdir """&amp;[2]!getdirpath($H57)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
-      </c>
-      <c r="J57" s="1" t="str">
-        <f>IF(
+      <c r="I57" s="1" t="e">
+        <f ca="1">IF($F57="○","mkdir """&amp;[2]!getdirpath($H57)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J57" s="1" t="e">
+        <f ca="1">IF(
   $F57="○",
   IF(
     $E57="file",
@@ -70110,7 +70123,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="1"/>
@@ -70149,12 +70162,12 @@
       <c r="H58" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="I58" s="1" t="str">
-        <f>IF($F58="○","mkdir """&amp;[2]!getdirpath($H58)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
-      </c>
-      <c r="J58" s="1" t="str">
-        <f>IF(
+      <c r="I58" s="1" t="e">
+        <f ca="1">IF($F58="○","mkdir """&amp;[2]!getdirpath($H58)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J58" s="1" t="e">
+        <f ca="1">IF(
   $F58="○",
   IF(
     $E58="file",
@@ -70163,7 +70176,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="1"/>
@@ -70202,12 +70215,12 @@
       <c r="H59" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="I59" s="1" t="str">
-        <f>IF($F59="○","mkdir """&amp;[2]!getdirpath($H59)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
-      </c>
-      <c r="J59" s="1" t="str">
-        <f>IF(
+      <c r="I59" s="1" t="e">
+        <f ca="1">IF($F59="○","mkdir """&amp;[2]!getdirpath($H59)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J59" s="1" t="e">
+        <f ca="1">IF(
   $F59="○",
   IF(
     $E59="file",
@@ -70216,7 +70229,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="1"/>
@@ -70255,12 +70268,12 @@
       <c r="H60" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="I60" s="1" t="str">
-        <f>IF($F60="○","mkdir """&amp;[2]!getdirpath($H60)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
-      </c>
-      <c r="J60" s="1" t="str">
-        <f>IF(
+      <c r="I60" s="1" t="e">
+        <f ca="1">IF($F60="○","mkdir """&amp;[2]!getdirpath($H60)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J60" s="1" t="e">
+        <f ca="1">IF(
   $F60="○",
   IF(
     $E60="file",
@@ -70269,7 +70282,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="1"/>
@@ -70308,12 +70321,12 @@
       <c r="H61" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="I61" s="1" t="str">
-        <f>IF($F61="○","mkdir """&amp;[2]!getdirpath($H61)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
-      </c>
-      <c r="J61" s="1" t="str">
-        <f>IF(
+      <c r="I61" s="1" t="e">
+        <f ca="1">IF($F61="○","mkdir """&amp;[2]!getdirpath($H61)&amp;"""","")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J61" s="1" t="e">
+        <f ca="1">IF(
   $F61="○",
   IF(
     $E61="file",
@@ -70322,7 +70335,7 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>#NAME?</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="1"/>
@@ -70361,9 +70374,9 @@
       <c r="H62" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I62" s="1" t="str">
-        <f>IF($F62="○","mkdir """&amp;[2]!getdirpath($H62)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes\MobileSync"</v>
+      <c r="I62" s="1" t="e">
+        <f ca="1">IF($F62="○","mkdir """&amp;[2]!getdirpath($H62)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J62" s="1" t="str">
         <f>IF(
@@ -70414,9 +70427,9 @@
       <c r="H63" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="I63" s="1" t="str">
-        <f>IF($F63="○","mkdir """&amp;[2]!getdirpath($H63)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes"</v>
+      <c r="I63" s="1" t="e">
+        <f ca="1">IF($F63="○","mkdir """&amp;[2]!getdirpath($H63)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J63" s="1" t="str">
         <f>IF(
@@ -70467,9 +70480,9 @@
       <c r="H64" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="I64" s="1" t="str">
-        <f>IF($F64="○","mkdir """&amp;[2]!getdirpath($H64)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes"</v>
+      <c r="I64" s="1" t="e">
+        <f ca="1">IF($F64="○","mkdir """&amp;[2]!getdirpath($H64)&amp;"""","")</f>
+        <v>#NAME?</v>
       </c>
       <c r="J64" s="1" t="str">
         <f>IF(

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://robocip20-my.sharepoint.com/personal/endo_tatsuya_robocip_or_jp/Documents/ドキュメント/_repos/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{0E8DEACF-3A2F-45BD-AAD8-EC9C0C256A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85CA8600-A5D7-4A1F-962E-0C2825CD44E4}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{0E8DEACF-3A2F-45BD-AAD8-EC9C0C256A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B70D513-9607-4648-8650-8F8FC2D7F038}"/>
   <bookViews>
-    <workbookView xWindow="67215" yWindow="-6930" windowWidth="32385" windowHeight="46050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="-6795" windowWidth="38385" windowHeight="42465" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -34,12 +34,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">linux環境構築!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$227</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$115</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$227</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$83</definedName>
     <definedName name="カテゴリ" localSheetId="7">[1]shortcut設定!$F$13:$F$37</definedName>
     <definedName name="カテゴリ">shortcut設定!$F$13:$F$37</definedName>
@@ -94,6 +94,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Tatsuya Endo</author>
+    <author>ROBOCIP(PC-31)</author>
   </authors>
   <commentList>
     <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -239,6 +240,23 @@
         </r>
       </text>
     </comment>
+    <comment ref="C205" authorId="1" shapeId="0" xr:uid="{79A801CC-78B5-4A0F-A0AC-94E4A411DD2F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>以下ファイルパスをすべてシンボリックリンクを介さないファイルパスにする必要がなる。
+・ScheduledBackup.bat内のファイルパス
+・ScheduledBackup.bat.lnkの指示先ファイルパス
+・ScheduledBackup.bat.lnkの作業ディレクトリパス</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -249,7 +267,7 @@
     <author>Tatsuya Endo</author>
   </authors>
   <commentList>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -267,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -285,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="F54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -302,7 +320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="F55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -319,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="B56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -790,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6429" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6438" uniqueCount="1567">
   <si>
     <t>○</t>
   </si>
@@ -8040,10 +8058,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C:\root\30_tool\ScheduledBackup.bat</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>VIMプラグイン（jellybeans.vim）</t>
     <phoneticPr fontId="7"/>
   </si>
@@ -8230,6 +8244,26 @@
   </si>
   <si>
     <t>curl -fsSL https://claude.ai/install.sh | bash</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:\root\30_tool\ScheduledBackup.bat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:\root\30_tool</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BackUpFiles.bat</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>C:\root\30_tool\BackUpFiles.bat</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>C:\codes\vbs\tools\win\file_ope\BackUpFiles.bat</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10012,15 +10046,15 @@
         <v>149</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="E5" s="142"/>
       <c r="F5" s="143"/>
       <c r="G5" s="119" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H5" s="117" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="I5" s="104" t="s">
         <v>28</v>
@@ -11312,7 +11346,7 @@
         <v>149</v>
       </c>
       <c r="D53" s="116" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="E53" s="142"/>
       <c r="F53" s="143"/>
@@ -11905,7 +11939,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="116" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E76" s="142" t="s">
         <v>934</v>
@@ -11913,7 +11947,7 @@
       <c r="F76" s="143"/>
       <c r="G76" s="117"/>
       <c r="H76" s="171" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="I76" s="104" t="s">
         <v>28</v>
@@ -60856,13 +60890,13 @@
         <v>837</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>1518</v>
+        <v>1562</v>
       </c>
       <c r="D205" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E205" s="26" t="s">
-        <v>39</v>
+        <v>1563</v>
       </c>
       <c r="F205" s="15" t="s">
         <v>0</v>
@@ -61051,7 +61085,7 @@
   ),
   ""
 )</f>
-        <v>"C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\ScheduledBackup.bat（定期ファイルバックアップ）.lnk" "C:\root\30_tool\ScheduledBackup.bat" "" ""</v>
+        <v>"C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\ScheduledBackup.bat（定期ファイルバックアップ）.lnk" "C:\root\30_tool\ScheduledBackup.bat" "" "C:\root\30_tool"</v>
       </c>
       <c r="AF205" s="9" t="str">
         <f>IF(
@@ -62324,13 +62358,13 @@
     </row>
     <row r="211" spans="1:36">
       <c r="A211" s="9" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>1486</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D211" s="15" t="s">
         <v>39</v>
@@ -62563,13 +62597,13 @@
     </row>
     <row r="212" spans="1:36">
       <c r="A212" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>1485</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>39</v>
@@ -67603,7 +67637,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A2:M85"/>
+  <dimension ref="A2:M86"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -67714,7 +67748,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -67735,7 +67769,7 @@
         <v>19</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="I12" s="1" t="str" cm="1">
         <f t="array" ref="I12">IF($F12="○","mkdir """&amp;[2]!getdirpath($H12)&amp;"""","")</f>
@@ -67754,7 +67788,7 @@
         <v>robocopy "C:\codes" "%USERPROFILE%\_repos\codes" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K12" s="1" t="str">
-        <f t="shared" ref="K12:K18" si="0">IF(F12="○","move /Y """&amp;G12&amp;""" """&amp;RIGHT(G12,LEN(G12)-FIND("●",SUBSTITUTE(G12,"\","●",LEN(G12)-LEN(SUBSTITUTE(G12,"\","")))))&amp;"_bak""","")</f>
+        <f t="shared" ref="K12:K19" si="0">IF(F12="○","move /Y """&amp;G12&amp;""" """&amp;RIGHT(G12,LEN(G12)-FIND("●",SUBSTITUTE(G12,"\","●",LEN(G12)-LEN(SUBSTITUTE(G12,"\","")))))&amp;"_bak""","")</f>
         <v>move /Y "C:\codes" "codes_bak"</v>
       </c>
       <c r="L12" s="1" t="str">
@@ -67775,7 +67809,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>2</v>
@@ -67793,10 +67827,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>1522</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>1523</v>
       </c>
       <c r="I13" s="1" t="str" cm="1">
         <f t="array" ref="I13">IF($F13="○","mkdir """&amp;[2]!getdirpath($H13)&amp;"""","")</f>
@@ -67819,7 +67853,7 @@
         <v>move /Y "C:\other" "other_bak"</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="M13" t="s">
         <v>1277</v>
@@ -67827,10 +67861,10 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>149</v>
@@ -67845,10 +67879,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="I14" s="1" t="str" cm="1">
         <f t="array" ref="I14">IF($F14="○","mkdir """&amp;[2]!getdirpath($H14)&amp;"""","")</f>
@@ -67871,7 +67905,7 @@
         <v>move /Y "C:\github_io" "github_io_bak"</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="M14" t="s">
         <v>28</v>
@@ -67879,7 +67913,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>33</v>
@@ -67984,7 +68018,7 @@
         <v>move /Y "C:\root" "root_bak"</v>
       </c>
       <c r="L16" s="1" t="str">
-        <f t="shared" ref="L16:L51" si="1">IF(
+        <f t="shared" ref="L16:L52" si="1">IF(
   F16="○",
   "mklink "&amp;IF(
     E16="folder",
@@ -68000,33 +68034,33 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="6" t="s">
-        <v>1134</v>
+      <c r="A17" s="1" t="s">
+        <v>1133</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>1564</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>15</v>
+        <v>1565</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>5</v>
+        <v>1566</v>
       </c>
       <c r="I17" s="1" t="str" cm="1">
         <f t="array" ref="I17">IF($F17="○","mkdir """&amp;[2]!getdirpath($H17)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\excel"</v>
+        <v>mkdir "C:\codes\vbs\tools\win\file_ope"</v>
       </c>
       <c r="J17" s="1" t="str" cm="1">
         <f t="array" ref="J17">IF(
@@ -68038,18 +68072,18 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns" /MIR /XD "System Volume Information"</v>
+        <v>copy "C:\root\30_tool\BackUpFiles.bat" "C:\codes\vbs\tools\win\file_ope"</v>
       </c>
       <c r="K17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "AddIns_bak"</v>
+        <f t="shared" ref="K17" si="2">IF(F17="○","move /Y """&amp;G17&amp;""" """&amp;RIGHT(G17,LEN(G17)-FIND("●",SUBSTITUTE(G17,"\","●",LEN(G17)-LEN(SUBSTITUTE(G17,"\","")))))&amp;"_bak""","")</f>
+        <v>move /Y "C:\root\30_tool\BackUpFiles.bat" "BackUpFiles.bat_bak"</v>
       </c>
       <c r="L17" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns"</v>
+        <v>mklink "C:\root\30_tool\BackUpFiles.bat" "C:\codes\vbs\tools\win\file_ope\BackUpFiles.bat"</v>
       </c>
       <c r="M17" t="s">
-        <v>1277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -68057,31 +68091,31 @@
         <v>1134</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="97" t="s">
-        <v>947</v>
-      </c>
-      <c r="H18" s="97" t="s">
-        <v>948</v>
-      </c>
-      <c r="I18" s="97" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1" t="str" cm="1">
         <f t="array" ref="I18">IF($F18="○","mkdir """&amp;[2]!getdirpath($H18)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J18" s="97" t="str" cm="1">
+        <v>mkdir "C:\codes\vba\excel"</v>
+      </c>
+      <c r="J18" s="1" t="str" cm="1">
         <f t="array" ref="J18">IF(
   $F18="○",
   IF(
@@ -68091,15 +68125,15 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K18" s="97" t="str">
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="97" t="str">
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "AddIns_bak"</v>
+      </c>
+      <c r="L18" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\AddIns" "C:\codes\vba\excel\AddIns"</v>
       </c>
       <c r="M18" t="s">
         <v>1277</v>
@@ -68110,31 +68144,31 @@
         <v>1134</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I19" s="1" t="str" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G19" s="97" t="s">
+        <v>947</v>
+      </c>
+      <c r="H19" s="97" t="s">
+        <v>948</v>
+      </c>
+      <c r="I19" s="97" t="str" cm="1">
         <f t="array" ref="I19">IF($F19="○","mkdir """&amp;[2]!getdirpath($H19)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vba\outlook"</v>
-      </c>
-      <c r="J19" s="1" t="str" cm="1">
+        <v/>
+      </c>
+      <c r="J19" s="97" t="str" cm="1">
         <f t="array" ref="J19">IF(
   $F19="○",
   IF(
@@ -68144,26 +68178,26 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns" /MIR /XD "System Volume Information"</v>
-      </c>
-      <c r="K19" s="1" t="str">
-        <f>IF(F19="○","move /Y """&amp;G19&amp;""" """&amp;RIGHT(G19,LEN(G19)-FIND("●",SUBSTITUTE(G19,"\","●",LEN(G19)-LEN(SUBSTITUTE(G19,"\","")))))&amp;"_bak""","")</f>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "Outlook_bak"</v>
-      </c>
-      <c r="L19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K19" s="97" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="L19" s="97" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns"</v>
+        <v/>
       </c>
       <c r="M19" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="1" t="s">
-        <v>157</v>
+      <c r="A20" s="6" t="s">
+        <v>1134</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1135</v>
+        <v>36</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>149</v>
@@ -68172,20 +68206,20 @@
         <v>149</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="I20" s="1" t="str" cm="1">
         <f t="array" ref="I20">IF($F20="○","mkdir """&amp;[2]!getdirpath($H20)&amp;"""","")</f>
-        <v>mkdir "C:\other\template"</v>
+        <v>mkdir "C:\codes\vba\outlook"</v>
       </c>
       <c r="J20" s="1" t="str" cm="1">
         <f t="array" ref="J20">IF(
@@ -68197,26 +68231,26 @@
   ),
   ""
 )</f>
-        <v>copy "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K20" s="1" t="str">
-        <f t="shared" ref="K20:K66" si="2">IF(F20="○","move /Y """&amp;G20&amp;""" """&amp;RIGHT(G20,LEN(G20)-FIND("●",SUBSTITUTE(G20,"\","●",LEN(G20)-LEN(SUBSTITUTE(G20,"\","")))))&amp;"_bak""","")</f>
-        <v>move /Y "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "fav.vssx_bak"</v>
+        <f>IF(F20="○","move /Y """&amp;G20&amp;""" """&amp;RIGHT(G20,LEN(G20)-FIND("●",SUBSTITUTE(G20,"\","●",LEN(G20)-LEN(SUBSTITUTE(G20,"\","")))))&amp;"_bak""","")</f>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "Outlook_bak"</v>
       </c>
       <c r="L20" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template\fav.vssx"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Microsoft\Outlook" "C:\codes\vba\outlook\AddIns"</v>
       </c>
       <c r="M20" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="6" t="s">
-        <v>876</v>
+      <c r="A21" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>1135</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>149</v>
@@ -68225,20 +68259,20 @@
         <v>149</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G21" s="172" t="s">
-        <v>148</v>
+      <c r="G21" s="1" t="s">
+        <v>950</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>9</v>
+        <v>158</v>
       </c>
       <c r="I21" s="1" t="str" cm="1">
         <f t="array" ref="I21">IF($F21="○","mkdir """&amp;[2]!getdirpath($H21)&amp;"""","")</f>
-        <v>mkdir "C:\codes"</v>
+        <v>mkdir "C:\other\template"</v>
       </c>
       <c r="J21" s="1" t="str" cm="1">
         <f t="array" ref="J21">IF(
@@ -68250,15 +68284,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac" /MIR /XD "System Volume Information"</v>
+        <v>copy "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template"</v>
       </c>
       <c r="K21" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Hidemaru\macro" "macro_bak"</v>
+        <f t="shared" ref="K21:K67" si="3">IF(F21="○","move /Y """&amp;G21&amp;""" """&amp;RIGHT(G21,LEN(G21)-FIND("●",SUBSTITUTE(G21,"\","●",LEN(G21)-LEN(SUBSTITUTE(G21,"\","")))))&amp;"_bak""","")</f>
+        <v>move /Y "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "fav.vssx_bak"</v>
       </c>
       <c r="L21" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac"</v>
+        <v>mklink "%MYDIRPATH_DOCUMENTS%\個人用図形\fav.vssx" "C:\other\template\fav.vssx"</v>
       </c>
       <c r="M21" t="s">
         <v>1277</v>
@@ -68269,7 +68303,7 @@
         <v>876</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>149</v>
@@ -68284,10 +68318,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="172" t="s">
-        <v>881</v>
+        <v>148</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>882</v>
+        <v>9</v>
       </c>
       <c r="I22" s="1" t="str" cm="1">
         <f t="array" ref="I22">IF($F22="○","mkdir """&amp;[2]!getdirpath($H22)&amp;"""","")</f>
@@ -68303,15 +68337,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K22" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Hidemaru\setting" "setting_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Hidemaru\macro" "macro_bak"</v>
       </c>
       <c r="L22" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru"</v>
+        <v>mklink /d "C:\prg_exe\Hidemaru\macro" "C:\codes\hmac"</v>
       </c>
       <c r="M22" t="s">
         <v>1277</v>
@@ -68322,7 +68356,7 @@
         <v>876</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>880</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>149</v>
@@ -68331,20 +68365,20 @@
         <v>149</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>12</v>
+      <c r="G23" s="172" t="s">
+        <v>881</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>3</v>
+        <v>882</v>
       </c>
       <c r="I23" s="1" t="str" cm="1">
         <f t="array" ref="I23">IF($F23="○","mkdir """&amp;[2]!getdirpath($H23)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim"</v>
+        <v>mkdir "C:\codes"</v>
       </c>
       <c r="J23" s="1" t="str" cm="1">
         <f t="array" ref="J23">IF(
@@ -68356,15 +68390,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim"</v>
+        <v>robocopy "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K23" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_gvimrc" "_gvimrc_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Hidemaru\setting" "setting_bak"</v>
       </c>
       <c r="L23" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim\_gvimrc"</v>
+        <v>mklink /d "C:\prg_exe\Hidemaru\setting" "C:\codes\hidemaru"</v>
       </c>
       <c r="M23" t="s">
         <v>1277</v>
@@ -68375,7 +68409,7 @@
         <v>876</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>149</v>
@@ -68390,10 +68424,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24" s="1" t="str" cm="1">
         <f t="array" ref="I24">IF($F24="○","mkdir """&amp;[2]!getdirpath($H24)&amp;"""","")</f>
@@ -68409,15 +68443,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_vimrc" "C:\codes\vim"</v>
+        <v>copy "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim"</v>
       </c>
       <c r="K24" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_vimrc" "_vimrc_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_gvimrc" "_gvimrc_bak"</v>
       </c>
       <c r="L24" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_vimrc" "C:\codes\vim\_vimrc"</v>
+        <v>mklink "C:\prg_exe\Vim\_gvimrc" "C:\codes\vim\_gvimrc"</v>
       </c>
       <c r="M24" t="s">
         <v>1277</v>
@@ -68428,7 +68462,7 @@
         <v>876</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>149</v>
@@ -68442,15 +68476,15 @@
       <c r="F25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G25" s="172" t="s">
-        <v>895</v>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>894</v>
+        <v>4</v>
       </c>
       <c r="I25" s="1" t="str" cm="1">
         <f t="array" ref="I25">IF($F25="○","mkdir """&amp;[2]!getdirpath($H25)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
+        <v>mkdir "C:\codes\vim"</v>
       </c>
       <c r="J25" s="1" t="str" cm="1">
         <f t="array" ref="J25">IF(
@@ -68462,15 +68496,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_vimrc" "C:\codes\vim"</v>
       </c>
       <c r="K25" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "bufferlist.vim_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_vimrc" "_vimrc_bak"</v>
       </c>
       <c r="L25" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_vimrc" "C:\codes\vim\_vimrc"</v>
       </c>
       <c r="M25" t="s">
         <v>1277</v>
@@ -68481,7 +68515,7 @@
         <v>876</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>149</v>
@@ -68496,14 +68530,14 @@
         <v>0</v>
       </c>
       <c r="G26" s="172" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>6</v>
+        <v>894</v>
       </c>
       <c r="I26" s="1" t="str" cm="1">
         <f t="array" ref="I26">IF($F26="○","mkdir """&amp;[2]!getdirpath($H26)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
       </c>
       <c r="J26" s="1" t="str" cm="1">
         <f t="array" ref="J26">IF(
@@ -68515,15 +68549,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin"</v>
       </c>
       <c r="K26" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "favex.vim_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "bufferlist.vim_bak"</v>
       </c>
       <c r="L26" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin\favex.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim" "C:\codes\vim\_plugins_user\bufferlist.vim\plugin\bufferlist.vim"</v>
       </c>
       <c r="M26" t="s">
         <v>1277</v>
@@ -68534,7 +68568,7 @@
         <v>876</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>149</v>
@@ -68549,14 +68583,14 @@
         <v>0</v>
       </c>
       <c r="G27" s="172" t="s">
-        <v>14</v>
+        <v>896</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" s="1" t="str" cm="1">
         <f t="array" ref="I27">IF($F27="○","mkdir """&amp;[2]!getdirpath($H27)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\FavEx"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
       </c>
       <c r="J27" s="1" t="str" cm="1">
         <f t="array" ref="J27">IF(
@@ -68568,15 +68602,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin"</v>
       </c>
       <c r="K27" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "favlist_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "favex.vim_bak"</v>
       </c>
       <c r="L27" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx\favlist"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\plugin\favex.vim" "C:\codes\vim\_plugins_user\FavEx\plugin\favex.vim"</v>
       </c>
       <c r="M27" t="s">
         <v>1277</v>
@@ -68587,7 +68621,7 @@
         <v>876</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1519</v>
+        <v>885</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>149</v>
@@ -68602,14 +68636,14 @@
         <v>0</v>
       </c>
       <c r="G28" s="172" t="s">
-        <v>897</v>
+        <v>14</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" s="1" t="str" cm="1">
         <f t="array" ref="I28">IF($F28="○","mkdir """&amp;[2]!getdirpath($H28)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\FavEx"</v>
       </c>
       <c r="J28" s="1" t="str" cm="1">
         <f t="array" ref="J28">IF(
@@ -68621,15 +68655,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx"</v>
       </c>
       <c r="K28" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "jellybeans.vim_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "favlist_bak"</v>
       </c>
       <c r="L28" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\FavEx\favlist" "C:\codes\vim\_plugins_user\FavEx\favlist"</v>
       </c>
       <c r="M28" t="s">
         <v>1277</v>
@@ -68640,7 +68674,7 @@
         <v>876</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>886</v>
+        <v>1518</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>149</v>
@@ -68655,14 +68689,14 @@
         <v>0</v>
       </c>
       <c r="G29" s="172" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I29" s="1" t="str" cm="1">
         <f t="array" ref="I29">IF($F29="○","mkdir """&amp;[2]!getdirpath($H29)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
       </c>
       <c r="J29" s="1" t="str" cm="1">
         <f t="array" ref="J29">IF(
@@ -68674,15 +68708,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors"</v>
       </c>
       <c r="K29" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "mark.vim_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "jellybeans.vim_bak"</v>
       </c>
       <c r="L29" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin\mark.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim" "C:\codes\vim\_plugins_user\jellybeans.vim\colors\jellybeans.vim"</v>
       </c>
       <c r="M29" t="s">
         <v>1277</v>
@@ -68693,7 +68727,7 @@
         <v>876</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>149</v>
@@ -68708,14 +68742,14 @@
         <v>0</v>
       </c>
       <c r="G30" s="172" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="1" t="str" cm="1">
         <f t="array" ref="I30">IF($F30="○","mkdir """&amp;[2]!getdirpath($H30)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
       </c>
       <c r="J30" s="1" t="str" cm="1">
         <f t="array" ref="J30">IF(
@@ -68727,15 +68761,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin"</v>
       </c>
       <c r="K30" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "qfixgrep.vim_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "mark.vim_bak"</v>
       </c>
       <c r="L30" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload\qfixgrep.vim"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\mark.vim\plugin\mark.vim" "C:\codes\vim\_plugins_user\mark.vim\plugin\mark.vim"</v>
       </c>
       <c r="M30" t="s">
         <v>1277</v>
@@ -68746,7 +68780,7 @@
         <v>876</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>149</v>
@@ -68761,14 +68795,14 @@
         <v>0</v>
       </c>
       <c r="G31" s="172" t="s">
-        <v>152</v>
+        <v>899</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="I31" s="1" t="str" cm="1">
         <f t="array" ref="I31">IF($F31="○","mkdir """&amp;[2]!getdirpath($H31)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vscode"</v>
+        <v>mkdir "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
       </c>
       <c r="J31" s="1" t="str" cm="1">
         <f t="array" ref="J31">IF(
@@ -68780,15 +68814,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload"</v>
       </c>
       <c r="K31" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "keybindings.json_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "qfixgrep.vim_bak"</v>
       </c>
       <c r="L31" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode\keybindings.json"</v>
+        <v>mklink "C:\prg_exe\Vim\_plugins_user\qfixapp\autoload\qfixgrep.vim" "C:\codes\vim\_plugins_user\qfixapp\autoload\qfixgrep.vim"</v>
       </c>
       <c r="M31" t="s">
         <v>1277</v>
@@ -68799,7 +68833,7 @@
         <v>876</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>149</v>
@@ -68814,10 +68848,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="172" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I32" s="1" t="str" cm="1">
         <f t="array" ref="I32">IF($F32="○","mkdir """&amp;[2]!getdirpath($H32)&amp;"""","")</f>
@@ -68833,15 +68867,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode"</v>
       </c>
       <c r="K32" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\VSCode\data\user-data\User\settings.json" "settings.json_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "keybindings.json_bak"</v>
       </c>
       <c r="L32" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode\settings.json"</v>
+        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\keybindings.json" "C:\codes\vscode\keybindings.json"</v>
       </c>
       <c r="M32" t="s">
         <v>1277</v>
@@ -68852,7 +68886,7 @@
         <v>876</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1120</v>
+        <v>878</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>149</v>
@@ -68867,10 +68901,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="172" t="s">
-        <v>1119</v>
+        <v>154</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1118</v>
+        <v>155</v>
       </c>
       <c r="I33" s="1" t="str" cm="1">
         <f t="array" ref="I33">IF($F33="○","mkdir """&amp;[2]!getdirpath($H33)&amp;"""","")</f>
@@ -68886,23 +68920,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode"</v>
+        <v>copy "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode"</v>
       </c>
       <c r="K33" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\VSCode\_update.ps1" "_update.ps1_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\VSCode\data\user-data\User\settings.json" "settings.json_bak"</v>
       </c>
       <c r="L33" s="1" t="str">
-        <f t="shared" ref="L33:L38" si="3">IF(
-  F33="○",
-  "mklink "&amp;IF(
-    E33="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G33&amp;""" """&amp;H33&amp;"""",
-  ""
-)</f>
-        <v>mklink "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode\update.ps1"</v>
+        <f t="shared" si="1"/>
+        <v>mklink "C:\prg_exe\VSCode\data\user-data\User\settings.json" "C:\codes\vscode\settings.json"</v>
       </c>
       <c r="M33" t="s">
         <v>1277</v>
@@ -68913,13 +68939,13 @@
         <v>876</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>16</v>
@@ -68928,14 +68954,14 @@
         <v>0</v>
       </c>
       <c r="G34" s="172" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="I34" s="1" t="str" cm="1">
         <f t="array" ref="I34">IF($F34="○","mkdir """&amp;[2]!getdirpath($H34)&amp;"""","")</f>
-        <v>mkdir "C:\codes\vbs\tools\x-finder"</v>
+        <v>mkdir "C:\codes\vscode"</v>
       </c>
       <c r="J34" s="1" t="str" cm="1">
         <f t="array" ref="J34">IF(
@@ -68947,15 +68973,23 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder"</v>
+        <v>copy "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode"</v>
       </c>
       <c r="K34" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "MergeToIniFromTabbak.vbs_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\VSCode\_update.ps1" "_update.ps1_bak"</v>
       </c>
       <c r="L34" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder\MergeToIniFromTabbak.vbs"</v>
+        <f t="shared" ref="L34:L39" si="4">IF(
+  F34="○",
+  "mklink "&amp;IF(
+    E34="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G34&amp;""" """&amp;H34&amp;"""",
+  ""
+)</f>
+        <v>mklink "C:\prg_exe\VSCode\_update.ps1" "C:\codes\vscode\update.ps1"</v>
       </c>
       <c r="M34" t="s">
         <v>1277</v>
@@ -68966,7 +69000,7 @@
         <v>876</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>0</v>
@@ -68981,14 +69015,14 @@
         <v>0</v>
       </c>
       <c r="G35" s="172" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="I35" s="1" t="str" cm="1">
         <f t="array" ref="I35">IF($F35="○","mkdir """&amp;[2]!getdirpath($H35)&amp;"""","")</f>
-        <v>mkdir "C:\codes\bat\tools\x-finder"</v>
+        <v>mkdir "C:\codes\vbs\tools\x-finder"</v>
       </c>
       <c r="J35" s="1" t="str" cm="1">
         <f t="array" ref="J35">IF(
@@ -69000,15 +69034,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder"</v>
+        <v>copy "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder"</v>
       </c>
       <c r="K35" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "BackupIniToTabbak.bat_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "MergeToIniFromTabbak.vbs_bak"</v>
       </c>
       <c r="L35" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder\BackupIniToTabbak.bat"</v>
+        <f t="shared" si="4"/>
+        <v>mklink "C:\prg_exe\X-Finder\MergeToIniFromTabbak.vbs" "C:\codes\vbs\tools\x-finder\MergeToIniFromTabbak.vbs"</v>
       </c>
       <c r="M35" t="s">
         <v>1277</v>
@@ -69019,13 +69053,13 @@
         <v>876</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>875</v>
+        <v>1130</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>16</v>
@@ -69033,15 +69067,15 @@
       <c r="F36" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>1114</v>
+      <c r="G36" s="172" t="s">
+        <v>1129</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>147</v>
+        <v>1128</v>
       </c>
       <c r="I36" s="1" t="str" cm="1">
         <f t="array" ref="I36">IF($F36="○","mkdir """&amp;[2]!getdirpath($H36)&amp;"""","")</f>
-        <v>mkdir "C:\codes\winterm"</v>
+        <v>mkdir "C:\codes\bat\tools\x-finder"</v>
       </c>
       <c r="J36" s="1" t="str" cm="1">
         <f t="array" ref="J36">IF(
@@ -69053,15 +69087,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm"</v>
+        <v>copy "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder"</v>
       </c>
       <c r="K36" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\WindowsTerminal\settings\settings.json" "settings.json_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "BackupIniToTabbak.bat_bak"</v>
       </c>
       <c r="L36" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm\settings.json"</v>
+        <f t="shared" si="4"/>
+        <v>mklink "C:\prg_exe\X-Finder\BackupIniToTabbak.bat" "C:\codes\bat\tools\x-finder\BackupIniToTabbak.bat"</v>
       </c>
       <c r="M36" t="s">
         <v>1277</v>
@@ -69072,13 +69106,13 @@
         <v>876</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1141</v>
+        <v>875</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>314</v>
+        <v>149</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>315</v>
+        <v>149</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>16</v>
@@ -69086,15 +69120,15 @@
       <c r="F37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>1143</v>
+      <c r="G37" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="I37" s="1" t="str" cm="1">
         <f t="array" ref="I37">IF($F37="○","mkdir """&amp;[2]!getdirpath($H37)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_alluser"</v>
+        <v>mkdir "C:\codes\winterm"</v>
       </c>
       <c r="J37" s="1" t="str" cm="1">
         <f t="array" ref="J37">IF(
@@ -69106,15 +69140,15 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser"</v>
+        <v>copy "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm"</v>
       </c>
       <c r="K37" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg\Git\etc\gitconfig" "gitconfig_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\WindowsTerminal\settings\settings.json" "settings.json_bak"</v>
       </c>
       <c r="L37" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser\gitconfig"</v>
+        <f t="shared" si="4"/>
+        <v>mklink "C:\prg_exe\WindowsTerminal\settings\settings.json" "C:\codes\winterm\settings.json"</v>
       </c>
       <c r="M37" t="s">
         <v>1277</v>
@@ -69125,7 +69159,7 @@
         <v>876</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>314</v>
@@ -69139,15 +69173,15 @@
       <c r="F38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>1142</v>
+      <c r="G38" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>1143</v>
       </c>
       <c r="I38" s="1" t="str" cm="1">
         <f t="array" ref="I38">IF($F38="○","mkdir """&amp;[2]!getdirpath($H38)&amp;"""","")</f>
-        <v>mkdir "C:\codes\git\setting_myuser"</v>
+        <v>mkdir "C:\codes\git\setting_alluser"</v>
       </c>
       <c r="J38" s="1" t="str" cm="1">
         <f t="array" ref="J38">IF(
@@ -69159,15 +69193,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser"</v>
+        <v>copy "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser"</v>
       </c>
       <c r="K38" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\.gitconfig" ".gitconfig_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg\Git\etc\gitconfig" "gitconfig_bak"</v>
       </c>
       <c r="L38" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>mklink "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser\.gitconfig"</v>
+        <f t="shared" si="4"/>
+        <v>mklink "C:\prg\Git\etc\gitconfig" "C:\codes\git\setting_alluser\gitconfig"</v>
       </c>
       <c r="M38" t="s">
         <v>1277</v>
@@ -69178,13 +69212,13 @@
         <v>876</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1442</v>
+        <v>1140</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>149</v>
+        <v>314</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>149</v>
+        <v>315</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>16</v>
@@ -69193,14 +69227,14 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1494</v>
+        <v>870</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1441</v>
+        <v>1142</v>
       </c>
       <c r="I39" s="1" t="str" cm="1">
         <f t="array" ref="I39">IF($F39="○","mkdir """&amp;[2]!getdirpath($H39)&amp;"""","")</f>
-        <v>mkdir "C:\codes\wezterm"</v>
+        <v>mkdir "C:\codes\git\setting_myuser"</v>
       </c>
       <c r="J39" s="1" t="str" cm="1">
         <f t="array" ref="J39">IF(
@@ -69212,56 +69246,48 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm"</v>
+        <v>copy "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser"</v>
       </c>
       <c r="K39" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\.config\wezterm\wezterm.lua" "wezterm.lua_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\.gitconfig" ".gitconfig_bak"</v>
       </c>
       <c r="L39" s="1" t="str">
-        <f t="shared" ref="L39" si="4">IF(
-  F39="○",
-  "mklink "&amp;IF(
-    E39="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G39&amp;""" """&amp;H39&amp;"""",
-  ""
-)</f>
-        <v>mklink "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm\wezterm.lua"</v>
+        <f t="shared" si="4"/>
+        <v>mklink "%USERPROFILE%\.gitconfig" "C:\codes\git\setting_myuser\.gitconfig"</v>
       </c>
       <c r="M39" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="1" t="s">
-        <v>874</v>
+      <c r="A40" s="6" t="s">
+        <v>876</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>80</v>
+        <v>1442</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>314</v>
+        <v>149</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>315</v>
+        <v>149</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1397</v>
+        <v>1494</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1061</v>
+        <v>1441</v>
       </c>
       <c r="I40" s="1" t="str" cm="1">
         <f t="array" ref="I40">IF($F40="○","mkdir """&amp;[2]!getdirpath($H40)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\HNXgrep"</v>
+        <v>mkdir "C:\codes\wezterm"</v>
       </c>
       <c r="J40" s="1" t="str" cm="1">
         <f t="array" ref="J40">IF(
@@ -69273,15 +69299,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep" /MIR /XD "System Volume Information"</v>
+        <v>copy "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm"</v>
       </c>
       <c r="K40" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Local\HNXgrep" "HNXgrep_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\.config\wezterm\wezterm.lua" "wezterm.lua_bak"</v>
       </c>
       <c r="L40" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep"</v>
+        <f t="shared" ref="L40" si="5">IF(
+  F40="○",
+  "mklink "&amp;IF(
+    E40="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G40&amp;""" """&amp;H40&amp;"""",
+  ""
+)</f>
+        <v>mklink "%USERPROFILE%\.config\wezterm\wezterm.lua" "C:\codes\wezterm\wezterm.lua"</v>
       </c>
       <c r="M40" t="s">
         <v>1277</v>
@@ -69292,7 +69326,7 @@
         <v>874</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>314</v>
@@ -69307,14 +69341,14 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>900</v>
+        <v>1397</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="I41" s="1" t="str" cm="1">
         <f t="array" ref="I41">IF($F41="○","mkdir """&amp;[2]!getdirpath($H41)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Icaros"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\HNXgrep"</v>
       </c>
       <c r="J41" s="1" t="str" cm="1">
         <f t="array" ref="J41">IF(
@@ -69326,15 +69360,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K41" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Local\Icaros" "Icaros_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Local\HNXgrep" "HNXgrep_bak"</v>
       </c>
       <c r="L41" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Local\HNXgrep" "G:\マイドライブ\100_programs\120_setting\HNXgrep\HNXgrep"</v>
       </c>
       <c r="M41" t="s">
         <v>1277</v>
@@ -69345,7 +69379,7 @@
         <v>874</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>314</v>
@@ -69360,14 +69394,14 @@
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>872</v>
+        <v>900</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I42" s="1" t="str" cm="1">
         <f t="array" ref="I42">IF($F42="○","mkdir """&amp;[2]!getdirpath($H42)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\EasyShot"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Icaros"</v>
       </c>
       <c r="J42" s="1" t="str" cm="1">
         <f t="array" ref="J42">IF(
@@ -69379,15 +69413,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K42" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\GZ20" "GZ20_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Local\Icaros" "Icaros_bak"</v>
       </c>
       <c r="L42" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Local\Icaros" "G:\マイドライブ\100_programs\120_setting\Icaros\Icaros"</v>
       </c>
       <c r="M42" t="s">
         <v>1277</v>
@@ -69398,7 +69432,7 @@
         <v>874</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>314</v>
@@ -69413,14 +69447,14 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>901</v>
+        <v>872</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I43" s="1" t="str" cm="1">
         <f t="array" ref="I43">IF($F43="○","mkdir """&amp;[2]!getdirpath($H43)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\DeInput"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\EasyShot"</v>
       </c>
       <c r="J43" s="1" t="str" cm="1">
         <f t="array" ref="J43">IF(
@@ -69432,15 +69466,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K43" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\KT Software" "KT Software_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\GZ20" "GZ20_bak"</v>
       </c>
       <c r="L43" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\GZ20" "G:\マイドライブ\100_programs\120_setting\EasyShot\GZ20"</v>
       </c>
       <c r="M43" t="s">
         <v>1277</v>
@@ -69451,7 +69485,7 @@
         <v>874</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>462</v>
+        <v>74</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>314</v>
@@ -69466,14 +69500,14 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1246</v>
+        <v>901</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I44" s="1" t="str" cm="1">
         <f t="array" ref="I44">IF($F44="○","mkdir """&amp;[2]!getdirpath($H44)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\MP3Tag"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\DeInput"</v>
       </c>
       <c r="J44" s="1" t="str" cm="1">
         <f t="array" ref="J44">IF(
@@ -69485,15 +69519,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K44" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Mp3tag" "Mp3tag_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\KT Software" "KT Software_bak"</v>
       </c>
       <c r="L44" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\KT Software" "G:\マイドライブ\100_programs\120_setting\DeInput\KT Software"</v>
       </c>
       <c r="M44" t="s">
         <v>1277</v>
@@ -69504,7 +69538,7 @@
         <v>874</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>462</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>314</v>
@@ -69516,19 +69550,19 @@
         <v>17</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" s="97" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H45" s="97" t="s">
-        <v>1248</v>
-      </c>
-      <c r="I45" s="97" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I45" s="1" t="str" cm="1">
         <f t="array" ref="I45">IF($F45="○","mkdir """&amp;[2]!getdirpath($H45)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J45" s="97" t="str" cm="1">
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\MP3Tag"</v>
+      </c>
+      <c r="J45" s="1" t="str" cm="1">
         <f t="array" ref="J45">IF(
   $F45="○",
   IF(
@@ -69538,15 +69572,15 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K45" s="97" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L45" s="97" t="str">
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K45" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Mp3tag" "Mp3tag_bak"</v>
+      </c>
+      <c r="L45" s="1" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Mp3tag" "G:\マイドライブ\100_programs\120_setting\MP3Tag\MP3Tag"</v>
       </c>
       <c r="M45" t="s">
         <v>1277</v>
@@ -69557,7 +69591,7 @@
         <v>874</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>314</v>
@@ -69569,19 +69603,19 @@
         <v>17</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="I46" s="1" t="str" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G46" s="97" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H46" s="97" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I46" s="97" t="str" cm="1">
         <f t="array" ref="I46">IF($F46="○","mkdir """&amp;[2]!getdirpath($H46)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Audacity"</v>
-      </c>
-      <c r="J46" s="1" t="str" cm="1">
+        <v/>
+      </c>
+      <c r="J46" s="97" t="str" cm="1">
         <f t="array" ref="J46">IF(
   $F46="○",
   IF(
@@ -69591,15 +69625,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity" /MIR /XD "System Volume Information"</v>
-      </c>
-      <c r="K46" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Audacity" "Audacity_bak"</v>
-      </c>
-      <c r="L46" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K46" s="97" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="L46" s="97" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity"</v>
+        <v/>
       </c>
       <c r="M46" t="s">
         <v>1277</v>
@@ -69610,7 +69644,7 @@
         <v>874</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>464</v>
+        <v>70</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>314</v>
@@ -69625,14 +69659,14 @@
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1474</v>
+        <v>866</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="I47" s="1" t="str" cm="1">
         <f t="array" ref="I47">IF($F47="○","mkdir """&amp;[2]!getdirpath($H47)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Subversion"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Audacity"</v>
       </c>
       <c r="J47" s="1" t="str" cm="1">
         <f t="array" ref="J47">IF(
@@ -69644,15 +69678,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K47" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Subversion" "Subversion_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Audacity" "Audacity_bak"</v>
       </c>
       <c r="L47" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Audacity" "G:\マイドライブ\100_programs\120_setting\Audacity\Audacity"</v>
       </c>
       <c r="M47" t="s">
         <v>1277</v>
@@ -69663,7 +69697,7 @@
         <v>874</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>49</v>
+        <v>464</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>314</v>
@@ -69678,14 +69712,14 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>889</v>
+        <v>1474</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="I48" s="1" t="str" cm="1">
         <f t="array" ref="I48">IF($F48="○","mkdir """&amp;[2]!getdirpath($H48)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseGit"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Subversion"</v>
       </c>
       <c r="J48" s="1" t="str" cm="1">
         <f t="array" ref="J48">IF(
@@ -69697,15 +69731,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K48" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\TortoiseGit" "TortoiseGit_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Subversion" "Subversion_bak"</v>
       </c>
       <c r="L48" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Subversion" "G:\マイドライブ\100_programs\120_setting\Subversion\Subversion"</v>
       </c>
       <c r="M48" t="s">
         <v>1277</v>
@@ -69716,7 +69750,7 @@
         <v>874</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>314</v>
@@ -69731,14 +69765,14 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>867</v>
+        <v>889</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="I49" s="1" t="str" cm="1">
         <f t="array" ref="I49">IF($F49="○","mkdir """&amp;[2]!getdirpath($H49)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseSVN"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseGit"</v>
       </c>
       <c r="J49" s="1" t="str" cm="1">
         <f t="array" ref="J49">IF(
@@ -69750,15 +69784,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K49" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "TortoiseSVN_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\TortoiseGit" "TortoiseGit_bak"</v>
       </c>
       <c r="L49" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN"</v>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseGit" "G:\マイドライブ\100_programs\120_setting\TortoiseGit\TortoiseGit"</v>
       </c>
       <c r="M49" t="s">
         <v>1277</v>
@@ -69769,13 +69803,13 @@
         <v>874</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>945</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>17</v>
@@ -69784,14 +69818,14 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>942</v>
+        <v>867</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1137</v>
+        <v>1069</v>
       </c>
       <c r="I50" s="1" t="str" cm="1">
         <f t="array" ref="I50">IF($F50="○","mkdir """&amp;[2]!getdirpath($H50)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Anki2"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\TortoiseSVN"</v>
       </c>
       <c r="J50" s="1" t="str" cm="1">
         <f t="array" ref="J50">IF(
@@ -69803,23 +69837,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\AppData\Roaming\Anki2" "Anki2_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "TortoiseSVN_bak"</v>
       </c>
       <c r="L50" s="1" t="str">
-        <f>IF(
-  F50="○",
-  "mklink "&amp;IF(
-    E50="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G50&amp;""" """&amp;H50&amp;"""",
-  ""
-)</f>
-        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2"</v>
+        <f t="shared" si="1"/>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\TortoiseSVN" "G:\マイドライブ\100_programs\120_setting\TortoiseSVN\TortoiseSVN"</v>
       </c>
       <c r="M50" t="s">
         <v>1277</v>
@@ -69830,13 +69856,13 @@
         <v>874</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>463</v>
+        <v>945</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
@@ -69845,14 +69871,14 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1398</v>
+        <v>942</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1070</v>
+        <v>1137</v>
       </c>
       <c r="I51" s="1" t="str" cm="1">
         <f t="array" ref="I51">IF($F51="○","mkdir """&amp;[2]!getdirpath($H51)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Anki2"</v>
       </c>
       <c r="J51" s="1" t="str" cm="1">
         <f t="array" ref="J51">IF(
@@ -69864,15 +69890,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K51" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\_Serato_" "_Serato__bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\AppData\Roaming\Anki2" "Anki2_bak"</v>
       </c>
       <c r="L51" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mklink /d "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_"</v>
+        <f>IF(
+  F51="○",
+  "mklink "&amp;IF(
+    E51="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G51&amp;""" """&amp;H51&amp;"""",
+  ""
+)</f>
+        <v>mklink /d "%USERPROFILE%\AppData\Roaming\Anki2" "G:\マイドライブ\100_programs\120_setting\Anki2\Anki2"</v>
       </c>
       <c r="M51" t="s">
         <v>1277</v>
@@ -69883,7 +69917,7 @@
         <v>874</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>873</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>314</v>
@@ -69898,10 +69932,10 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>869</v>
+        <v>1398</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="I52" s="1" t="str" cm="1">
         <f t="array" ref="I52">IF($F52="○","mkdir """&amp;[2]!getdirpath($H52)&amp;"""","")</f>
@@ -69917,23 +69951,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K52" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\_Serato_Backup" "_Serato_Backup_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\_Serato_" "_Serato__bak"</v>
       </c>
       <c r="L52" s="1" t="str">
-        <f t="shared" ref="L52:L66" si="5">IF(
-  F52="○",
-  "mklink "&amp;IF(
-    E52="folder",
-    "/d ",
-    ""
-  )&amp;""""&amp;G52&amp;""" """&amp;H52&amp;"""",
-  ""
-)</f>
-        <v>mklink /d "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup"</v>
+        <f t="shared" si="1"/>
+        <v>mklink /d "%USERPROFILE%\Music\_Serato_" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_"</v>
       </c>
       <c r="M52" t="s">
         <v>1277</v>
@@ -69944,31 +69970,31 @@
         <v>874</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>944</v>
+        <v>873</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G53" s="97" t="s">
-        <v>943</v>
-      </c>
-      <c r="H53" s="97" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I53" s="97" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I53" s="1" t="str" cm="1">
         <f t="array" ref="I53">IF($F53="○","mkdir """&amp;[2]!getdirpath($H53)&amp;"""","")</f>
-        <v/>
-      </c>
-      <c r="J53" s="97" t="str" cm="1">
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\Serato"</v>
+      </c>
+      <c r="J53" s="1" t="str" cm="1">
         <f t="array" ref="J53">IF(
   $F53="○",
   IF(
@@ -69978,14 +70004,14 @@
   ),
   ""
 )</f>
-        <v/>
-      </c>
-      <c r="K53" s="97" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L53" s="97" t="str">
-        <f>IF(
+        <v>robocopy "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup" /MIR /XD "System Volume Information"</v>
+      </c>
+      <c r="K53" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\_Serato_Backup" "_Serato_Backup_bak"</v>
+      </c>
+      <c r="L53" s="1" t="str">
+        <f t="shared" ref="L53:L67" si="6">IF(
   F53="○",
   "mklink "&amp;IF(
     E53="folder",
@@ -69994,7 +70020,7 @@
   )&amp;""""&amp;G53&amp;""" """&amp;H53&amp;"""",
   ""
 )</f>
-        <v/>
+        <v>mklink /d "%USERPROFILE%\Music\_Serato_Backup" "G:\マイドライブ\100_programs\120_setting\Serato\_Serato_Backup"</v>
       </c>
       <c r="M53" t="s">
         <v>1277</v>
@@ -70014,16 +70040,16 @@
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G54" s="97" t="s">
-        <v>1146</v>
+        <v>943</v>
       </c>
       <c r="H54" s="97" t="s">
-        <v>1147</v>
+        <v>1078</v>
       </c>
       <c r="I54" s="97" t="str" cm="1">
         <f t="array" ref="I54">IF($F54="○","mkdir """&amp;[2]!getdirpath($H54)&amp;"""","")</f>
@@ -70042,7 +70068,7 @@
         <v/>
       </c>
       <c r="K54" s="97" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L54" s="97" t="str">
@@ -70066,31 +70092,31 @@
         <v>874</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1136</v>
+        <v>944</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="I55" s="1" t="str" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G55" s="97" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H55" s="97" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I55" s="97" t="str" cm="1">
         <f t="array" ref="I55">IF($F55="○","mkdir """&amp;[2]!getdirpath($H55)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
-      </c>
-      <c r="J55" s="1" t="str" cm="1">
+        <v/>
+      </c>
+      <c r="J55" s="97" t="str" cm="1">
         <f t="array" ref="J55">IF(
   $F55="○",
   IF(
@@ -70100,14 +70126,14 @@
   ),
   ""
 )</f>
-        <v>copy "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
-      </c>
-      <c r="K55" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "C:\prg_exe\X-Finder\XF.ini" "XF.ini_bak"</v>
-      </c>
-      <c r="L55" s="1" t="str">
-        <f t="shared" ref="L55" si="6">IF(
+        <v/>
+      </c>
+      <c r="K55" s="97" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="L55" s="97" t="str">
+        <f>IF(
   F55="○",
   "mklink "&amp;IF(
     E55="folder",
@@ -70116,7 +70142,7 @@
   )&amp;""""&amp;G55&amp;""" """&amp;H55&amp;"""",
   ""
 )</f>
-        <v>mklink "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder\XF.ini"</v>
+        <v/>
       </c>
       <c r="M55" t="s">
         <v>1277</v>
@@ -70127,29 +70153,29 @@
         <v>874</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>906</v>
+        <v>1136</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>315</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1399</v>
+        <v>1138</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1072</v>
+        <v>1139</v>
       </c>
       <c r="I56" s="1" t="str" cm="1">
         <f t="array" ref="I56">IF($F56="○","mkdir """&amp;[2]!getdirpath($H56)&amp;"""","")</f>
-        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
       </c>
       <c r="J56" s="1" t="str" cm="1">
         <f t="array" ref="J56">IF(
@@ -70161,15 +70187,23 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries" /MIR /XD "System Volume Information"</v>
+        <v>copy "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder"</v>
       </c>
       <c r="K56" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "Previous iTunes Libraries_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "C:\prg_exe\X-Finder\XF.ini" "XF.ini_bak"</v>
       </c>
       <c r="L56" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries"</v>
+        <f t="shared" ref="L56" si="7">IF(
+  F56="○",
+  "mklink "&amp;IF(
+    E56="folder",
+    "/d ",
+    ""
+  )&amp;""""&amp;G56&amp;""" """&amp;H56&amp;"""",
+  ""
+)</f>
+        <v>mklink "C:\prg_exe\X-Finder\XF.ini" "G:\マイドライブ\100_programs\120_setting\X-Finder\XF.ini"</v>
       </c>
       <c r="M56" t="s">
         <v>1277</v>
@@ -70180,7 +70214,7 @@
         <v>874</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>314</v>
@@ -70189,16 +70223,16 @@
         <v>315</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>903</v>
+        <v>1399</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="I57" s="1" t="str" cm="1">
         <f t="array" ref="I57">IF($F57="○","mkdir """&amp;[2]!getdirpath($H57)&amp;"""","")</f>
@@ -70214,15 +70248,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K57" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "iTunes Library Extras.itdb_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "Previous iTunes Libraries_bak"</v>
       </c>
       <c r="L57" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Extras.itdb"</v>
+        <f t="shared" si="6"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\Previous iTunes Libraries" "G:\マイドライブ\100_programs\120_setting\iTunes\Previous iTunes Libraries"</v>
       </c>
       <c r="M57" t="s">
         <v>1277</v>
@@ -70233,7 +70267,7 @@
         <v>874</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>314</v>
@@ -70248,10 +70282,10 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="I58" s="1" t="str" cm="1">
         <f t="array" ref="I58">IF($F58="○","mkdir """&amp;[2]!getdirpath($H58)&amp;"""","")</f>
@@ -70267,15 +70301,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K58" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "iTunes Library Genius.itdb_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "iTunes Library Extras.itdb_bak"</v>
       </c>
       <c r="L58" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Genius.itdb"</v>
+        <f t="shared" si="6"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Extras.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Extras.itdb"</v>
       </c>
       <c r="M58" t="s">
         <v>1277</v>
@@ -70286,7 +70320,7 @@
         <v>874</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>314</v>
@@ -70301,10 +70335,10 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="I59" s="1" t="str" cm="1">
         <f t="array" ref="I59">IF($F59="○","mkdir """&amp;[2]!getdirpath($H59)&amp;"""","")</f>
@@ -70320,15 +70354,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K59" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "iTunes Library.itl_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "iTunes Library Genius.itdb_bak"</v>
       </c>
       <c r="L59" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library.itl"</v>
+        <f t="shared" si="6"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library Genius.itdb" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library Genius.itdb"</v>
       </c>
       <c r="M59" t="s">
         <v>1277</v>
@@ -70339,7 +70373,7 @@
         <v>874</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>314</v>
@@ -70354,10 +70388,10 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="I60" s="1" t="str" cm="1">
         <f t="array" ref="I60">IF($F60="○","mkdir """&amp;[2]!getdirpath($H60)&amp;"""","")</f>
@@ -70373,15 +70407,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K60" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "iTunes Music Library.xml_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "iTunes Library.itl_bak"</v>
       </c>
       <c r="L60" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Music Library.xml"</v>
+        <f t="shared" si="6"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Library.itl" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Library.itl"</v>
       </c>
       <c r="M60" t="s">
         <v>1277</v>
@@ -70392,7 +70426,7 @@
         <v>874</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>314</v>
@@ -70406,11 +70440,11 @@
       <c r="F61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G61" s="172" t="s">
-        <v>912</v>
+      <c r="G61" s="1" t="s">
+        <v>911</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I61" s="1" t="str" cm="1">
         <f t="array" ref="I61">IF($F61="○","mkdir """&amp;[2]!getdirpath($H61)&amp;"""","")</f>
@@ -70426,15 +70460,15 @@
   ),
   ""
 )</f>
-        <v>copy "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K61" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\sentinel" "sentinel_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "iTunes Music Library.xml_bak"</v>
       </c>
       <c r="L61" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes\sentinel"</v>
+        <f t="shared" si="6"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\iTunes Music Library.xml" "G:\マイドライブ\100_programs\120_setting\iTunes\iTunes Music Library.xml"</v>
       </c>
       <c r="M61" t="s">
         <v>1277</v>
@@ -70442,10 +70476,10 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>314</v>
@@ -70454,20 +70488,20 @@
         <v>315</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>1367</v>
+      <c r="G62" s="172" t="s">
+        <v>912</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>313</v>
+        <v>1077</v>
       </c>
       <c r="I62" s="1" t="str" cm="1">
         <f t="array" ref="I62">IF($F62="○","mkdir """&amp;[2]!getdirpath($H62)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes\MobileSync"</v>
+        <v>mkdir "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="J62" s="1" t="str" cm="1">
         <f t="array" ref="J62">IF(
@@ -70479,15 +70513,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp" /MIR /XD "System Volume Information"</v>
+        <v>copy "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes"</v>
       </c>
       <c r="K62" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Apple\MobileSync\Backup" "Backup_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\sentinel" "sentinel_bak"</v>
       </c>
       <c r="L62" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink /d "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp"</v>
+        <f t="shared" si="6"/>
+        <v>mklink "%USERPROFILE%\Music\iTunes\sentinel" "G:\マイドライブ\100_programs\120_setting\iTunes\sentinel"</v>
       </c>
       <c r="M62" t="s">
         <v>1277</v>
@@ -70498,7 +70532,7 @@
         <v>888</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>314</v>
@@ -70513,14 +70547,14 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>316</v>
+        <v>1367</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I63" s="1" t="str" cm="1">
         <f t="array" ref="I63">IF($F63="○","mkdir """&amp;[2]!getdirpath($H63)&amp;"""","")</f>
-        <v>mkdir "X:\720_Evacuate_iTunes"</v>
+        <v>mkdir "X:\720_Evacuate_iTunes\MobileSync"</v>
       </c>
       <c r="J63" s="1" t="str" cm="1">
         <f t="array" ref="J63">IF(
@@ -70532,15 +70566,15 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K63" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\Album Artwork" "Album Artwork_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Apple\MobileSync\Backup" "Backup_bak"</v>
       </c>
       <c r="L63" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media"</v>
+        <f t="shared" si="6"/>
+        <v>mklink /d "%USERPROFILE%\Apple\MobileSync\Backup" "X:\720_Evacuate_iTunes\MobileSync\BackUp"</v>
       </c>
       <c r="M63" t="s">
         <v>1277</v>
@@ -70551,7 +70585,7 @@
         <v>888</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>314</v>
@@ -70566,10 +70600,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I64" s="1" t="str" cm="1">
         <f t="array" ref="I64">IF($F64="○","mkdir """&amp;[2]!getdirpath($H64)&amp;"""","")</f>
@@ -70585,32 +70619,48 @@
   ),
   ""
 )</f>
-        <v>robocopy "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync" /MIR /XD "System Volume Information"</v>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K64" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Media" "iTunes Media_bak"</v>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\Album Artwork" "Album Artwork_bak"</v>
       </c>
       <c r="L64" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>mklink /d "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync"</v>
+        <f t="shared" si="6"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\Album Artwork" "X:\720_Evacuate_iTunes\iTunes Media"</v>
       </c>
       <c r="M64" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
+      <c r="A65" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="I65" s="1" t="str" cm="1">
         <f t="array" ref="I65">IF($F65="○","mkdir """&amp;[2]!getdirpath($H65)&amp;"""","")</f>
-        <v/>
+        <v>mkdir "X:\720_Evacuate_iTunes"</v>
       </c>
       <c r="J65" s="1" t="str" cm="1">
         <f t="array" ref="J65">IF(
@@ -70622,15 +70672,15 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>robocopy "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync" /MIR /XD "System Volume Information"</v>
       </c>
       <c r="K65" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>move /Y "%USERPROFILE%\Music\iTunes\iTunes Media" "iTunes Media_bak"</v>
       </c>
       <c r="L65" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f t="shared" si="6"/>
+        <v>mklink /d "%USERPROFILE%\Music\iTunes\iTunes Media" "X:\720_Evacuate_iTunes\MobileSync"</v>
       </c>
       <c r="M65" t="s">
         <v>1277</v>
@@ -70662,115 +70712,152 @@
         <v/>
       </c>
       <c r="K66" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="L66" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M66" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
-      <c r="A68" t="s">
-        <v>926</v>
+    <row r="67" spans="1:13">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1" t="str" cm="1">
+        <f t="array" ref="I67">IF($F67="○","mkdir """&amp;[2]!getdirpath($H67)&amp;"""","")</f>
+        <v/>
+      </c>
+      <c r="J67" s="1" t="str" cm="1">
+        <f t="array" ref="J67">IF(
+  $F67="○",
+  IF(
+    $E67="file",
+    "copy """&amp;$G67&amp;""" """&amp;[2]!getdirpath($H67)&amp;"""",
+    "robocopy """&amp;$G67&amp;""" """&amp;H67&amp;""" /MIR /XD ""System Volume Information"""
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="K67" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="L67" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M67" t="s">
+        <v>1277</v>
       </c>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="95" t="s">
-        <v>925</v>
+      <c r="A69" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" t="s">
-        <v>891</v>
+      <c r="A70" s="95" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="95" t="s">
-        <v>890</v>
+      <c r="A71" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" t="s">
-        <v>892</v>
+      <c r="A72" s="95" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>918</v>
+        <v>893</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="95" t="s">
-        <v>921</v>
+      <c r="A79" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="95" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>941</v>
+      <c r="A81" s="95" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>1088</v>
+        <v>951</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
         <v>1115</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:L66" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A11:L67" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="7"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E66" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E67" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"file,folder"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F66 C12:D66" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:D67 F12:F67" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -71931,7 +72018,7 @@
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="174" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D48" s="174" t="s">
         <v>39</v>
@@ -71947,7 +72034,7 @@
       </c>
       <c r="B49" s="41"/>
       <c r="C49" s="174" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D49" s="174"/>
       <c r="E49" s="174"/>
@@ -71961,7 +72048,7 @@
       </c>
       <c r="B50" s="41"/>
       <c r="C50" s="36" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>39</v>
@@ -71988,7 +72075,7 @@
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="36" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D51" s="36" t="s">
         <v>518</v>
@@ -72015,7 +72102,7 @@
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="45" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D52" s="45" t="s">
         <v>518</v>
@@ -72042,7 +72129,7 @@
       </c>
       <c r="B53" s="41"/>
       <c r="C53" s="36" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>39</v>
@@ -72573,13 +72660,13 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="32" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B73" s="45" t="s">
         <v>1546</v>
       </c>
-      <c r="B73" s="45" t="s">
+      <c r="C73" s="36" t="s">
         <v>1547</v>
-      </c>
-      <c r="C73" s="36" t="s">
-        <v>1548</v>
       </c>
       <c r="D73" s="36" t="str">
         <f>$C73</f>
@@ -72604,7 +72691,7 @@
       <c r="A74" s="41"/>
       <c r="B74" s="144"/>
       <c r="C74" s="36" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D74" s="36" t="str">
         <f>$C74</f>
@@ -72626,7 +72713,7 @@
       <c r="A75" s="41"/>
       <c r="B75" s="144"/>
       <c r="C75" s="36" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D75" s="36" t="str">
         <f t="shared" ref="D75:E79" si="7">$C75</f>
@@ -72648,7 +72735,7 @@
       <c r="A76" s="41"/>
       <c r="B76" s="144"/>
       <c r="C76" s="36" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D76" s="36" t="str">
         <f t="shared" si="7"/>
@@ -73004,7 +73091,7 @@
         <v>1238</v>
       </c>
       <c r="C90" s="144" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D90" s="144" t="str">
         <f>$C90</f>
@@ -73131,11 +73218,11 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="33" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B95" s="32"/>
       <c r="C95" s="34" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D95" s="34" t="s">
         <v>310</v>
@@ -73160,7 +73247,7 @@
       </c>
       <c r="B96" s="41"/>
       <c r="C96" s="36" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D96" s="36" t="s">
         <v>1464</v>
@@ -73185,7 +73272,7 @@
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="36" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D97" s="36" t="str">
         <f t="shared" ref="D97:E99" si="9">C97</f>
@@ -73212,7 +73299,7 @@
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="36" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D98" s="36" t="str">
         <f t="shared" si="9"/>
@@ -73239,7 +73326,7 @@
       </c>
       <c r="B99" s="42"/>
       <c r="C99" s="38" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D99" s="38" t="str">
         <f t="shared" si="9"/>
@@ -73262,11 +73349,11 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="26" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B100" s="26"/>
       <c r="C100" s="26" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D100" s="26"/>
       <c r="E100" s="26"/>
@@ -73279,11 +73366,11 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="26" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="26" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="26"/>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://robocip20-my.sharepoint.com/personal/endo_tatsuya_robocip_or_jp/Documents/ドキュメント/_repos/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{0E8DEACF-3A2F-45BD-AAD8-EC9C0C256A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B70D513-9607-4648-8650-8F8FC2D7F038}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{0E8DEACF-3A2F-45BD-AAD8-EC9C0C256A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9842C8-1704-418C-81F7-5289DEEFCE7D}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="-6795" windowWidth="38385" windowHeight="42465" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="-6795" windowWidth="38385" windowHeight="42465" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$116</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$227</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$67</definedName>
@@ -375,7 +375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C79" authorId="0" shapeId="0" xr:uid="{CA356C80-7B70-4EE7-B6F8-8CB81F6261A9}">
+    <comment ref="C80" authorId="0" shapeId="0" xr:uid="{CA356C80-7B70-4EE7-B6F8-8CB81F6261A9}">
       <text>
         <r>
           <rPr>
@@ -391,7 +391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{AEB1A5C2-D3BB-4B5C-A1E6-36BA6B0143FC}">
+    <comment ref="D80" authorId="0" shapeId="0" xr:uid="{AEB1A5C2-D3BB-4B5C-A1E6-36BA6B0143FC}">
       <text>
         <r>
           <rPr>
@@ -407,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E79" authorId="0" shapeId="0" xr:uid="{9E937EA5-3343-4855-90CE-B7E0D415796E}">
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{9E937EA5-3343-4855-90CE-B7E0D415796E}">
       <text>
         <r>
           <rPr>
@@ -423,7 +423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="C90" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6438" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="1568">
   <si>
     <t>○</t>
   </si>
@@ -8264,6 +8264,10 @@
   </si>
   <si>
     <t>C:\codes\vbs\tools\win\file_ope\BackUpFiles.bat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>createhardlink ~/_dotfiles/.claude/settings.json .claude/settings.json</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -70876,7 +70880,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:I115"/>
+  <dimension ref="A2:I116"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -71536,7 +71540,7 @@
         <v>\cp -rf ~/_dotfiles/.bashrc ./.</v>
       </c>
       <c r="E31" s="36" t="str">
-        <f t="shared" ref="E31:E45" si="2">$C31</f>
+        <f t="shared" ref="E31:E46" si="2">$C31</f>
         <v>\cp -rf ~/_dotfiles/.bashrc ./.</v>
       </c>
       <c r="F31" s="37" t="s">
@@ -71590,7 +71594,7 @@
         <v>1473</v>
       </c>
       <c r="D33" s="36" t="str">
-        <f t="shared" ref="D33:D45" si="3">$C33</f>
+        <f t="shared" ref="D33:D46" si="3">$C33</f>
         <v>createhardlink ~/_dotfiles/.bashrc              .bashrc</v>
       </c>
       <c r="E33" s="36" t="str">
@@ -71848,15 +71852,15 @@
         <v>1097</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>1477</v>
+        <v>1567</v>
       </c>
       <c r="D42" s="36" t="str">
         <f t="shared" si="3"/>
-        <v>agt=gemini &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>createhardlink ~/_dotfiles/.claude/settings.json .claude/settings.json</v>
       </c>
       <c r="E42" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>agt=gemini &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>createhardlink ~/_dotfiles/.claude/settings.json .claude/settings.json</v>
       </c>
       <c r="F42" s="37" t="s">
         <v>0</v>
@@ -71877,15 +71881,15 @@
         <v>1097</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D43" s="36" t="str">
         <f t="shared" si="3"/>
-        <v>agt=claude &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=gemini &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="E43" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>agt=claude &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=gemini &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="F43" s="37" t="s">
         <v>0</v>
@@ -71906,15 +71910,15 @@
         <v>1097</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="D44" s="36" t="str">
         <f t="shared" si="3"/>
-        <v>agt=gemini &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=claude &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="E44" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>agt=gemini &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=claude &amp;&amp; skill=func-header-comment &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="F44" s="37" t="s">
         <v>0</v>
@@ -71935,15 +71939,15 @@
         <v>1097</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D45" s="36" t="str">
         <f t="shared" si="3"/>
-        <v>agt=claude &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=gemini &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="E45" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>agt=claude &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+        <v>agt=gemini &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
       </c>
       <c r="F45" s="37" t="s">
         <v>0</v>
@@ -71957,76 +71961,89 @@
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H46" s="134" t="s">
-        <v>1117</v>
-      </c>
+      <c r="A46" s="41" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D46" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>agt=claude &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+      </c>
+      <c r="E46" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>agt=claude &amp;&amp; skill=func-tree           &amp;&amp; createhardlink ~/_dotfiles/.ai_agents/skills/${skill}/SKILL.md .${agt}/skills/${skill}/SKILL.md</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H46" s="36"/>
       <c r="I46" t="s">
-        <v>1109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="B47" s="32" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>1348</v>
-      </c>
-      <c r="D47" s="34" t="s">
+      <c r="A47" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D47" s="26" t="s">
         <v>518</v>
       </c>
-      <c r="E47" s="34" t="s">
+      <c r="E47" s="26" t="s">
         <v>1197</v>
       </c>
-      <c r="F47" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H47" s="34" t="s">
-        <v>1116</v>
+      <c r="F47" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" s="134" t="s">
+        <v>1117</v>
       </c>
       <c r="I47" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="32" t="s">
         <v>517</v>
       </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="174" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D48" s="174" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="174"/>
-      <c r="F48" s="175"/>
-      <c r="G48" s="175"/>
-      <c r="H48" s="174"/>
+      <c r="B48" s="32" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1109</v>
+      </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="41" t="s">
@@ -72034,9 +72051,11 @@
       </c>
       <c r="B49" s="41"/>
       <c r="C49" s="174" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D49" s="174"/>
+        <v>1539</v>
+      </c>
+      <c r="D49" s="174" t="s">
+        <v>39</v>
+      </c>
       <c r="E49" s="174"/>
       <c r="F49" s="175"/>
       <c r="G49" s="175"/>
@@ -72047,27 +72066,14 @@
         <v>517</v>
       </c>
       <c r="B50" s="41"/>
-      <c r="C50" s="36" t="s">
-        <v>1541</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H50" s="36" t="s">
-        <v>537</v>
-      </c>
-      <c r="I50" t="s">
-        <v>28</v>
-      </c>
+      <c r="C50" s="174" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D50" s="174"/>
+      <c r="E50" s="174"/>
+      <c r="F50" s="175"/>
+      <c r="G50" s="175"/>
+      <c r="H50" s="174"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="41" t="s">
@@ -72075,13 +72081,13 @@
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="36" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>518</v>
+        <v>39</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>1197</v>
+        <v>39</v>
       </c>
       <c r="F51" s="37" t="s">
         <v>0</v>
@@ -72093,7 +72099,7 @@
         <v>537</v>
       </c>
       <c r="I51" t="s">
-        <v>1109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -72101,22 +72107,22 @@
         <v>517</v>
       </c>
       <c r="B52" s="41"/>
-      <c r="C52" s="45" t="s">
-        <v>1543</v>
-      </c>
-      <c r="D52" s="45" t="s">
+      <c r="C52" s="36" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D52" s="36" t="s">
         <v>518</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="36" t="s">
         <v>1197</v>
       </c>
-      <c r="F52" s="46" t="s">
+      <c r="F52" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="G52" s="46" t="s">
+      <c r="G52" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="36" t="s">
         <v>537</v>
       </c>
       <c r="I52" t="s">
@@ -72128,22 +72134,22 @@
         <v>517</v>
       </c>
       <c r="B53" s="41"/>
-      <c r="C53" s="36" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="36" t="s">
+      <c r="C53" s="45" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="E53" s="45" t="s">
         <v>1197</v>
       </c>
-      <c r="F53" s="37" t="s">
+      <c r="F53" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G53" s="37" t="s">
+      <c r="G53" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="H53" s="36" t="s">
+      <c r="H53" s="45" t="s">
         <v>537</v>
       </c>
       <c r="I53" t="s">
@@ -72154,15 +72160,15 @@
       <c r="A54" s="41" t="s">
         <v>517</v>
       </c>
-      <c r="B54" s="132"/>
+      <c r="B54" s="41"/>
       <c r="C54" s="36" t="s">
-        <v>1357</v>
+        <v>1544</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>39</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>39</v>
+        <v>1197</v>
       </c>
       <c r="F54" s="37" t="s">
         <v>0</v>
@@ -72174,105 +72180,105 @@
         <v>537</v>
       </c>
       <c r="I54" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="41" t="s">
+        <v>517</v>
+      </c>
+      <c r="B55" s="132"/>
+      <c r="C55" s="36" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H55" s="36" t="s">
+        <v>537</v>
+      </c>
+      <c r="I55" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="150" customFormat="1">
-      <c r="A55" s="42" t="s">
+    <row r="56" spans="1:9" s="150" customFormat="1">
+      <c r="A56" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="B55" s="148" t="s">
+      <c r="B56" s="148" t="s">
         <v>1199</v>
       </c>
-      <c r="C55" s="148" t="s">
+      <c r="C56" s="148" t="s">
         <v>1197</v>
       </c>
-      <c r="D55" s="151" t="s">
+      <c r="D56" s="151" t="s">
         <v>1202</v>
       </c>
-      <c r="E55" s="151" t="s">
+      <c r="E56" s="151" t="s">
         <v>1202</v>
       </c>
-      <c r="F55" s="149" t="s">
+      <c r="F56" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="G55" s="149" t="s">
+      <c r="G56" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="H55" s="148" t="s">
+      <c r="H56" s="148" t="s">
         <v>537</v>
       </c>
-      <c r="I55" s="150" t="s">
+      <c r="I56" s="150" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="135" t="s">
-        <v>519</v>
-      </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32" t="s">
-        <v>520</v>
-      </c>
-      <c r="D56" s="32" t="str">
-        <f>C$56</f>
-        <v>vim ~/.ssh/config</v>
-      </c>
-      <c r="E56" s="32" t="str">
-        <f>D$56</f>
-        <v>vim ~/.ssh/config</v>
-      </c>
-      <c r="F56" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="H56" s="32"/>
-      <c r="I56" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="100" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="98" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D57" s="98" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E57" s="98" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H57" s="26" t="s">
-        <v>1033</v>
-      </c>
+      <c r="A57" s="135" t="s">
+        <v>519</v>
+      </c>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32" t="s">
+        <v>520</v>
+      </c>
+      <c r="D57" s="32" t="str">
+        <f>C$57</f>
+        <v>vim ~/.ssh/config</v>
+      </c>
+      <c r="E57" s="32" t="str">
+        <f>D$57</f>
+        <v>vim ~/.ssh/config</v>
+      </c>
+      <c r="F57" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="H57" s="32"/>
       <c r="I57" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="100" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="98" t="s">
         <v>1035</v>
       </c>
-      <c r="D58" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E58" s="26" t="s">
-        <v>1197</v>
+      <c r="D58" s="98" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E58" s="98" t="s">
+        <v>1204</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>149</v>
@@ -72281,27 +72287,25 @@
         <v>149</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="I58" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="136" t="s">
-        <v>300</v>
-      </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="167" t="s">
-        <v>301</v>
-      </c>
-      <c r="D59" s="26" t="str">
-        <f>C59</f>
-        <v>省略（~/.tmux.conf参照）</v>
-      </c>
-      <c r="E59" s="26" t="str">
-        <f>D59</f>
-        <v>省略（~/.tmux.conf参照）</v>
+      <c r="A59" s="100" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="98" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>1197</v>
       </c>
       <c r="F59" s="15" t="s">
         <v>149</v>
@@ -72309,76 +72313,79 @@
       <c r="G59" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="H59" s="26"/>
+      <c r="H59" s="26" t="s">
+        <v>1034</v>
+      </c>
       <c r="I59" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="137" t="s">
-        <v>295</v>
-      </c>
-      <c r="B60" s="32" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C60" s="168" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D60" s="34" t="str">
+      <c r="A60" s="136" t="s">
+        <v>300</v>
+      </c>
+      <c r="B60" s="26"/>
+      <c r="C60" s="167" t="s">
+        <v>301</v>
+      </c>
+      <c r="D60" s="26" t="str">
         <f>C60</f>
-        <v>sudo apt install -y software-properties-common</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F60" s="35" t="s">
+        <v>省略（~/.tmux.conf参照）</v>
+      </c>
+      <c r="E60" s="26" t="str">
+        <f>D60</f>
+        <v>省略（~/.tmux.conf参照）</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G60" s="35" t="s">
+      <c r="G60" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="H60" s="34"/>
+      <c r="H60" s="26"/>
       <c r="I60" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="138" t="s">
+      <c r="A61" s="137" t="s">
         <v>295</v>
       </c>
-      <c r="B61" s="43"/>
-      <c r="C61" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="D61" s="36" t="str">
-        <f t="shared" ref="D61:E71" si="4">C61</f>
-        <v>sudo add-apt-repository ppa:greymd/tmux-xpanes</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F61" s="37" t="s">
+      <c r="B61" s="32" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C61" s="168" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D61" s="34" t="str">
+        <f>C61</f>
+        <v>sudo apt install -y software-properties-common</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F61" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="G61" s="37" t="s">
+      <c r="G61" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="H61" s="36"/>
+      <c r="H61" s="34"/>
       <c r="I61" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="139" t="s">
+      <c r="A62" s="138" t="s">
         <v>295</v>
       </c>
-      <c r="B62" s="44"/>
+      <c r="B62" s="43"/>
       <c r="C62" s="40" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D62" s="36" t="str">
-        <f t="shared" si="4"/>
-        <v>sudo apt update</v>
+        <f t="shared" ref="D62:E72" si="4">C62</f>
+        <v>sudo add-apt-repository ppa:greymd/tmux-xpanes</v>
       </c>
       <c r="E62" s="36" t="s">
         <v>39</v>
@@ -72395,70 +72402,71 @@
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="44" t="s">
+      <c r="A63" s="139" t="s">
         <v>295</v>
       </c>
-      <c r="B63" s="170"/>
+      <c r="B63" s="44"/>
       <c r="C63" s="40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D63" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>sudo apt install -y tmux-xpanes</v>
+        <v>sudo apt update</v>
       </c>
       <c r="E63" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F63" s="39" t="s">
+      <c r="F63" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="G63" s="39" t="s">
+      <c r="G63" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="H63" s="38"/>
+      <c r="H63" s="36"/>
       <c r="I63" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="145"/>
-      <c r="B64" s="38" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C64" s="169" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D64" s="38" t="str">
-        <f>C64</f>
-        <v>xpanes -e "top" "vmstat 1" "watch -n 1 free"</v>
-      </c>
-      <c r="E64" s="38" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F64" s="35" t="s">
+      <c r="A64" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="B64" s="170"/>
+      <c r="C64" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="D64" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>sudo apt install -y tmux-xpanes</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="G64" s="35" t="s">
+      <c r="G64" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="H64" s="34"/>
+      <c r="H64" s="38"/>
       <c r="I64" t="s">
-        <v>28</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="D65" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="E65" s="34" t="s">
-        <v>310</v>
+      <c r="A65" s="145"/>
+      <c r="B65" s="38" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C65" s="169" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D65" s="38" t="str">
+        <f>C65</f>
+        <v>xpanes -e "top" "vmstat 1" "watch -n 1 free"</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>1203</v>
       </c>
       <c r="F65" s="35" t="s">
         <v>149</v>
@@ -72468,30 +72476,30 @@
       </c>
       <c r="H65" s="34"/>
       <c r="I65" t="s">
-        <v>1109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="41" t="s">
+      <c r="A66" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="B66" s="41"/>
-      <c r="C66" s="36" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D66" s="36" t="s">
-        <v>1464</v>
-      </c>
-      <c r="E66" s="36" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H66" s="36"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="E66" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="G66" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="H66" s="34"/>
       <c r="I66" t="s">
         <v>1109</v>
       </c>
@@ -72502,15 +72510,13 @@
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="D67" s="36" t="str">
-        <f t="shared" si="4"/>
-        <v>git config --global core.editor vim</v>
-      </c>
-      <c r="E67" s="36" t="str">
-        <f t="shared" si="4"/>
-        <v>git config --global core.editor vim</v>
+        <v>1464</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E67" s="36" t="s">
+        <v>1464</v>
       </c>
       <c r="F67" s="37" t="s">
         <v>0</v>
@@ -72529,15 +72535,15 @@
       </c>
       <c r="B68" s="41"/>
       <c r="C68" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D68" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global diff.tool vimdiff</v>
+        <v>git config --global core.editor vim</v>
       </c>
       <c r="E68" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global diff.tool vimdiff</v>
+        <v>git config --global core.editor vim</v>
       </c>
       <c r="F68" s="37" t="s">
         <v>0</v>
@@ -72556,15 +72562,15 @@
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D69" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global difftool.prompt false</v>
+        <v>git config --global diff.tool vimdiff</v>
       </c>
       <c r="E69" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global difftool.prompt false</v>
+        <v>git config --global diff.tool vimdiff</v>
       </c>
       <c r="F69" s="37" t="s">
         <v>0</v>
@@ -72583,15 +72589,15 @@
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D70" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global merge.tool vimdiff</v>
+        <v>git config --global difftool.prompt false</v>
       </c>
       <c r="E70" s="36" t="str">
         <f t="shared" si="4"/>
-        <v>git config --global merge.tool vimdiff</v>
+        <v>git config --global difftool.prompt false</v>
       </c>
       <c r="F70" s="37" t="s">
         <v>0</v>
@@ -72609,97 +72615,99 @@
         <v>299</v>
       </c>
       <c r="B71" s="41"/>
-      <c r="C71" s="45" t="s">
+      <c r="C71" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="D71" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>git config --global merge.tool vimdiff</v>
+      </c>
+      <c r="E71" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>git config --global merge.tool vimdiff</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" s="36"/>
+      <c r="I71" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" s="41"/>
+      <c r="C72" s="45" t="s">
         <v>309</v>
       </c>
-      <c r="D71" s="45" t="str">
+      <c r="D72" s="45" t="str">
         <f t="shared" si="4"/>
         <v>git config --global mergetool.prompt false</v>
       </c>
-      <c r="E71" s="45" t="str">
+      <c r="E72" s="45" t="str">
         <f t="shared" si="4"/>
         <v>git config --global mergetool.prompt false</v>
       </c>
-      <c r="F71" s="46" t="s">
+      <c r="F72" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G71" s="46" t="s">
+      <c r="G72" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="H71" s="45"/>
-      <c r="I71" t="s">
+      <c r="H72" s="45"/>
+      <c r="I72" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="42" t="s">
+    <row r="73" spans="1:9">
+      <c r="A73" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="42"/>
-      <c r="C72" s="38" t="s">
+      <c r="B73" s="42"/>
+      <c r="C73" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="D72" s="38" t="str">
-        <f t="shared" ref="D72:E72" si="5">C72</f>
+      <c r="D73" s="38" t="str">
+        <f t="shared" ref="D73:E73" si="5">C73</f>
         <v>git config --global credential.helper store</v>
       </c>
-      <c r="E72" s="38" t="str">
+      <c r="E73" s="38" t="str">
         <f t="shared" si="5"/>
         <v>git config --global credential.helper store</v>
       </c>
-      <c r="F72" s="39" t="s">
+      <c r="F73" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="G72" s="39" t="s">
+      <c r="G73" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="H72" s="38"/>
-      <c r="I72" t="s">
+      <c r="H73" s="38"/>
+      <c r="I73" t="s">
         <v>1109</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="32" t="s">
-        <v>1545</v>
-      </c>
-      <c r="B73" s="45" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C73" s="36" t="s">
-        <v>1547</v>
-      </c>
-      <c r="D73" s="36" t="str">
-        <f>$C73</f>
-        <v>cd ~/_dotfiles</v>
-      </c>
-      <c r="E73" s="36" t="str">
-        <f>$C73</f>
-        <v>cd ~/_dotfiles</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H73" s="36"/>
-      <c r="I73" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="41"/>
-      <c r="B74" s="144"/>
+      <c r="A74" s="32" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B74" s="45" t="s">
+        <v>1546</v>
+      </c>
       <c r="C74" s="36" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D74" s="36" t="str">
         <f>$C74</f>
-        <v>git init</v>
+        <v>cd ~/_dotfiles</v>
       </c>
       <c r="E74" s="36" t="str">
-        <f t="shared" ref="E74:E76" si="6">$C74</f>
-        <v>git init</v>
+        <f>$C74</f>
+        <v>cd ~/_dotfiles</v>
       </c>
       <c r="F74" s="37" t="s">
         <v>0</v>
@@ -72708,20 +72716,23 @@
         <v>0</v>
       </c>
       <c r="H74" s="36"/>
+      <c r="I74" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="41"/>
       <c r="B75" s="144"/>
       <c r="C75" s="36" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D75" s="36" t="str">
-        <f t="shared" ref="D75:E79" si="7">$C75</f>
-        <v>git add *</v>
+        <f>$C75</f>
+        <v>git init</v>
       </c>
       <c r="E75" s="36" t="str">
-        <f t="shared" si="6"/>
-        <v>git add *</v>
+        <f t="shared" ref="E75:E77" si="6">$C75</f>
+        <v>git init</v>
       </c>
       <c r="F75" s="37" t="s">
         <v>0</v>
@@ -72735,15 +72746,15 @@
       <c r="A76" s="41"/>
       <c r="B76" s="144"/>
       <c r="C76" s="36" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D76" s="36" t="str">
-        <f t="shared" si="7"/>
-        <v>git commit -m 'initial commit'</v>
+        <f t="shared" ref="D76:E80" si="7">$C76</f>
+        <v>git add *</v>
       </c>
       <c r="E76" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>git commit -m 'initial commit'</v>
+        <v>git add *</v>
       </c>
       <c r="F76" s="37" t="s">
         <v>0</v>
@@ -72754,22 +72765,18 @@
       <c r="H76" s="36"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="41" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B77" s="45" t="s">
-        <v>1095</v>
-      </c>
+      <c r="A77" s="41"/>
+      <c r="B77" s="144"/>
       <c r="C77" s="36" t="s">
-        <v>1093</v>
+        <v>1550</v>
       </c>
       <c r="D77" s="36" t="str">
         <f t="shared" si="7"/>
-        <v>wget https://raw.githubusercontent.com/draemonash2/codes/master/sh/backup_files.sh</v>
+        <v>git commit -m 'initial commit'</v>
       </c>
       <c r="E77" s="36" t="str">
-        <f t="shared" si="7"/>
-        <v>wget https://raw.githubusercontent.com/draemonash2/codes/master/sh/backup_files.sh</v>
+        <f t="shared" si="6"/>
+        <v>git commit -m 'initial commit'</v>
       </c>
       <c r="F77" s="37" t="s">
         <v>0</v>
@@ -72778,27 +72785,24 @@
         <v>0</v>
       </c>
       <c r="H77" s="36"/>
-      <c r="I77" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="41" t="s">
         <v>1096</v>
       </c>
-      <c r="B78" s="132" t="s">
+      <c r="B78" s="45" t="s">
         <v>1095</v>
       </c>
       <c r="C78" s="36" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D78" s="36" t="str">
         <f t="shared" si="7"/>
-        <v>mv backup_files.sh _backup_files.sh</v>
+        <v>wget https://raw.githubusercontent.com/draemonash2/codes/master/sh/backup_files.sh</v>
       </c>
       <c r="E78" s="36" t="str">
         <f t="shared" si="7"/>
-        <v>mv backup_files.sh _backup_files.sh</v>
+        <v>wget https://raw.githubusercontent.com/draemonash2/codes/master/sh/backup_files.sh</v>
       </c>
       <c r="F78" s="37" t="s">
         <v>0</v>
@@ -72812,82 +72816,87 @@
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="42" t="s">
+      <c r="A79" s="41" t="s">
         <v>1096</v>
       </c>
-      <c r="B79" s="38" t="s">
+      <c r="B79" s="132" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C79" s="36" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D79" s="36" t="str">
+        <f t="shared" si="7"/>
+        <v>mv backup_files.sh _backup_files.sh</v>
+      </c>
+      <c r="E79" s="36" t="str">
+        <f t="shared" si="7"/>
+        <v>mv backup_files.sh _backup_files.sh</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H79" s="36"/>
+      <c r="I79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="42" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B80" s="38" t="s">
         <v>1099</v>
       </c>
-      <c r="C79" s="38" t="s">
+      <c r="C80" s="38" t="s">
         <v>1098</v>
       </c>
-      <c r="D79" s="38" t="str">
+      <c r="D80" s="38" t="str">
         <f t="shared" si="7"/>
         <v>crontab -e</v>
       </c>
-      <c r="E79" s="38" t="str">
+      <c r="E80" s="38" t="str">
         <f t="shared" si="7"/>
         <v>crontab -e</v>
       </c>
-      <c r="F79" s="39" t="s">
+      <c r="F80" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="G79" s="39" t="s">
+      <c r="G80" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="H79" s="38"/>
-      <c r="I79" t="s">
+      <c r="H80" s="38"/>
+      <c r="I80" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B80" s="33" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C80" s="34" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D80" s="34" t="str">
-        <f>C80</f>
-        <v>sudo apt-get update</v>
-      </c>
-      <c r="E80" s="152" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F80" s="35" t="s">
-        <v>1190</v>
-      </c>
-      <c r="G80" s="35" t="s">
-        <v>1190</v>
-      </c>
-      <c r="H80" s="34"/>
-      <c r="I80" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="144"/>
-      <c r="B81" s="144"/>
-      <c r="C81" s="36" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D81" s="36" t="str">
-        <f t="shared" ref="D81:D88" si="8">C81</f>
-        <v>sudo apt-get install -y ca-certificates curl gnupg lsb-release</v>
-      </c>
-      <c r="E81" s="153" t="s">
+      <c r="A81" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D81" s="34" t="str">
+        <f>C81</f>
+        <v>sudo apt-get update</v>
+      </c>
+      <c r="E81" s="152" t="s">
         <v>1197</v>
       </c>
-      <c r="F81" s="37" t="s">
+      <c r="F81" s="35" t="s">
         <v>1190</v>
       </c>
-      <c r="G81" s="37" t="s">
+      <c r="G81" s="35" t="s">
         <v>1190</v>
       </c>
-      <c r="H81" s="36"/>
+      <c r="H81" s="34"/>
       <c r="I81" t="s">
         <v>1109</v>
       </c>
@@ -72896,11 +72905,11 @@
       <c r="A82" s="144"/>
       <c r="B82" s="144"/>
       <c r="C82" s="36" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D82" s="36" t="str">
-        <f t="shared" si="8"/>
-        <v>sudo mkdir -p /etc/apt/keyrings</v>
+        <f t="shared" ref="D82:D89" si="8">C82</f>
+        <v>sudo apt-get install -y ca-certificates curl gnupg lsb-release</v>
       </c>
       <c r="E82" s="153" t="s">
         <v>1197</v>
@@ -72920,11 +72929,11 @@
       <c r="A83" s="144"/>
       <c r="B83" s="144"/>
       <c r="C83" s="36" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D83" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>curl -fsSL https://download.docker.com/linux/ubuntu/gpg | sudo gpg --dearmor -o /etc/apt/keyrings/docker.gpg</v>
+        <v>sudo mkdir -p /etc/apt/keyrings</v>
       </c>
       <c r="E83" s="153" t="s">
         <v>1197</v>
@@ -72937,18 +72946,18 @@
       </c>
       <c r="H83" s="36"/>
       <c r="I83" t="s">
-        <v>28</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="144"/>
       <c r="B84" s="144"/>
       <c r="C84" s="36" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D84" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>echo "deb [arch=$(dpkg --print-architecture) signed-by=/etc/apt/keyrings/docker.gpg] https://download.docker.com/linux/ubuntu $(lsb_release -cs) stable" | sudo tee /etc/apt/sources.list.d/docker.list &gt; /dev/null</v>
+        <v>curl -fsSL https://download.docker.com/linux/ubuntu/gpg | sudo gpg --dearmor -o /etc/apt/keyrings/docker.gpg</v>
       </c>
       <c r="E84" s="153" t="s">
         <v>1197</v>
@@ -72968,11 +72977,11 @@
       <c r="A85" s="144"/>
       <c r="B85" s="144"/>
       <c r="C85" s="36" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D85" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>sudo apt-get update</v>
+        <v>echo "deb [arch=$(dpkg --print-architecture) signed-by=/etc/apt/keyrings/docker.gpg] https://download.docker.com/linux/ubuntu $(lsb_release -cs) stable" | sudo tee /etc/apt/sources.list.d/docker.list &gt; /dev/null</v>
       </c>
       <c r="E85" s="153" t="s">
         <v>1197</v>
@@ -72992,11 +73001,11 @@
       <c r="A86" s="144"/>
       <c r="B86" s="144"/>
       <c r="C86" s="36" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="D86" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>sudo apt-get install -y docker-ce docker-ce-cli containerd.io docker-compose-plugin</v>
+        <v>sudo apt-get update</v>
       </c>
       <c r="E86" s="153" t="s">
         <v>1197</v>
@@ -73016,11 +73025,11 @@
       <c r="A87" s="144"/>
       <c r="B87" s="144"/>
       <c r="C87" s="36" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D87" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>sudo groupadd docker</v>
+        <v>sudo apt-get install -y docker-ce docker-ce-cli containerd.io docker-compose-plugin</v>
       </c>
       <c r="E87" s="153" t="s">
         <v>1197</v>
@@ -73040,11 +73049,11 @@
       <c r="A88" s="144"/>
       <c r="B88" s="144"/>
       <c r="C88" s="36" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D88" s="36" t="str">
         <f t="shared" si="8"/>
-        <v>sudo usermod -aG docker $USER</v>
+        <v>sudo groupadd docker</v>
       </c>
       <c r="E88" s="153" t="s">
         <v>1197</v>
@@ -73062,100 +73071,97 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="144"/>
-      <c r="B89" s="145"/>
-      <c r="C89" s="38" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E89" s="154" t="s">
+      <c r="B89" s="144"/>
+      <c r="C89" s="36" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D89" s="36" t="str">
+        <f t="shared" si="8"/>
+        <v>sudo usermod -aG docker $USER</v>
+      </c>
+      <c r="E89" s="153" t="s">
         <v>1197</v>
       </c>
-      <c r="F89" s="39" t="s">
+      <c r="F89" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="G89" s="39" t="s">
+      <c r="G89" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="H89" s="38" t="s">
-        <v>1189</v>
-      </c>
+      <c r="H89" s="36"/>
       <c r="I89" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="144"/>
-      <c r="B90" s="144" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C90" s="144" t="s">
-        <v>1551</v>
-      </c>
-      <c r="D90" s="144" t="str">
-        <f>$C90</f>
-        <v>mkdir -p ~/.docker; echo -e "{\n    \"detachKeys\": \"ctrl-\\\\\\\\,ctrl-\\\\\\\\\"\n}" &gt; ~/.docker/config.json</v>
-      </c>
-      <c r="E90" s="160" t="s">
-        <v>1241</v>
+      <c r="B90" s="145"/>
+      <c r="C90" s="38" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D90" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E90" s="154" t="s">
+        <v>1197</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>149</v>
+        <v>1190</v>
       </c>
       <c r="G90" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="H90" s="144"/>
+        <v>1190</v>
+      </c>
+      <c r="H90" s="38" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I90" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="144"/>
-      <c r="B91" s="32" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C91" s="34" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D91" s="34" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E91" s="152" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F91" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G91" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H91" s="34"/>
-      <c r="I91" t="s">
-        <v>1109</v>
-      </c>
+      <c r="B91" s="144" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C91" s="144" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D91" s="144" t="str">
+        <f>$C91</f>
+        <v>mkdir -p ~/.docker; echo -e "{\n    \"detachKeys\": \"ctrl-\\\\\\\\,ctrl-\\\\\\\\\"\n}" &gt; ~/.docker/config.json</v>
+      </c>
+      <c r="E91" s="160" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F91" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="G91" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H91" s="144"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="41" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B92" s="41" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C92" s="45" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D92" s="45" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E92" s="173" t="s">
+      <c r="A92" s="144"/>
+      <c r="B92" s="32" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D92" s="34" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E92" s="152" t="s">
         <v>1197</v>
       </c>
-      <c r="F92" s="46" t="s">
+      <c r="F92" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G92" s="46" t="s">
+      <c r="G92" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="H92" s="45"/>
+      <c r="H92" s="34"/>
       <c r="I92" t="s">
         <v>1109</v>
       </c>
@@ -73168,13 +73174,13 @@
         <v>1100</v>
       </c>
       <c r="C93" s="45" t="s">
-        <v>1410</v>
+        <v>1104</v>
       </c>
       <c r="D93" s="45" t="s">
-        <v>1411</v>
+        <v>1105</v>
       </c>
       <c r="E93" s="173" t="s">
-        <v>39</v>
+        <v>1197</v>
       </c>
       <c r="F93" s="46" t="s">
         <v>0</v>
@@ -73184,84 +73190,86 @@
       </c>
       <c r="H93" s="45"/>
       <c r="I93" t="s">
-        <v>28</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="42" t="s">
+      <c r="A94" s="41" t="s">
         <v>1102</v>
       </c>
-      <c r="B94" s="26" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C94" s="26" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D94" s="26" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E94" s="155" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F94" s="15" t="s">
+      <c r="B94" s="41" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C94" s="45" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D94" s="45" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E94" s="173" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G94" s="15" t="s">
+      <c r="G94" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="H94" s="26" t="s">
-        <v>1164</v>
-      </c>
+      <c r="H94" s="45"/>
       <c r="I94" t="s">
-        <v>1109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="33" t="s">
-        <v>1552</v>
-      </c>
-      <c r="B95" s="32"/>
-      <c r="C95" s="34" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D95" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="E95" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="F95" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="G95" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="H95" s="34"/>
+      <c r="A95" s="42" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C95" s="26" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E95" s="155" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H95" s="26" t="s">
+        <v>1164</v>
+      </c>
       <c r="I95" t="s">
-        <v>28</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="B96" s="41"/>
-      <c r="C96" s="36" t="s">
-        <v>1554</v>
-      </c>
-      <c r="D96" s="36" t="s">
-        <v>1464</v>
-      </c>
-      <c r="E96" s="36" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F96" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G96" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H96" s="36"/>
+      <c r="A96" s="33" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B96" s="32"/>
+      <c r="C96" s="34" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D96" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="E96" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="F96" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="G96" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="H96" s="34"/>
       <c r="I96" t="s">
         <v>28</v>
       </c>
@@ -73272,15 +73280,13 @@
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="36" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D97" s="36" t="str">
-        <f t="shared" ref="D97:E99" si="9">C97</f>
-        <v>nvm install 24</v>
-      </c>
-      <c r="E97" s="36" t="str">
-        <f t="shared" si="9"/>
-        <v>nvm install 24</v>
+        <v>1554</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E97" s="36" t="s">
+        <v>1464</v>
       </c>
       <c r="F97" s="37" t="s">
         <v>0</v>
@@ -73299,15 +73305,15 @@
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="36" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D98" s="36" t="str">
-        <f t="shared" si="9"/>
-        <v>node -v</v>
+        <f t="shared" ref="D98:E100" si="9">C98</f>
+        <v>nvm install 24</v>
       </c>
       <c r="E98" s="36" t="str">
         <f t="shared" si="9"/>
-        <v>node -v</v>
+        <v>nvm install 24</v>
       </c>
       <c r="F98" s="37" t="s">
         <v>0</v>
@@ -73321,56 +73327,66 @@
       </c>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="42" t="s">
+      <c r="A99" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="B99" s="42"/>
-      <c r="C99" s="38" t="s">
+      <c r="B99" s="41"/>
+      <c r="C99" s="36" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D99" s="36" t="str">
+        <f t="shared" si="9"/>
+        <v>node -v</v>
+      </c>
+      <c r="E99" s="36" t="str">
+        <f t="shared" si="9"/>
+        <v>node -v</v>
+      </c>
+      <c r="F99" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G99" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H99" s="36"/>
+      <c r="I99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="B100" s="42"/>
+      <c r="C100" s="38" t="s">
         <v>1557</v>
       </c>
-      <c r="D99" s="38" t="str">
+      <c r="D100" s="38" t="str">
         <f t="shared" si="9"/>
         <v>npm -v</v>
       </c>
-      <c r="E99" s="38" t="str">
+      <c r="E100" s="38" t="str">
         <f t="shared" si="9"/>
         <v>npm -v</v>
       </c>
-      <c r="F99" s="39" t="s">
+      <c r="F100" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="G99" s="39" t="s">
+      <c r="G100" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="H99" s="38"/>
-      <c r="I99" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="26" t="s">
-        <v>1558</v>
-      </c>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D100" s="26"/>
-      <c r="E100" s="26"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="26"/>
+      <c r="H100" s="38"/>
       <c r="I100" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="26" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="26" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="26"/>
@@ -73382,9 +73398,13 @@
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="26"/>
+      <c r="A102" s="26" t="s">
+        <v>1560</v>
+      </c>
       <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="C102" s="26" t="s">
+        <v>1561</v>
+      </c>
       <c r="D102" s="26"/>
       <c r="E102" s="26"/>
       <c r="F102" s="15"/>
@@ -73443,7 +73463,7 @@
       <c r="G106" s="15"/>
       <c r="H106" s="26"/>
       <c r="I106" t="s">
-        <v>1109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -73563,18 +73583,31 @@
         <v>1109</v>
       </c>
     </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="26"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="26"/>
+      <c r="E116" s="26"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
+      <c r="H116" s="26"/>
+      <c r="I116" t="s">
+        <v>1109</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="A60" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="C58" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="C57" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D57" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="A61" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="C59" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="C58" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D58" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
     <hyperlink ref="A9" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
     <hyperlink ref="E19" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="E57" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="B80" r:id="rId8" display="Docker インストール" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="A95" r:id="rId9" xr:uid="{67E57ADF-7465-4531-8803-81062D8C9605}"/>
+    <hyperlink ref="E58" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="B81" r:id="rId8" display="Docker インストール" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="A96" r:id="rId9" xr:uid="{67E57ADF-7465-4531-8803-81062D8C9605}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="24" orientation="portrait" horizontalDpi="4294967293" r:id="rId10"/>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC3144F-1D64-419C-9523-6DA2AC96F5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D85E81-9CAE-40EC-909B-DB71E4614BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="36375" windowHeight="43185" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="42720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -797,7 +797,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6461" uniqueCount="1572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6478" uniqueCount="1576">
   <si>
     <t>○</t>
   </si>
@@ -8280,6 +8280,25 @@
   <si>
     <t>-</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Shutdown.vbs</t>
+  </si>
+  <si>
+    <t>時刻指定シャットダウン</t>
+    <rPh sb="0" eb="2">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:\codes\vbs\tools\win\other\Shutdown.vbs</t>
+  </si>
+  <si>
+    <t>sht</t>
   </si>
 </sst>
 </file>
@@ -8824,7 +8843,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8841,8 +8860,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9371,14 +9393,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="ハイパーリンク 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="標準 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="標準 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="標準 3 2" xfId="6" xr:uid="{434FB8F1-F054-492B-94AE-8C12B4AF6F3F}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -14077,7 +14118,7 @@
         <v>935</v>
       </c>
       <c r="R11" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R11:R74" si="0">IF(
   AND(
     $A11&lt;&gt;"",
     COUNTIF(C:C,$A11)&gt;1
@@ -14088,7 +14129,7 @@
         <v/>
       </c>
       <c r="S11" s="9" t="str">
-        <f t="shared" ref="S11:S42" si="0">IF(
+        <f t="shared" ref="S11:S42" si="1">IF(
   OR(
     $H11="",
     $H11="-",
@@ -14219,7 +14260,7 @@
         <v>113</v>
       </c>
       <c r="AC11" s="20" t="str">
-        <f t="shared" ref="AC11:AC42" si="1">IF(AND($M11&lt;&gt;"",$M11&lt;&gt;"-")," (&amp;"&amp;$M11&amp;")","")</f>
+        <f t="shared" ref="AC11:AC42" si="2">IF(AND($M11&lt;&gt;"",$M11&lt;&gt;"-")," (&amp;"&amp;$M11&amp;")","")</f>
         <v/>
       </c>
       <c r="AD11" s="13" t="str">
@@ -14253,7 +14294,7 @@
         <v/>
       </c>
       <c r="AG11" s="13" t="str">
-        <f t="shared" ref="AG11:AG42" si="2">IF(
+        <f t="shared" ref="AG11:AG42" si="3">IF(
   AND($A11&lt;&gt;"",$O11&lt;&gt;"-",$O11&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O11&amp;""" /tr """&amp;$C11&amp;""" /sc daily /st "&amp;$P11&amp;" /rl highest"
@@ -14263,7 +14304,7 @@
         <v/>
       </c>
       <c r="AH11" s="13" t="str">
-        <f t="shared" ref="AH11:AH42" si="3">IF(
+        <f t="shared" ref="AH11:AH42" si="4">IF(
   AND($A11&lt;&gt;"",$O11&lt;&gt;"-",$O11&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O11&amp;""""
@@ -14343,18 +14384,11 @@
         <v>935</v>
       </c>
       <c r="R12" s="9" t="str">
-        <f>IF(
-  AND(
-    $A12&lt;&gt;"",
-    COUNTIF(C:C,$A12)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S12" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T12" s="13" t="str">
@@ -14477,7 +14511,7 @@
         <v>122</v>
       </c>
       <c r="AC12" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD12" s="13" t="str">
@@ -14511,11 +14545,11 @@
         <v/>
       </c>
       <c r="AG12" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH12" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI12" s="13" t="str">
@@ -14589,18 +14623,11 @@
         <v>935</v>
       </c>
       <c r="R13" s="9" t="str">
-        <f>IF(
-  AND(
-    $A13&lt;&gt;"",
-    COUNTIF(C:C,$A13)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S13" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T13" s="13" t="str">
@@ -14723,7 +14750,7 @@
         <v>142</v>
       </c>
       <c r="AC13" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD13" s="13" t="str">
@@ -14757,11 +14784,11 @@
         <v/>
       </c>
       <c r="AG13" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH13" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI13" s="13" t="str">
@@ -14835,18 +14862,11 @@
         <v>935</v>
       </c>
       <c r="R14" s="9" t="str">
-        <f>IF(
-  AND(
-    $A14&lt;&gt;"",
-    COUNTIF(C:C,$A14)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S14" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T14" s="13" t="str">
@@ -14969,7 +14989,7 @@
         <v>142</v>
       </c>
       <c r="AC14" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD14" s="13" t="str">
@@ -15003,11 +15023,11 @@
         <v/>
       </c>
       <c r="AG14" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH14" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI14" s="13" t="str">
@@ -15081,18 +15101,11 @@
         <v>935</v>
       </c>
       <c r="R15" s="9" t="str">
-        <f>IF(
-  AND(
-    $A15&lt;&gt;"",
-    COUNTIF(C:C,$A15)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S15" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T15" s="13" t="str">
@@ -15215,7 +15228,7 @@
         <v>121</v>
       </c>
       <c r="AC15" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD15" s="13" t="str">
@@ -15249,11 +15262,11 @@
         <v/>
       </c>
       <c r="AG15" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH15" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI15" s="13" t="str">
@@ -15328,18 +15341,11 @@
         <v>935</v>
       </c>
       <c r="R16" s="9" t="str">
-        <f>IF(
-  AND(
-    $A16&lt;&gt;"",
-    COUNTIF(C:C,$A16)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T16" s="13" t="e">
@@ -15462,7 +15468,7 @@
         <v>121</v>
       </c>
       <c r="AC16" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD16" s="13" t="str">
@@ -15496,11 +15502,11 @@
         <v/>
       </c>
       <c r="AG16" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH16" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI16" s="13" t="str">
@@ -15574,18 +15580,11 @@
         <v>935</v>
       </c>
       <c r="R17" s="9" t="str">
-        <f>IF(
-  AND(
-    $A17&lt;&gt;"",
-    COUNTIF(C:C,$A17)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T17" s="13" t="str">
@@ -15708,7 +15707,7 @@
         <v>172</v>
       </c>
       <c r="AC17" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD17" s="13" t="str">
@@ -15742,11 +15741,11 @@
         <v/>
       </c>
       <c r="AG17" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH17" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI17" s="13" t="str">
@@ -15820,18 +15819,11 @@
         <v>935</v>
       </c>
       <c r="R18" s="9" t="str">
-        <f>IF(
-  AND(
-    $A18&lt;&gt;"",
-    COUNTIF(C:C,$A18)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T18" s="13" t="str">
@@ -15954,7 +15946,7 @@
         <v>161</v>
       </c>
       <c r="AC18" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD18" s="13" t="str">
@@ -15988,11 +15980,11 @@
         <v/>
       </c>
       <c r="AG18" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH18" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI18" s="13" t="str">
@@ -16066,18 +16058,11 @@
         <v>935</v>
       </c>
       <c r="R19" s="9" t="str">
-        <f>IF(
-  AND(
-    $A19&lt;&gt;"",
-    COUNTIF(C:C,$A19)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S19" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T19" s="13" t="str">
@@ -16200,7 +16185,7 @@
         <v>134</v>
       </c>
       <c r="AC19" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD19" s="13" t="str">
@@ -16234,11 +16219,11 @@
         <v/>
       </c>
       <c r="AG19" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH19" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI19" s="13" t="str">
@@ -16312,18 +16297,11 @@
         <v>935</v>
       </c>
       <c r="R20" s="9" t="str">
-        <f>IF(
-  AND(
-    $A20&lt;&gt;"",
-    COUNTIF(C:C,$A20)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T20" s="13" t="str">
@@ -16446,7 +16424,7 @@
         <v>172</v>
       </c>
       <c r="AC20" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD20" s="13" t="str">
@@ -16480,11 +16458,11 @@
         <v/>
       </c>
       <c r="AG20" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH20" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI20" s="13" t="str">
@@ -16558,18 +16536,11 @@
         <v>935</v>
       </c>
       <c r="R21" s="9" t="str">
-        <f>IF(
-  AND(
-    $A21&lt;&gt;"",
-    COUNTIF(C:C,$A21)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T21" s="13" t="str">
@@ -16692,7 +16663,7 @@
         <v>172</v>
       </c>
       <c r="AC21" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD21" s="13" t="str">
@@ -16726,11 +16697,11 @@
         <v/>
       </c>
       <c r="AG21" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH21" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI21" s="13" t="str">
@@ -16804,18 +16775,11 @@
         <v>935</v>
       </c>
       <c r="R22" s="9" t="str">
-        <f>IF(
-  AND(
-    $A22&lt;&gt;"",
-    COUNTIF(C:C,$A22)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T22" s="13" t="str">
@@ -16938,7 +16902,7 @@
         <v>171</v>
       </c>
       <c r="AC22" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD22" s="13" t="str">
@@ -16972,11 +16936,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\AutoMute（自動ミュート）.lnk</v>
       </c>
       <c r="AG22" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH22" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI22" s="13" t="str">
@@ -17050,18 +17014,11 @@
         <v>935</v>
       </c>
       <c r="R23" s="9" t="str">
-        <f>IF(
-  AND(
-    $A23&lt;&gt;"",
-    COUNTIF(C:C,$A23)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T23" s="13" t="str">
@@ -17184,7 +17141,7 @@
         <v>172</v>
       </c>
       <c r="AC23" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD23" s="13" t="str">
@@ -17218,11 +17175,11 @@
         <v/>
       </c>
       <c r="AG23" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH23" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI23" s="13" t="str">
@@ -17296,18 +17253,11 @@
         <v>935</v>
       </c>
       <c r="R24" s="9" t="str">
-        <f>IF(
-  AND(
-    $A24&lt;&gt;"",
-    COUNTIF(C:C,$A24)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T24" s="13" t="str">
@@ -17430,7 +17380,7 @@
         <v>113</v>
       </c>
       <c r="AC24" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD24" s="13" t="str">
@@ -17464,11 +17414,11 @@
         <v/>
       </c>
       <c r="AG24" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH24" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI24" s="13" t="str">
@@ -17542,18 +17492,11 @@
         <v>935</v>
       </c>
       <c r="R25" s="9" t="str">
-        <f>IF(
-  AND(
-    $A25&lt;&gt;"",
-    COUNTIF(C:C,$A25)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T25" s="13" t="str">
@@ -17676,7 +17619,7 @@
         <v>113</v>
       </c>
       <c r="AC25" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD25" s="13" t="str">
@@ -17710,11 +17653,11 @@
         <v/>
       </c>
       <c r="AG25" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH25" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI25" s="13" t="str">
@@ -17788,18 +17731,11 @@
         <v>935</v>
       </c>
       <c r="R26" s="9" t="str">
-        <f>IF(
-  AND(
-    $A26&lt;&gt;"",
-    COUNTIF(C:C,$A26)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T26" s="13" t="str">
@@ -17922,7 +17858,7 @@
         <v>113</v>
       </c>
       <c r="AC26" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD26" s="13" t="str">
@@ -17956,11 +17892,11 @@
         <v/>
       </c>
       <c r="AG26" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH26" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI26" s="13" t="str">
@@ -18034,18 +17970,11 @@
         <v>935</v>
       </c>
       <c r="R27" s="9" t="str">
-        <f>IF(
-  AND(
-    $A27&lt;&gt;"",
-    COUNTIF(C:C,$A27)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S27" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T27" s="13" t="str">
@@ -18168,7 +18097,7 @@
         <v>113</v>
       </c>
       <c r="AC27" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD27" s="13" t="str">
@@ -18202,11 +18131,11 @@
         <v/>
       </c>
       <c r="AG27" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH27" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI27" s="13" t="str">
@@ -18280,18 +18209,11 @@
         <v>935</v>
       </c>
       <c r="R28" s="9" t="str">
-        <f>IF(
-  AND(
-    $A28&lt;&gt;"",
-    COUNTIF(C:C,$A28)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T28" s="13" t="str">
@@ -18414,7 +18336,7 @@
         <v>113</v>
       </c>
       <c r="AC28" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD28" s="13" t="str">
@@ -18448,11 +18370,11 @@
         <v/>
       </c>
       <c r="AG28" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH28" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI28" s="13" t="str">
@@ -18526,18 +18448,11 @@
         <v>935</v>
       </c>
       <c r="R29" s="9" t="str">
-        <f>IF(
-  AND(
-    $A29&lt;&gt;"",
-    COUNTIF(C:C,$A29)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T29" s="13" t="str">
@@ -18660,7 +18575,7 @@
         <v>112</v>
       </c>
       <c r="AC29" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD29" s="13" t="str">
@@ -18694,11 +18609,11 @@
         <v/>
       </c>
       <c r="AG29" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH29" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI29" s="13" t="str">
@@ -18772,18 +18687,11 @@
         <v>935</v>
       </c>
       <c r="R30" s="9" t="str">
-        <f>IF(
-  AND(
-    $A30&lt;&gt;"",
-    COUNTIF(C:C,$A30)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T30" s="13" t="str">
@@ -18906,7 +18814,7 @@
         <v>112</v>
       </c>
       <c r="AC30" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD30" s="13" t="str">
@@ -18940,11 +18848,11 @@
         <v/>
       </c>
       <c r="AG30" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH30" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI30" s="13" t="str">
@@ -19018,18 +18926,11 @@
         <v>935</v>
       </c>
       <c r="R31" s="9" t="str">
-        <f>IF(
-  AND(
-    $A31&lt;&gt;"",
-    COUNTIF(C:C,$A31)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T31" s="13" t="str">
@@ -19152,7 +19053,7 @@
         <v>112</v>
       </c>
       <c r="AC31" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD31" s="13" t="str">
@@ -19186,11 +19087,11 @@
         <v/>
       </c>
       <c r="AG31" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH31" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI31" s="13" t="str">
@@ -19264,18 +19165,11 @@
         <v>935</v>
       </c>
       <c r="R32" s="9" t="str">
-        <f>IF(
-  AND(
-    $A32&lt;&gt;"",
-    COUNTIF(C:C,$A32)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T32" s="13" t="str">
@@ -19398,7 +19292,7 @@
         <v>121</v>
       </c>
       <c r="AC32" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD32" s="13" t="str">
@@ -19432,11 +19326,11 @@
         <v/>
       </c>
       <c r="AG32" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH32" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI32" s="13" t="str">
@@ -19510,18 +19404,11 @@
         <v>935</v>
       </c>
       <c r="R33" s="9" t="str">
-        <f>IF(
-  AND(
-    $A33&lt;&gt;"",
-    COUNTIF(C:C,$A33)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T33" s="13" t="str">
@@ -19644,7 +19531,7 @@
         <v>172</v>
       </c>
       <c r="AC33" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD33" s="13" t="str">
@@ -19678,11 +19565,11 @@
         <v/>
       </c>
       <c r="AG33" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH33" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI33" s="13" t="str">
@@ -19756,18 +19643,11 @@
         <v>935</v>
       </c>
       <c r="R34" s="9" t="str">
-        <f>IF(
-  AND(
-    $A34&lt;&gt;"",
-    COUNTIF(C:C,$A34)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S34" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T34" s="13" t="str">
@@ -19890,7 +19770,7 @@
         <v>171</v>
       </c>
       <c r="AC34" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD34" s="13" t="str">
@@ -19924,11 +19804,11 @@
         <v/>
       </c>
       <c r="AG34" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH34" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI34" s="13" t="str">
@@ -20002,18 +19882,11 @@
         <v>935</v>
       </c>
       <c r="R35" s="9" t="str">
-        <f>IF(
-  AND(
-    $A35&lt;&gt;"",
-    COUNTIF(C:C,$A35)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S35" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T35" s="13" t="str">
@@ -20136,7 +20009,7 @@
         <v>171</v>
       </c>
       <c r="AC35" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD35" s="13" t="str">
@@ -20170,11 +20043,11 @@
         <v/>
       </c>
       <c r="AG35" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH35" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI35" s="13" t="str">
@@ -20248,18 +20121,11 @@
         <v>935</v>
       </c>
       <c r="R36" s="9" t="str">
-        <f>IF(
-  AND(
-    $A36&lt;&gt;"",
-    COUNTIF(C:C,$A36)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S36" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T36" s="13" t="str">
@@ -20382,7 +20248,7 @@
         <v>111</v>
       </c>
       <c r="AC36" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD36" s="13" t="str">
@@ -20416,11 +20282,11 @@
         <v/>
       </c>
       <c r="AG36" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH36" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI36" s="13" t="str">
@@ -20494,18 +20360,11 @@
         <v>935</v>
       </c>
       <c r="R37" s="9" t="str">
-        <f>IF(
-  AND(
-    $A37&lt;&gt;"",
-    COUNTIF(C:C,$A37)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S37" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T37" s="13" t="str">
@@ -20628,7 +20487,7 @@
         <v>172</v>
       </c>
       <c r="AC37" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD37" s="13" t="str">
@@ -20662,11 +20521,11 @@
         <v/>
       </c>
       <c r="AG37" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH37" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI37" s="13" t="str">
@@ -20740,18 +20599,11 @@
         <v>935</v>
       </c>
       <c r="R38" s="9" t="str">
-        <f>IF(
-  AND(
-    $A38&lt;&gt;"",
-    COUNTIF(C:C,$A38)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S38" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T38" s="13" t="str">
@@ -20874,7 +20726,7 @@
         <v>134</v>
       </c>
       <c r="AC38" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD38" s="13" t="str">
@@ -20908,11 +20760,11 @@
         <v/>
       </c>
       <c r="AG38" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH38" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI38" s="13" t="str">
@@ -20986,18 +20838,11 @@
         <v>935</v>
       </c>
       <c r="R39" s="9" t="str">
-        <f>IF(
-  AND(
-    $A39&lt;&gt;"",
-    COUNTIF(C:C,$A39)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S39" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T39" s="13" t="str">
@@ -21120,7 +20965,7 @@
         <v>121</v>
       </c>
       <c r="AC39" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD39" s="13" t="str">
@@ -21154,11 +20999,11 @@
         <v/>
       </c>
       <c r="AG39" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH39" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI39" s="13" t="str">
@@ -21232,18 +21077,11 @@
         <v>935</v>
       </c>
       <c r="R40" s="9" t="str">
-        <f>IF(
-  AND(
-    $A40&lt;&gt;"",
-    COUNTIF(C:C,$A40)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S40" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T40" s="13" t="str">
@@ -21366,7 +21204,7 @@
         <v>121</v>
       </c>
       <c r="AC40" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD40" s="13" t="str">
@@ -21400,11 +21238,11 @@
         <v/>
       </c>
       <c r="AG40" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH40" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI40" s="13" t="str">
@@ -21478,18 +21316,11 @@
         <v>935</v>
       </c>
       <c r="R41" s="9" t="str">
-        <f>IF(
-  AND(
-    $A41&lt;&gt;"",
-    COUNTIF(C:C,$A41)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S41" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T41" s="13" t="str">
@@ -21612,7 +21443,7 @@
         <v>112</v>
       </c>
       <c r="AC41" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD41" s="13" t="str">
@@ -21646,11 +21477,11 @@
         <v/>
       </c>
       <c r="AG41" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH41" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI41" s="13" t="str">
@@ -21724,18 +21555,11 @@
         <v>935</v>
       </c>
       <c r="R42" s="9" t="str">
-        <f>IF(
-  AND(
-    $A42&lt;&gt;"",
-    COUNTIF(C:C,$A42)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S42" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="T42" s="13" t="str">
@@ -21858,7 +21682,7 @@
         <v>111</v>
       </c>
       <c r="AC42" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AD42" s="13" t="str">
@@ -21892,11 +21716,11 @@
         <v/>
       </c>
       <c r="AG42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AH42" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AI42" s="13" t="str">
@@ -21970,18 +21794,11 @@
         <v>935</v>
       </c>
       <c r="R43" s="9" t="str">
-        <f>IF(
-  AND(
-    $A43&lt;&gt;"",
-    COUNTIF(C:C,$A43)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S43" s="9" t="str">
-        <f t="shared" ref="S43:S73" si="4">IF(
+        <f t="shared" ref="S43:S73" si="5">IF(
   OR(
     $H43="",
     $H43="-",
@@ -22112,7 +21929,7 @@
         <v>121</v>
       </c>
       <c r="AC43" s="20" t="str">
-        <f t="shared" ref="AC43:AC73" si="5">IF(AND($M43&lt;&gt;"",$M43&lt;&gt;"-")," (&amp;"&amp;$M43&amp;")","")</f>
+        <f t="shared" ref="AC43:AC73" si="6">IF(AND($M43&lt;&gt;"",$M43&lt;&gt;"-")," (&amp;"&amp;$M43&amp;")","")</f>
         <v/>
       </c>
       <c r="AD43" s="13" t="str">
@@ -22146,7 +21963,7 @@
         <v/>
       </c>
       <c r="AG43" s="13" t="str">
-        <f t="shared" ref="AG43:AG73" si="6">IF(
+        <f t="shared" ref="AG43:AG73" si="7">IF(
   AND($A43&lt;&gt;"",$O43&lt;&gt;"-",$O43&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O43&amp;""" /tr """&amp;$C43&amp;""" /sc daily /st "&amp;$P43&amp;" /rl highest"
@@ -22156,7 +21973,7 @@
         <v/>
       </c>
       <c r="AH43" s="13" t="str">
-        <f t="shared" ref="AH43:AH73" si="7">IF(
+        <f t="shared" ref="AH43:AH73" si="8">IF(
   AND($A43&lt;&gt;"",$O43&lt;&gt;"-",$O43&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O43&amp;""""
@@ -22236,18 +22053,11 @@
         <v>935</v>
       </c>
       <c r="R44" s="9" t="str">
-        <f>IF(
-  AND(
-    $A44&lt;&gt;"",
-    COUNTIF(C:C,$A44)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S44" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T44" s="13" t="str">
@@ -22370,7 +22180,7 @@
         <v>113</v>
       </c>
       <c r="AC44" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD44" s="13" t="str">
@@ -22404,11 +22214,11 @@
         <v/>
       </c>
       <c r="AG44" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH44" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI44" s="13" t="str">
@@ -22482,18 +22292,11 @@
         <v>935</v>
       </c>
       <c r="R45" s="9" t="str">
-        <f>IF(
-  AND(
-    $A45&lt;&gt;"",
-    COUNTIF(C:C,$A45)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S45" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T45" s="13" t="str">
@@ -22616,7 +22419,7 @@
         <v>161</v>
       </c>
       <c r="AC45" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD45" s="13" t="str">
@@ -22650,11 +22453,11 @@
         <v/>
       </c>
       <c r="AG45" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH45" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI45" s="13" t="str">
@@ -22728,18 +22531,11 @@
         <v>935</v>
       </c>
       <c r="R46" s="9" t="str">
-        <f>IF(
-  AND(
-    $A46&lt;&gt;"",
-    COUNTIF(C:C,$A46)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S46" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T46" s="13" t="str">
@@ -22862,7 +22658,7 @@
         <v>121</v>
       </c>
       <c r="AC46" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD46" s="13" t="str">
@@ -22896,11 +22692,11 @@
         <v/>
       </c>
       <c r="AG46" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH46" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI46" s="13" t="str">
@@ -22974,18 +22770,11 @@
         <v>935</v>
       </c>
       <c r="R47" s="9" t="str">
-        <f>IF(
-  AND(
-    $A47&lt;&gt;"",
-    COUNTIF(C:C,$A47)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S47" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T47" s="13" t="str">
@@ -23108,7 +22897,7 @@
         <v>123</v>
       </c>
       <c r="AC47" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD47" s="13" t="str">
@@ -23142,11 +22931,11 @@
         <v/>
       </c>
       <c r="AG47" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH47" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI47" s="13" t="str">
@@ -23220,18 +23009,11 @@
         <v>935</v>
       </c>
       <c r="R48" s="9" t="str">
-        <f>IF(
-  AND(
-    $A48&lt;&gt;"",
-    COUNTIF(C:C,$A48)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S48" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T48" s="13" t="str">
@@ -23354,7 +23136,7 @@
         <v>133</v>
       </c>
       <c r="AC48" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD48" s="13" t="str">
@@ -23388,11 +23170,11 @@
         <v/>
       </c>
       <c r="AG48" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH48" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI48" s="13" t="str">
@@ -23466,18 +23248,11 @@
         <v>935</v>
       </c>
       <c r="R49" s="9" t="str">
-        <f>IF(
-  AND(
-    $A49&lt;&gt;"",
-    COUNTIF(C:C,$A49)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S49" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T49" s="13" t="str">
@@ -23600,7 +23375,7 @@
         <v>123</v>
       </c>
       <c r="AC49" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD49" s="13" t="str">
@@ -23634,11 +23409,11 @@
         <v/>
       </c>
       <c r="AG49" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH49" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI49" s="13" t="str">
@@ -23712,18 +23487,11 @@
         <v>935</v>
       </c>
       <c r="R50" s="9" t="str">
-        <f>IF(
-  AND(
-    $A50&lt;&gt;"",
-    COUNTIF(C:C,$A50)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S50" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T50" s="13" t="str">
@@ -23846,7 +23614,7 @@
         <v>153</v>
       </c>
       <c r="AC50" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD50" s="13" t="str">
@@ -23880,11 +23648,11 @@
         <v/>
       </c>
       <c r="AG50" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH50" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI50" s="13" t="str">
@@ -23958,18 +23726,11 @@
         <v>935</v>
       </c>
       <c r="R51" s="9" t="str">
-        <f>IF(
-  AND(
-    $A51&lt;&gt;"",
-    COUNTIF(C:C,$A51)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S51" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T51" s="13" t="str">
@@ -24092,7 +23853,7 @@
         <v>122</v>
       </c>
       <c r="AC51" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD51" s="13" t="str">
@@ -24126,11 +23887,11 @@
         <v/>
       </c>
       <c r="AG51" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH51" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI51" s="13" t="str">
@@ -24204,18 +23965,11 @@
         <v>935</v>
       </c>
       <c r="R52" s="9" t="str">
-        <f>IF(
-  AND(
-    $A52&lt;&gt;"",
-    COUNTIF(C:C,$A52)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S52" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T52" s="13" t="str">
@@ -24338,7 +24092,7 @@
         <v>161</v>
       </c>
       <c r="AC52" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD52" s="13" t="str">
@@ -24372,11 +24126,11 @@
         <v/>
       </c>
       <c r="AG52" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH52" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI52" s="13" t="str">
@@ -24450,18 +24204,11 @@
         <v>935</v>
       </c>
       <c r="R53" s="9" t="str">
-        <f>IF(
-  AND(
-    $A53&lt;&gt;"",
-    COUNTIF(C:C,$A53)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S53" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T53" s="13" t="str">
@@ -24584,7 +24331,7 @@
         <v>121</v>
       </c>
       <c r="AC53" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD53" s="13" t="str">
@@ -24618,11 +24365,11 @@
         <v/>
       </c>
       <c r="AG53" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH53" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI53" s="13" t="str">
@@ -24696,18 +24443,11 @@
         <v>935</v>
       </c>
       <c r="R54" s="9" t="str">
-        <f>IF(
-  AND(
-    $A54&lt;&gt;"",
-    COUNTIF(C:C,$A54)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S54" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T54" s="13" t="str">
@@ -24830,7 +24570,7 @@
         <v>123</v>
       </c>
       <c r="AC54" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD54" s="13" t="str">
@@ -24864,11 +24604,11 @@
         <v/>
       </c>
       <c r="AG54" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH54" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI54" s="13" t="str">
@@ -24942,18 +24682,11 @@
         <v>935</v>
       </c>
       <c r="R55" s="9" t="str">
-        <f>IF(
-  AND(
-    $A55&lt;&gt;"",
-    COUNTIF(C:C,$A55)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S55" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T55" s="13" t="str">
@@ -25076,7 +24809,7 @@
         <v>121</v>
       </c>
       <c r="AC55" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD55" s="13" t="str">
@@ -25110,11 +24843,11 @@
         <v/>
       </c>
       <c r="AG55" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI55" s="13" t="str">
@@ -25188,18 +24921,11 @@
         <v>935</v>
       </c>
       <c r="R56" s="9" t="str">
-        <f>IF(
-  AND(
-    $A56&lt;&gt;"",
-    COUNTIF(C:C,$A56)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S56" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T56" s="13" t="str">
@@ -25322,7 +25048,7 @@
         <v>171</v>
       </c>
       <c r="AC56" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD56" s="13" t="str">
@@ -25356,11 +25082,11 @@
         <v/>
       </c>
       <c r="AG56" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI56" s="13" t="str">
@@ -25434,18 +25160,11 @@
         <v>935</v>
       </c>
       <c r="R57" s="9" t="str">
-        <f>IF(
-  AND(
-    $A57&lt;&gt;"",
-    COUNTIF(C:C,$A57)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S57" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T57" s="13" t="str">
@@ -25568,7 +25287,7 @@
         <v>171</v>
       </c>
       <c r="AC57" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD57" s="13" t="str">
@@ -25602,11 +25321,11 @@
         <v/>
       </c>
       <c r="AG57" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI57" s="13" t="str">
@@ -25680,18 +25399,11 @@
         <v>935</v>
       </c>
       <c r="R58" s="9" t="str">
-        <f>IF(
-  AND(
-    $A58&lt;&gt;"",
-    COUNTIF(C:C,$A58)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S58" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T58" s="13" t="str">
@@ -25814,7 +25526,7 @@
         <v>171</v>
       </c>
       <c r="AC58" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD58" s="13" t="str">
@@ -25848,11 +25560,11 @@
         <v/>
       </c>
       <c r="AG58" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI58" s="13" t="str">
@@ -25926,18 +25638,11 @@
         <v>935</v>
       </c>
       <c r="R59" s="9" t="str">
-        <f>IF(
-  AND(
-    $A59&lt;&gt;"",
-    COUNTIF(C:C,$A59)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S59" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T59" s="13" t="str">
@@ -26060,7 +25765,7 @@
         <v>113</v>
       </c>
       <c r="AC59" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD59" s="13" t="str">
@@ -26094,11 +25799,11 @@
         <v/>
       </c>
       <c r="AG59" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI59" s="13" t="str">
@@ -26172,18 +25877,11 @@
         <v>935</v>
       </c>
       <c r="R60" s="9" t="str">
-        <f>IF(
-  AND(
-    $A60&lt;&gt;"",
-    COUNTIF(C:C,$A60)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S60" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T60" s="13" t="str">
@@ -26306,7 +26004,7 @@
         <v>153</v>
       </c>
       <c r="AC60" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD60" s="13" t="str">
@@ -26340,11 +26038,11 @@
         <v/>
       </c>
       <c r="AG60" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI60" s="13" t="str">
@@ -26418,18 +26116,11 @@
         <v>935</v>
       </c>
       <c r="R61" s="9" t="str">
-        <f>IF(
-  AND(
-    $A61&lt;&gt;"",
-    COUNTIF(C:C,$A61)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S61" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T61" s="13" t="str">
@@ -26552,7 +26243,7 @@
         <v>123</v>
       </c>
       <c r="AC61" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD61" s="13" t="str">
@@ -26586,11 +26277,11 @@
         <v/>
       </c>
       <c r="AG61" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI61" s="13" t="str">
@@ -26664,18 +26355,11 @@
         <v>935</v>
       </c>
       <c r="R62" s="9" t="str">
-        <f>IF(
-  AND(
-    $A62&lt;&gt;"",
-    COUNTIF(C:C,$A62)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S62" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T62" s="13" t="str">
@@ -26798,7 +26482,7 @@
         <v>153</v>
       </c>
       <c r="AC62" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD62" s="13" t="str">
@@ -26832,11 +26516,11 @@
         <v/>
       </c>
       <c r="AG62" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI62" s="13" t="str">
@@ -26910,18 +26594,11 @@
         <v>935</v>
       </c>
       <c r="R63" s="9" t="str">
-        <f>IF(
-  AND(
-    $A63&lt;&gt;"",
-    COUNTIF(C:C,$A63)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S63" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T63" s="13" t="str">
@@ -27044,7 +26721,7 @@
         <v>121</v>
       </c>
       <c r="AC63" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD63" s="13" t="str">
@@ -27078,11 +26755,11 @@
         <v/>
       </c>
       <c r="AG63" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH63" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI63" s="13" t="str">
@@ -27156,18 +26833,11 @@
         <v>935</v>
       </c>
       <c r="R64" s="9" t="str">
-        <f>IF(
-  AND(
-    $A64&lt;&gt;"",
-    COUNTIF(C:C,$A64)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S64" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T64" s="13" t="str">
@@ -27290,7 +26960,7 @@
         <v>172</v>
       </c>
       <c r="AC64" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD64" s="13" t="str">
@@ -27324,11 +26994,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\KeePass（パスワード管理）.lnk</v>
       </c>
       <c r="AG64" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH64" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI64" s="13" t="str">
@@ -27402,18 +27072,11 @@
         <v>935</v>
       </c>
       <c r="R65" s="9" t="str">
-        <f>IF(
-  AND(
-    $A65&lt;&gt;"",
-    COUNTIF(C:C,$A65)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S65" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T65" s="13" t="str">
@@ -27536,7 +27199,7 @@
         <v>113</v>
       </c>
       <c r="AC65" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD65" s="13" t="str">
@@ -27570,11 +27233,11 @@
         <v/>
       </c>
       <c r="AG65" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH65" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI65" s="13" t="str">
@@ -27648,18 +27311,11 @@
         <v>935</v>
       </c>
       <c r="R66" s="9" t="str">
-        <f>IF(
-  AND(
-    $A66&lt;&gt;"",
-    COUNTIF(C:C,$A66)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S66" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T66" s="13" t="str">
@@ -27782,7 +27438,7 @@
         <v>172</v>
       </c>
       <c r="AC66" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD66" s="13" t="str">
@@ -27816,11 +27472,11 @@
         <v/>
       </c>
       <c r="AG66" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH66" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI66" s="13" t="str">
@@ -27894,18 +27550,11 @@
         <v>935</v>
       </c>
       <c r="R67" s="9" t="str">
-        <f>IF(
-  AND(
-    $A67&lt;&gt;"",
-    COUNTIF(C:C,$A67)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S67" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T67" s="13" t="str">
@@ -28028,7 +27677,7 @@
         <v>143</v>
       </c>
       <c r="AC67" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD67" s="13" t="str">
@@ -28062,11 +27711,11 @@
         <v/>
       </c>
       <c r="AG67" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH67" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI67" s="13" t="str">
@@ -28140,18 +27789,11 @@
         <v>935</v>
       </c>
       <c r="R68" s="9" t="str">
-        <f>IF(
-  AND(
-    $A68&lt;&gt;"",
-    COUNTIF(C:C,$A68)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S68" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T68" s="13" t="str">
@@ -28274,7 +27916,7 @@
         <v>113</v>
       </c>
       <c r="AC68" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD68" s="13" t="str">
@@ -28308,11 +27950,11 @@
         <v/>
       </c>
       <c r="AG68" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH68" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI68" s="13" t="str">
@@ -28386,18 +28028,11 @@
         <v>935</v>
       </c>
       <c r="R69" s="9" t="str">
-        <f>IF(
-  AND(
-    $A69&lt;&gt;"",
-    COUNTIF(C:C,$A69)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S69" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T69" s="13" t="str">
@@ -28520,7 +28155,7 @@
         <v>154</v>
       </c>
       <c r="AC69" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD69" s="13" t="str">
@@ -28554,11 +28189,11 @@
         <v/>
       </c>
       <c r="AG69" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH69" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI69" s="13" t="str">
@@ -28632,18 +28267,11 @@
         <v>935</v>
       </c>
       <c r="R70" s="9" t="str">
-        <f>IF(
-  AND(
-    $A70&lt;&gt;"",
-    COUNTIF(C:C,$A70)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S70" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T70" s="13" t="str">
@@ -28766,7 +28394,7 @@
         <v>121</v>
       </c>
       <c r="AC70" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD70" s="13" t="str">
@@ -28800,11 +28428,11 @@
         <v/>
       </c>
       <c r="AG70" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH70" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI70" s="13" t="str">
@@ -28878,14 +28506,7 @@
         <v>39</v>
       </c>
       <c r="R71" s="9" t="str">
-        <f>IF(
-  AND(
-    $A71&lt;&gt;"",
-    COUNTIF(C:C,$A71)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S71" s="9" t="str">
@@ -29144,18 +28765,11 @@
         <v>935</v>
       </c>
       <c r="R72" s="9" t="str">
-        <f>IF(
-  AND(
-    $A72&lt;&gt;"",
-    COUNTIF(C:C,$A72)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S72" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T72" s="13" t="str">
@@ -29278,7 +28892,7 @@
         <v>134</v>
       </c>
       <c r="AC72" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD72" s="13" t="str">
@@ -29312,11 +28926,11 @@
         <v/>
       </c>
       <c r="AG72" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH72" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI72" s="13" t="str">
@@ -29390,18 +29004,11 @@
         <v>935</v>
       </c>
       <c r="R73" s="9" t="str">
-        <f>IF(
-  AND(
-    $A73&lt;&gt;"",
-    COUNTIF(C:C,$A73)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S73" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T73" s="13" t="str">
@@ -29524,7 +29131,7 @@
         <v>144</v>
       </c>
       <c r="AC73" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AD73" s="13" t="str">
@@ -29558,11 +29165,11 @@
         <v/>
       </c>
       <c r="AG73" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AH73" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AI73" s="13" t="str">
@@ -29636,18 +29243,11 @@
         <v>935</v>
       </c>
       <c r="R74" s="9" t="str">
-        <f>IF(
-  AND(
-    $A74&lt;&gt;"",
-    COUNTIF(C:C,$A74)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S74" s="9" t="str">
-        <f t="shared" ref="S74:S105" si="8">IF(
+        <f t="shared" ref="S74:S105" si="9">IF(
   OR(
     $H74="",
     $H74="-",
@@ -29778,7 +29378,7 @@
         <v>154</v>
       </c>
       <c r="AC74" s="20" t="str">
-        <f t="shared" ref="AC74:AC105" si="9">IF(AND($M74&lt;&gt;"",$M74&lt;&gt;"-")," (&amp;"&amp;$M74&amp;")","")</f>
+        <f t="shared" ref="AC74:AC105" si="10">IF(AND($M74&lt;&gt;"",$M74&lt;&gt;"-")," (&amp;"&amp;$M74&amp;")","")</f>
         <v/>
       </c>
       <c r="AD74" s="13" t="str">
@@ -29812,7 +29412,7 @@
         <v/>
       </c>
       <c r="AG74" s="13" t="str">
-        <f t="shared" ref="AG74:AG105" si="10">IF(
+        <f t="shared" ref="AG74:AG105" si="11">IF(
   AND($A74&lt;&gt;"",$O74&lt;&gt;"-",$O74&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O74&amp;""" /tr """&amp;$C74&amp;""" /sc daily /st "&amp;$P74&amp;" /rl highest"
@@ -29822,7 +29422,7 @@
         <v/>
       </c>
       <c r="AH74" s="13" t="str">
-        <f t="shared" ref="AH74:AH105" si="11">IF(
+        <f t="shared" ref="AH74:AH105" si="12">IF(
   AND($A74&lt;&gt;"",$O74&lt;&gt;"-",$O74&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O74&amp;""""
@@ -29902,7 +29502,7 @@
         <v>935</v>
       </c>
       <c r="R75" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R75:R138" si="13">IF(
   AND(
     $A75&lt;&gt;"",
     COUNTIF(C:C,$A75)&gt;1
@@ -29913,7 +29513,7 @@
         <v/>
       </c>
       <c r="S75" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T75" s="13" t="str">
@@ -30036,7 +29636,7 @@
         <v>162</v>
       </c>
       <c r="AC75" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD75" s="13" t="str">
@@ -30070,11 +29670,11 @@
         <v/>
       </c>
       <c r="AG75" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH75" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI75" s="13" t="str">
@@ -30148,18 +29748,11 @@
         <v>935</v>
       </c>
       <c r="R76" s="9" t="str">
-        <f>IF(
-  AND(
-    $A76&lt;&gt;"",
-    COUNTIF(C:C,$A76)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S76" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T76" s="13" t="str">
@@ -30282,7 +29875,7 @@
         <v>111</v>
       </c>
       <c r="AC76" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD76" s="13" t="str">
@@ -30316,11 +29909,11 @@
         <v/>
       </c>
       <c r="AG76" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH76" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI76" s="13" t="str">
@@ -30394,18 +29987,11 @@
         <v>935</v>
       </c>
       <c r="R77" s="9" t="str">
-        <f>IF(
-  AND(
-    $A77&lt;&gt;"",
-    COUNTIF(C:C,$A77)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S77" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T77" s="13" t="str">
@@ -30528,7 +30114,7 @@
         <v>172</v>
       </c>
       <c r="AC77" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD77" s="13" t="str">
@@ -30562,11 +30148,11 @@
         <v/>
       </c>
       <c r="AG77" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH77" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI77" s="13" t="str">
@@ -30640,18 +30226,11 @@
         <v>935</v>
       </c>
       <c r="R78" s="9" t="str">
-        <f>IF(
-  AND(
-    $A78&lt;&gt;"",
-    COUNTIF(C:C,$A78)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S78" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T78" s="13" t="str">
@@ -30774,7 +30353,7 @@
         <v>162</v>
       </c>
       <c r="AC78" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD78" s="13" t="str">
@@ -30808,11 +30387,11 @@
         <v/>
       </c>
       <c r="AG78" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH78" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI78" s="13" t="str">
@@ -30886,18 +30465,11 @@
         <v>935</v>
       </c>
       <c r="R79" s="9" t="str">
-        <f>IF(
-  AND(
-    $A79&lt;&gt;"",
-    COUNTIF(C:C,$A79)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S79" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T79" s="13" t="str">
@@ -31020,7 +30592,7 @@
         <v>122</v>
       </c>
       <c r="AC79" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD79" s="13" t="str">
@@ -31054,11 +30626,11 @@
         <v/>
       </c>
       <c r="AG79" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH79" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI79" s="13" t="str">
@@ -31132,18 +30704,11 @@
         <v>935</v>
       </c>
       <c r="R80" s="9" t="str">
-        <f>IF(
-  AND(
-    $A80&lt;&gt;"",
-    COUNTIF(C:C,$A80)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S80" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T80" s="13" t="str">
@@ -31266,7 +30831,7 @@
         <v>122</v>
       </c>
       <c r="AC80" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD80" s="13" t="str">
@@ -31300,11 +30865,11 @@
         <v/>
       </c>
       <c r="AG80" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH80" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI80" s="13" t="str">
@@ -31378,18 +30943,11 @@
         <v>935</v>
       </c>
       <c r="R81" s="9" t="str">
-        <f>IF(
-  AND(
-    $A81&lt;&gt;"",
-    COUNTIF(C:C,$A81)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S81" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T81" s="13" t="str">
@@ -31512,7 +31070,7 @@
         <v>122</v>
       </c>
       <c r="AC81" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD81" s="13" t="str">
@@ -31546,11 +31104,11 @@
         <v/>
       </c>
       <c r="AG81" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH81" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI81" s="13" t="str">
@@ -31624,18 +31182,11 @@
         <v>935</v>
       </c>
       <c r="R82" s="9" t="str">
-        <f>IF(
-  AND(
-    $A82&lt;&gt;"",
-    COUNTIF(C:C,$A82)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S82" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T82" s="13" t="str">
@@ -31758,7 +31309,7 @@
         <v>123</v>
       </c>
       <c r="AC82" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD82" s="13" t="str">
@@ -31792,11 +31343,11 @@
         <v/>
       </c>
       <c r="AG82" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH82" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI82" s="13" t="str">
@@ -31870,18 +31421,11 @@
         <v>935</v>
       </c>
       <c r="R83" s="9" t="str">
-        <f>IF(
-  AND(
-    $A83&lt;&gt;"",
-    COUNTIF(C:C,$A83)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S83" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T83" s="13" t="str">
@@ -32004,7 +31548,7 @@
         <v>113</v>
       </c>
       <c r="AC83" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD83" s="13" t="str">
@@ -32038,11 +31582,11 @@
         <v/>
       </c>
       <c r="AG83" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH83" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI83" s="13" t="str">
@@ -32116,18 +31660,11 @@
         <v>935</v>
       </c>
       <c r="R84" s="9" t="str">
-        <f>IF(
-  AND(
-    $A84&lt;&gt;"",
-    COUNTIF(C:C,$A84)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S84" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T84" s="13" t="str">
@@ -32250,7 +31787,7 @@
         <v>172</v>
       </c>
       <c r="AC84" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD84" s="13" t="str">
@@ -32284,11 +31821,11 @@
         <v/>
       </c>
       <c r="AG84" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH84" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI84" s="13" t="str">
@@ -32363,18 +31900,11 @@
         <v>935</v>
       </c>
       <c r="R85" s="9" t="str">
-        <f>IF(
-  AND(
-    $A85&lt;&gt;"",
-    COUNTIF(C:C,$A85)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S85" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T85" s="13" t="e">
@@ -32497,7 +32027,7 @@
         <v>172</v>
       </c>
       <c r="AC85" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD85" s="13" t="str">
@@ -32531,11 +32061,11 @@
         <v/>
       </c>
       <c r="AG85" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH85" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI85" s="13" t="str">
@@ -32609,18 +32139,11 @@
         <v>935</v>
       </c>
       <c r="R86" s="9" t="str">
-        <f>IF(
-  AND(
-    $A86&lt;&gt;"",
-    COUNTIF(C:C,$A86)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S86" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T86" s="13" t="str">
@@ -32743,7 +32266,7 @@
         <v>113</v>
       </c>
       <c r="AC86" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD86" s="13" t="str">
@@ -32777,11 +32300,11 @@
         <v/>
       </c>
       <c r="AG86" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH86" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI86" s="13" t="str">
@@ -32855,18 +32378,11 @@
         <v>935</v>
       </c>
       <c r="R87" s="9" t="str">
-        <f>IF(
-  AND(
-    $A87&lt;&gt;"",
-    COUNTIF(C:C,$A87)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S87" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T87" s="13" t="str">
@@ -32989,7 +32505,7 @@
         <v>171</v>
       </c>
       <c r="AC87" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD87" s="13" t="str">
@@ -33023,11 +32539,11 @@
         <v/>
       </c>
       <c r="AG87" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH87" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI87" s="13" t="str">
@@ -33101,18 +32617,11 @@
         <v>935</v>
       </c>
       <c r="R88" s="9" t="str">
-        <f>IF(
-  AND(
-    $A88&lt;&gt;"",
-    COUNTIF(C:C,$A88)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S88" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T88" s="13" t="str">
@@ -33235,7 +32744,7 @@
         <v>162</v>
       </c>
       <c r="AC88" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD88" s="13" t="str">
@@ -33269,11 +32778,11 @@
         <v/>
       </c>
       <c r="AG88" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH88" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI88" s="13" t="str">
@@ -33347,18 +32856,11 @@
         <v>935</v>
       </c>
       <c r="R89" s="9" t="str">
-        <f>IF(
-  AND(
-    $A89&lt;&gt;"",
-    COUNTIF(C:C,$A89)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S89" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T89" s="13" t="str">
@@ -33481,7 +32983,7 @@
         <v>123</v>
       </c>
       <c r="AC89" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD89" s="13" t="str">
@@ -33515,11 +33017,11 @@
         <v/>
       </c>
       <c r="AG89" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH89" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI89" s="13" t="str">
@@ -33593,18 +33095,11 @@
         <v>935</v>
       </c>
       <c r="R90" s="9" t="str">
-        <f>IF(
-  AND(
-    $A90&lt;&gt;"",
-    COUNTIF(C:C,$A90)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S90" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T90" s="13" t="str">
@@ -33727,7 +33222,7 @@
         <v>111</v>
       </c>
       <c r="AC90" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD90" s="13" t="str">
@@ -33761,11 +33256,11 @@
         <v/>
       </c>
       <c r="AG90" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH90" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI90" s="13" t="str">
@@ -33839,18 +33334,11 @@
         <v>935</v>
       </c>
       <c r="R91" s="9" t="str">
-        <f>IF(
-  AND(
-    $A91&lt;&gt;"",
-    COUNTIF(C:C,$A91)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S91" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T91" s="13" t="str">
@@ -33973,7 +33461,7 @@
         <v>153</v>
       </c>
       <c r="AC91" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD91" s="13" t="str">
@@ -34007,11 +33495,11 @@
         <v/>
       </c>
       <c r="AG91" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH91" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI91" s="13" t="str">
@@ -34085,18 +33573,11 @@
         <v>935</v>
       </c>
       <c r="R92" s="9" t="str">
-        <f>IF(
-  AND(
-    $A92&lt;&gt;"",
-    COUNTIF(C:C,$A92)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S92" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T92" s="13" t="str">
@@ -34219,7 +33700,7 @@
         <v>161</v>
       </c>
       <c r="AC92" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD92" s="13" t="str">
@@ -34253,11 +33734,11 @@
         <v/>
       </c>
       <c r="AG92" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH92" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI92" s="13" t="str">
@@ -34331,18 +33812,11 @@
         <v>935</v>
       </c>
       <c r="R93" s="9" t="str">
-        <f>IF(
-  AND(
-    $A93&lt;&gt;"",
-    COUNTIF(C:C,$A93)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S93" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T93" s="13" t="str">
@@ -34465,7 +33939,7 @@
         <v>113</v>
       </c>
       <c r="AC93" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD93" s="13" t="str">
@@ -34499,11 +33973,11 @@
         <v/>
       </c>
       <c r="AG93" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH93" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI93" s="13" t="str">
@@ -34577,18 +34051,11 @@
         <v>935</v>
       </c>
       <c r="R94" s="9" t="str">
-        <f>IF(
-  AND(
-    $A94&lt;&gt;"",
-    COUNTIF(C:C,$A94)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S94" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T94" s="13" t="str">
@@ -34711,7 +34178,7 @@
         <v>123</v>
       </c>
       <c r="AC94" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD94" s="13" t="str">
@@ -34745,11 +34212,11 @@
         <v/>
       </c>
       <c r="AG94" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH94" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI94" s="13" t="str">
@@ -34823,18 +34290,11 @@
         <v>935</v>
       </c>
       <c r="R95" s="9" t="str">
-        <f>IF(
-  AND(
-    $A95&lt;&gt;"",
-    COUNTIF(C:C,$A95)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S95" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T95" s="13" t="str">
@@ -34957,7 +34417,7 @@
         <v>134</v>
       </c>
       <c r="AC95" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD95" s="13" t="str">
@@ -34991,11 +34451,11 @@
         <v/>
       </c>
       <c r="AG95" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH95" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI95" s="13" t="str">
@@ -35069,18 +34529,11 @@
         <v>935</v>
       </c>
       <c r="R96" s="9" t="str">
-        <f>IF(
-  AND(
-    $A96&lt;&gt;"",
-    COUNTIF(C:C,$A96)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S96" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T96" s="13" t="str">
@@ -35203,7 +34656,7 @@
         <v>122</v>
       </c>
       <c r="AC96" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD96" s="13" t="str">
@@ -35237,11 +34690,11 @@
         <v/>
       </c>
       <c r="AG96" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH96" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI96" s="13" t="str">
@@ -35315,18 +34768,11 @@
         <v>935</v>
       </c>
       <c r="R97" s="9" t="str">
-        <f>IF(
-  AND(
-    $A97&lt;&gt;"",
-    COUNTIF(C:C,$A97)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S97" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T97" s="13" t="str">
@@ -35449,7 +34895,7 @@
         <v>162</v>
       </c>
       <c r="AC97" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD97" s="13" t="str">
@@ -35483,11 +34929,11 @@
         <v/>
       </c>
       <c r="AG97" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH97" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI97" s="13" t="str">
@@ -35561,18 +35007,11 @@
         <v>935</v>
       </c>
       <c r="R98" s="9" t="str">
-        <f>IF(
-  AND(
-    $A98&lt;&gt;"",
-    COUNTIF(C:C,$A98)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S98" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T98" s="13" t="str">
@@ -35695,7 +35134,7 @@
         <v>161</v>
       </c>
       <c r="AC98" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD98" s="13" t="str">
@@ -35729,11 +35168,11 @@
         <v/>
       </c>
       <c r="AG98" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH98" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI98" s="13" t="str">
@@ -35807,18 +35246,11 @@
         <v>935</v>
       </c>
       <c r="R99" s="9" t="str">
-        <f>IF(
-  AND(
-    $A99&lt;&gt;"",
-    COUNTIF(C:C,$A99)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S99" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T99" s="13" t="str">
@@ -35941,7 +35373,7 @@
         <v>121</v>
       </c>
       <c r="AC99" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD99" s="13" t="str">
@@ -35975,11 +35407,11 @@
         <v/>
       </c>
       <c r="AG99" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH99" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI99" s="13" t="str">
@@ -36053,18 +35485,11 @@
         <v>935</v>
       </c>
       <c r="R100" s="9" t="str">
-        <f>IF(
-  AND(
-    $A100&lt;&gt;"",
-    COUNTIF(C:C,$A100)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S100" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T100" s="13" t="str">
@@ -36187,7 +35612,7 @@
         <v>172</v>
       </c>
       <c r="AC100" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD100" s="13" t="str">
@@ -36221,11 +35646,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\TVClock（デスクトップ時計）.lnk</v>
       </c>
       <c r="AG100" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH100" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI100" s="13" t="str">
@@ -36299,18 +35724,11 @@
         <v>935</v>
       </c>
       <c r="R101" s="9" t="str">
-        <f>IF(
-  AND(
-    $A101&lt;&gt;"",
-    COUNTIF(C:C,$A101)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S101" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T101" s="13" t="str">
@@ -36433,7 +35851,7 @@
         <v>111</v>
       </c>
       <c r="AC101" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD101" s="13" t="str">
@@ -36467,11 +35885,11 @@
         <v/>
       </c>
       <c r="AG101" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH101" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI101" s="13" t="str">
@@ -36545,18 +35963,11 @@
         <v>935</v>
       </c>
       <c r="R102" s="9" t="str">
-        <f>IF(
-  AND(
-    $A102&lt;&gt;"",
-    COUNTIF(C:C,$A102)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S102" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T102" s="13" t="str">
@@ -36679,7 +36090,7 @@
         <v>172</v>
       </c>
       <c r="AC102" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD102" s="13" t="str">
@@ -36713,11 +36124,11 @@
         <v/>
       </c>
       <c r="AG102" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH102" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI102" s="13" t="str">
@@ -36791,18 +36202,11 @@
         <v>935</v>
       </c>
       <c r="R103" s="9" t="str">
-        <f>IF(
-  AND(
-    $A103&lt;&gt;"",
-    COUNTIF(C:C,$A103)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S103" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T103" s="13" t="str">
@@ -36925,7 +36329,7 @@
         <v>172</v>
       </c>
       <c r="AC103" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AD103" s="13" t="str">
@@ -36959,11 +36363,11 @@
         <v/>
       </c>
       <c r="AG103" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH103" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI103" s="13" t="str">
@@ -37037,18 +36441,11 @@
         <v>935</v>
       </c>
       <c r="R104" s="9" t="str">
-        <f>IF(
-  AND(
-    $A104&lt;&gt;"",
-    COUNTIF(C:C,$A104)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S104" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T104" s="13" t="str">
@@ -37171,7 +36568,7 @@
         <v>123</v>
       </c>
       <c r="AC104" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> (&amp;V)</v>
       </c>
       <c r="AD104" s="13" t="str">
@@ -37205,11 +36602,11 @@
         <v/>
       </c>
       <c r="AG104" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH104" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI104" s="13" t="str">
@@ -37283,18 +36680,11 @@
         <v>935</v>
       </c>
       <c r="R105" s="9" t="str">
-        <f>IF(
-  AND(
-    $A105&lt;&gt;"",
-    COUNTIF(C:C,$A105)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S105" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T105" s="13" t="str">
@@ -37417,7 +36807,7 @@
         <v>123</v>
       </c>
       <c r="AC105" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve"> (&amp;C)</v>
       </c>
       <c r="AD105" s="13" t="str">
@@ -37451,11 +36841,11 @@
         <v/>
       </c>
       <c r="AG105" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AH105" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AI105" s="13" t="str">
@@ -37529,18 +36919,11 @@
         <v>935</v>
       </c>
       <c r="R106" s="9" t="str">
-        <f>IF(
-  AND(
-    $A106&lt;&gt;"",
-    COUNTIF(C:C,$A106)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S106" s="9" t="str">
-        <f t="shared" ref="S106:S152" si="12">IF(
+        <f t="shared" ref="S106:S152" si="14">IF(
   OR(
     $H106="",
     $H106="-",
@@ -37671,7 +37054,7 @@
         <v>113</v>
       </c>
       <c r="AC106" s="20" t="str">
-        <f t="shared" ref="AC106:AC152" si="13">IF(AND($M106&lt;&gt;"",$M106&lt;&gt;"-")," (&amp;"&amp;$M106&amp;")","")</f>
+        <f t="shared" ref="AC106:AC152" si="15">IF(AND($M106&lt;&gt;"",$M106&lt;&gt;"-")," (&amp;"&amp;$M106&amp;")","")</f>
         <v/>
       </c>
       <c r="AD106" s="13" t="str">
@@ -37705,7 +37088,7 @@
         <v/>
       </c>
       <c r="AG106" s="13" t="str">
-        <f t="shared" ref="AG106:AG152" si="14">IF(
+        <f t="shared" ref="AG106:AG152" si="16">IF(
   AND($A106&lt;&gt;"",$O106&lt;&gt;"-",$O106&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O106&amp;""" /tr """&amp;$C106&amp;""" /sc daily /st "&amp;$P106&amp;" /rl highest"
@@ -37715,7 +37098,7 @@
         <v/>
       </c>
       <c r="AH106" s="13" t="str">
-        <f t="shared" ref="AH106:AH152" si="15">IF(
+        <f t="shared" ref="AH106:AH152" si="17">IF(
   AND($A106&lt;&gt;"",$O106&lt;&gt;"-",$O106&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O106&amp;""""
@@ -37795,18 +37178,11 @@
         <v>935</v>
       </c>
       <c r="R107" s="9" t="str">
-        <f>IF(
-  AND(
-    $A107&lt;&gt;"",
-    COUNTIF(C:C,$A107)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S107" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T107" s="13" t="str">
@@ -37929,7 +37305,7 @@
         <v>171</v>
       </c>
       <c r="AC107" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD107" s="13" t="str">
@@ -37963,11 +37339,11 @@
         <v/>
       </c>
       <c r="AG107" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH107" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI107" s="13" t="str">
@@ -38041,18 +37417,11 @@
         <v>935</v>
       </c>
       <c r="R108" s="9" t="str">
-        <f>IF(
-  AND(
-    $A108&lt;&gt;"",
-    COUNTIF(C:C,$A108)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S108" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T108" s="13" t="str">
@@ -38175,7 +37544,7 @@
         <v>123</v>
       </c>
       <c r="AC108" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD108" s="13" t="str">
@@ -38209,11 +37578,11 @@
         <v/>
       </c>
       <c r="AG108" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH108" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI108" s="13" t="str">
@@ -38287,18 +37656,11 @@
         <v>935</v>
       </c>
       <c r="R109" s="9" t="str">
-        <f>IF(
-  AND(
-    $A109&lt;&gt;"",
-    COUNTIF(C:C,$A109)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S109" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T109" s="13" t="str">
@@ -38421,7 +37783,7 @@
         <v>122</v>
       </c>
       <c r="AC109" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD109" s="13" t="str">
@@ -38455,11 +37817,11 @@
         <v/>
       </c>
       <c r="AG109" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH109" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI109" s="13" t="str">
@@ -38533,18 +37895,11 @@
         <v>935</v>
       </c>
       <c r="R110" s="9" t="str">
-        <f>IF(
-  AND(
-    $A110&lt;&gt;"",
-    COUNTIF(C:C,$A110)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S110" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T110" s="13" t="str">
@@ -38667,7 +38022,7 @@
         <v>172</v>
       </c>
       <c r="AC110" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD110" s="13" t="str">
@@ -38701,11 +38056,11 @@
         <v/>
       </c>
       <c r="AG110" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH110" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI110" s="13" t="str">
@@ -38779,18 +38134,11 @@
         <v>935</v>
       </c>
       <c r="R111" s="9" t="str">
-        <f>IF(
-  AND(
-    $A111&lt;&gt;"",
-    COUNTIF(C:C,$A111)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S111" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T111" s="13" t="str">
@@ -38913,7 +38261,7 @@
         <v>172</v>
       </c>
       <c r="AC111" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD111" s="13" t="str">
@@ -38947,11 +38295,11 @@
         <v/>
       </c>
       <c r="AG111" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH111" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI111" s="13" t="str">
@@ -39025,18 +38373,11 @@
         <v>935</v>
       </c>
       <c r="R112" s="9" t="str">
-        <f>IF(
-  AND(
-    $A112&lt;&gt;"",
-    COUNTIF(C:C,$A112)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S112" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T112" s="13" t="str">
@@ -39159,7 +38500,7 @@
         <v>122</v>
       </c>
       <c r="AC112" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD112" s="13" t="str">
@@ -39193,11 +38534,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\X-Finder（ファイラー）.lnk</v>
       </c>
       <c r="AG112" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH112" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI112" s="13" t="str">
@@ -39271,18 +38612,11 @@
         <v>935</v>
       </c>
       <c r="R113" s="9" t="str">
-        <f>IF(
-  AND(
-    $A113&lt;&gt;"",
-    COUNTIF(C:C,$A113)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S113" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T113" s="13" t="str">
@@ -39405,7 +38739,7 @@
         <v>162</v>
       </c>
       <c r="AC113" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD113" s="13" t="str">
@@ -39439,11 +38773,11 @@
         <v/>
       </c>
       <c r="AG113" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH113" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI113" s="13" t="str">
@@ -39517,18 +38851,11 @@
         <v>935</v>
       </c>
       <c r="R114" s="9" t="str">
-        <f>IF(
-  AND(
-    $A114&lt;&gt;"",
-    COUNTIF(C:C,$A114)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S114" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T114" s="13" t="str">
@@ -39651,7 +38978,7 @@
         <v>172</v>
       </c>
       <c r="AC114" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD114" s="13" t="str">
@@ -39685,11 +39012,11 @@
         <v/>
       </c>
       <c r="AG114" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH114" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI114" s="13" t="str">
@@ -39763,18 +39090,11 @@
         <v>1112</v>
       </c>
       <c r="R115" s="9" t="str">
-        <f>IF(
-  AND(
-    $A115&lt;&gt;"",
-    COUNTIF(C:C,$A115)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S115" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T115" s="13" t="str">
@@ -39897,7 +39217,7 @@
         <v>162</v>
       </c>
       <c r="AC115" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD115" s="13" t="str">
@@ -39931,11 +39251,11 @@
         <v/>
       </c>
       <c r="AG115" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH115" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI115" s="13" t="str">
@@ -40009,18 +39329,11 @@
         <v>1162</v>
       </c>
       <c r="R116" s="9" t="str">
-        <f>IF(
-  AND(
-    $A116&lt;&gt;"",
-    COUNTIF(C:C,$A116)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S116" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T116" s="13" t="str">
@@ -40143,7 +39456,7 @@
         <v>171</v>
       </c>
       <c r="AC116" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD116" s="13" t="str">
@@ -40177,11 +39490,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\HiddeX（ボスが来た）.lnk</v>
       </c>
       <c r="AG116" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH116" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI116" s="13" t="str">
@@ -40255,18 +39568,11 @@
         <v>934</v>
       </c>
       <c r="R117" s="9" t="str">
-        <f>IF(
-  AND(
-    $A117&lt;&gt;"",
-    COUNTIF(C:C,$A117)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S117" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T117" s="13" t="str">
@@ -40389,7 +39695,7 @@
         <v>113</v>
       </c>
       <c r="AC117" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD117" s="13" t="str">
@@ -40423,11 +39729,11 @@
         <v/>
       </c>
       <c r="AG117" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH117" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI117" s="13" t="str">
@@ -40501,18 +39807,11 @@
         <v>934</v>
       </c>
       <c r="R118" s="9" t="str">
-        <f>IF(
-  AND(
-    $A118&lt;&gt;"",
-    COUNTIF(C:C,$A118)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S118" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T118" s="13" t="str">
@@ -40635,7 +39934,7 @@
         <v>113</v>
       </c>
       <c r="AC118" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD118" s="13" t="str">
@@ -40669,11 +39968,11 @@
         <v/>
       </c>
       <c r="AG118" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH118" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI118" s="13" t="str">
@@ -40747,14 +40046,7 @@
         <v>1403</v>
       </c>
       <c r="R119" s="9" t="str">
-        <f>IF(
-  AND(
-    $A119&lt;&gt;"",
-    COUNTIF(C:C,$A119)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S119" s="9" t="str">
@@ -41013,18 +40305,11 @@
         <v>1245</v>
       </c>
       <c r="R120" s="9" t="str">
-        <f>IF(
-  AND(
-    $A120&lt;&gt;"",
-    COUNTIF(C:C,$A120)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S120" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T120" s="13" t="str">
@@ -41147,7 +40432,7 @@
         <v>143</v>
       </c>
       <c r="AC120" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD120" s="13" t="str">
@@ -41181,11 +40466,11 @@
         <v/>
       </c>
       <c r="AG120" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH120" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI120" s="13" t="str">
@@ -41259,18 +40544,11 @@
         <v>39</v>
       </c>
       <c r="R121" s="9" t="str">
-        <f>IF(
-  AND(
-    $A121&lt;&gt;"",
-    COUNTIF(C:C,$A121)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S121" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T121" s="13" t="str">
@@ -41393,7 +40671,7 @@
         <v>171</v>
       </c>
       <c r="AC121" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD121" s="13" t="str">
@@ -41427,11 +40705,11 @@
         <v/>
       </c>
       <c r="AG121" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH121" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI121" s="13" t="str">
@@ -41505,18 +40783,11 @@
         <v>1371</v>
       </c>
       <c r="R122" s="9" t="str">
-        <f>IF(
-  AND(
-    $A122&lt;&gt;"",
-    COUNTIF(C:C,$A122)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S122" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T122" s="13" t="str">
@@ -41639,7 +40910,7 @@
         <v>123</v>
       </c>
       <c r="AC122" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD122" s="13" t="str">
@@ -41673,11 +40944,11 @@
         <v/>
       </c>
       <c r="AG122" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH122" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI122" s="13" t="str">
@@ -41751,18 +41022,11 @@
         <v>1374</v>
       </c>
       <c r="R123" s="9" t="str">
-        <f>IF(
-  AND(
-    $A123&lt;&gt;"",
-    COUNTIF(C:C,$A123)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S123" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T123" s="13" t="str">
@@ -41885,7 +41149,7 @@
         <v>153</v>
       </c>
       <c r="AC123" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD123" s="13" t="str">
@@ -41919,11 +41183,11 @@
         <v/>
       </c>
       <c r="AG123" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH123" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI123" s="13" t="str">
@@ -41997,14 +41261,7 @@
         <v>1396</v>
       </c>
       <c r="R124" s="9" t="str">
-        <f>IF(
-  AND(
-    $A124&lt;&gt;"",
-    COUNTIF(C:C,$A124)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S124" s="9" t="str">
@@ -42263,14 +41520,7 @@
         <v>1407</v>
       </c>
       <c r="R125" s="9" t="str">
-        <f>IF(
-  AND(
-    $A125&lt;&gt;"",
-    COUNTIF(C:C,$A125)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S125" s="9" t="str">
@@ -42529,14 +41779,7 @@
         <v>1415</v>
       </c>
       <c r="R126" s="9" t="str">
-        <f>IF(
-  AND(
-    $A126&lt;&gt;"",
-    COUNTIF(C:C,$A126)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S126" s="9" t="str">
@@ -42795,18 +42038,11 @@
         <v>39</v>
       </c>
       <c r="R127" s="9" t="str">
-        <f>IF(
-  AND(
-    $A127&lt;&gt;"",
-    COUNTIF(C:C,$A127)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S127" s="9" t="str">
-        <f t="shared" ref="S127" si="16">IF(
+        <f t="shared" ref="S127" si="18">IF(
   OR(
     $H127="",
     $H127="-",
@@ -42937,7 +42173,7 @@
         <v>113</v>
       </c>
       <c r="AC127" s="20" t="str">
-        <f t="shared" ref="AC127" si="17">IF(AND($M127&lt;&gt;"",$M127&lt;&gt;"-")," (&amp;"&amp;$M127&amp;")","")</f>
+        <f t="shared" ref="AC127" si="19">IF(AND($M127&lt;&gt;"",$M127&lt;&gt;"-")," (&amp;"&amp;$M127&amp;")","")</f>
         <v/>
       </c>
       <c r="AD127" s="13" t="str">
@@ -42971,7 +42207,7 @@
         <v/>
       </c>
       <c r="AG127" s="13" t="str">
-        <f t="shared" ref="AG127" si="18">IF(
+        <f t="shared" ref="AG127" si="20">IF(
   AND($A127&lt;&gt;"",$O127&lt;&gt;"-",$O127&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O127&amp;""" /tr """&amp;$C127&amp;""" /sc daily /st "&amp;$P127&amp;" /rl highest"
@@ -42981,7 +42217,7 @@
         <v/>
       </c>
       <c r="AH127" s="13" t="str">
-        <f t="shared" ref="AH127" si="19">IF(
+        <f t="shared" ref="AH127" si="21">IF(
   AND($A127&lt;&gt;"",$O127&lt;&gt;"-",$O127&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O127&amp;""""
@@ -43061,14 +42297,7 @@
         <v>1439</v>
       </c>
       <c r="R128" s="9" t="str">
-        <f>IF(
-  AND(
-    $A128&lt;&gt;"",
-    COUNTIF(C:C,$A128)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S128" s="9" t="str">
@@ -43327,14 +42556,7 @@
         <v>39</v>
       </c>
       <c r="R129" s="9" t="str">
-        <f>IF(
-  AND(
-    $A129&lt;&gt;"",
-    COUNTIF(C:C,$A129)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S129" s="9" t="str">
@@ -43593,14 +42815,7 @@
         <v>39</v>
       </c>
       <c r="R130" s="9" t="str">
-        <f>IF(
-  AND(
-    $A130&lt;&gt;"",
-    COUNTIF(C:C,$A130)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S130" s="9" t="str">
@@ -43859,14 +43074,7 @@
         <v>1571</v>
       </c>
       <c r="R131" s="9" t="str">
-        <f>IF(
-  AND(
-    $A131&lt;&gt;"",
-    COUNTIF(C:C,$A131)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S131" s="9" t="str">
@@ -44125,18 +43333,11 @@
         <v>935</v>
       </c>
       <c r="R132" s="9" t="str">
-        <f>IF(
-  AND(
-    $A132&lt;&gt;"",
-    COUNTIF(C:C,$A132)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S132" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T132" s="13" t="str">
@@ -44259,7 +43460,7 @@
         <v>123</v>
       </c>
       <c r="AC132" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD132" s="13" t="str">
@@ -44293,11 +43494,11 @@
         <v/>
       </c>
       <c r="AG132" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH132" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI132" s="13" t="str">
@@ -44371,18 +43572,11 @@
         <v>935</v>
       </c>
       <c r="R133" s="9" t="str">
-        <f>IF(
-  AND(
-    $A133&lt;&gt;"",
-    COUNTIF(C:C,$A133)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S133" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T133" s="13" t="str">
@@ -44505,7 +43699,7 @@
         <v>133</v>
       </c>
       <c r="AC133" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD133" s="13" t="str">
@@ -44539,11 +43733,11 @@
         <v/>
       </c>
       <c r="AG133" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH133" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI133" s="13" t="str">
@@ -44617,18 +43811,11 @@
         <v>935</v>
       </c>
       <c r="R134" s="9" t="str">
-        <f>IF(
-  AND(
-    $A134&lt;&gt;"",
-    COUNTIF(C:C,$A134)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S134" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T134" s="13" t="str">
@@ -44751,7 +43938,7 @@
         <v>172</v>
       </c>
       <c r="AC134" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD134" s="13" t="str">
@@ -44785,11 +43972,11 @@
         <v/>
       </c>
       <c r="AG134" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH134" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI134" s="13" t="str">
@@ -44863,18 +44050,11 @@
         <v>935</v>
       </c>
       <c r="R135" s="9" t="str">
-        <f>IF(
-  AND(
-    $A135&lt;&gt;"",
-    COUNTIF(C:C,$A135)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S135" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T135" s="13" t="str">
@@ -44997,7 +44177,7 @@
         <v>123</v>
       </c>
       <c r="AC135" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD135" s="13" t="str">
@@ -45031,11 +44211,11 @@
         <v/>
       </c>
       <c r="AG135" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH135" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI135" s="13" t="str">
@@ -45109,18 +44289,11 @@
         <v>935</v>
       </c>
       <c r="R136" s="9" t="str">
-        <f>IF(
-  AND(
-    $A136&lt;&gt;"",
-    COUNTIF(C:C,$A136)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S136" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T136" s="13" t="str">
@@ -45243,7 +44416,7 @@
         <v>123</v>
       </c>
       <c r="AC136" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD136" s="13" t="str">
@@ -45277,11 +44450,11 @@
         <v/>
       </c>
       <c r="AG136" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH136" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI136" s="13" t="str">
@@ -45355,18 +44528,11 @@
         <v>39</v>
       </c>
       <c r="R137" s="9" t="str">
-        <f>IF(
-  AND(
-    $A137&lt;&gt;"",
-    COUNTIF(C:C,$A137)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S137" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T137" s="13" t="str">
@@ -45489,7 +44655,7 @@
         <v>113</v>
       </c>
       <c r="AC137" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD137" s="13" t="str">
@@ -45523,11 +44689,11 @@
         <v/>
       </c>
       <c r="AG137" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH137" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI137" s="13" t="str">
@@ -45601,18 +44767,11 @@
         <v>1374</v>
       </c>
       <c r="R138" s="9" t="str">
-        <f>IF(
-  AND(
-    $A138&lt;&gt;"",
-    COUNTIF(C:C,$A138)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S138" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T138" s="13" t="str">
@@ -45735,7 +44894,7 @@
         <v>123</v>
       </c>
       <c r="AC138" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD138" s="13" t="str">
@@ -45769,11 +44928,11 @@
         <v/>
       </c>
       <c r="AG138" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH138" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI138" s="13" t="str">
@@ -45847,7 +45006,7 @@
         <v>1387</v>
       </c>
       <c r="R139" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R139:R202" si="22">IF(
   AND(
     $A139&lt;&gt;"",
     COUNTIF(C:C,$A139)&gt;1
@@ -46113,14 +45272,7 @@
         <v>39</v>
       </c>
       <c r="R140" s="9" t="str">
-        <f>IF(
-  AND(
-    $A140&lt;&gt;"",
-    COUNTIF(C:C,$A140)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S140" s="9" t="str">
@@ -46379,14 +45531,7 @@
         <v>1436</v>
       </c>
       <c r="R141" s="9" t="str">
-        <f>IF(
-  AND(
-    $A141&lt;&gt;"",
-    COUNTIF(C:C,$A141)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S141" s="9" t="str">
@@ -46645,14 +45790,7 @@
         <v>39</v>
       </c>
       <c r="R142" s="9" t="str">
-        <f>IF(
-  AND(
-    $A142&lt;&gt;"",
-    COUNTIF(C:C,$A142)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S142" s="9" t="str">
@@ -46911,14 +46049,7 @@
         <v>39</v>
       </c>
       <c r="R143" s="9" t="str">
-        <f>IF(
-  AND(
-    $A143&lt;&gt;"",
-    COUNTIF(C:C,$A143)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S143" s="9" t="str">
@@ -47177,18 +46308,11 @@
         <v>39</v>
       </c>
       <c r="R144" s="9" t="str">
-        <f>IF(
-  AND(
-    $A144&lt;&gt;"",
-    COUNTIF(C:C,$A144)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S144" s="9" t="str">
-        <f t="shared" ref="S144" si="20">IF(
+        <f t="shared" ref="S144" si="23">IF(
   OR(
     $H144="",
     $H144="-",
@@ -47319,7 +46443,7 @@
         <v>162</v>
       </c>
       <c r="AC144" s="20" t="str">
-        <f t="shared" ref="AC144" si="21">IF(AND($M144&lt;&gt;"",$M144&lt;&gt;"-")," (&amp;"&amp;$M144&amp;")","")</f>
+        <f t="shared" ref="AC144" si="24">IF(AND($M144&lt;&gt;"",$M144&lt;&gt;"-")," (&amp;"&amp;$M144&amp;")","")</f>
         <v/>
       </c>
       <c r="AD144" s="13" t="str">
@@ -47353,7 +46477,7 @@
         <v/>
       </c>
       <c r="AG144" s="13" t="str">
-        <f t="shared" ref="AG144" si="22">IF(
+        <f t="shared" ref="AG144" si="25">IF(
   AND($A144&lt;&gt;"",$O144&lt;&gt;"-",$O144&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O144&amp;""" /tr """&amp;$C144&amp;""" /sc daily /st "&amp;$P144&amp;" /rl highest"
@@ -47363,7 +46487,7 @@
         <v/>
       </c>
       <c r="AH144" s="13" t="str">
-        <f t="shared" ref="AH144" si="23">IF(
+        <f t="shared" ref="AH144" si="26">IF(
   AND($A144&lt;&gt;"",$O144&lt;&gt;"-",$O144&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O144&amp;""""
@@ -47443,18 +46567,11 @@
         <v>935</v>
       </c>
       <c r="R145" s="9" t="str">
-        <f>IF(
-  AND(
-    $A145&lt;&gt;"",
-    COUNTIF(C:C,$A145)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S145" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T145" s="13" t="str">
@@ -47577,7 +46694,7 @@
         <v>161</v>
       </c>
       <c r="AC145" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD145" s="13" t="str">
@@ -47611,11 +46728,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\MicrosoftEdge（ブラウザ）.lnk</v>
       </c>
       <c r="AG145" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH145" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI145" s="13" t="str">
@@ -47689,18 +46806,11 @@
         <v>935</v>
       </c>
       <c r="R146" s="9" t="str">
-        <f>IF(
-  AND(
-    $A146&lt;&gt;"",
-    COUNTIF(C:C,$A146)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S146" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T146" s="13" t="str">
@@ -47823,7 +46933,7 @@
         <v>123</v>
       </c>
       <c r="AC146" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD146" s="13" t="str">
@@ -47857,11 +46967,11 @@
         <v/>
       </c>
       <c r="AG146" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH146" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI146" s="13" t="str">
@@ -47935,18 +47045,11 @@
         <v>935</v>
       </c>
       <c r="R147" s="9" t="str">
-        <f>IF(
-  AND(
-    $A147&lt;&gt;"",
-    COUNTIF(C:C,$A147)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S147" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T147" s="13" t="str">
@@ -48069,7 +47172,7 @@
         <v>123</v>
       </c>
       <c r="AC147" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD147" s="13" t="str">
@@ -48103,11 +47206,11 @@
         <v/>
       </c>
       <c r="AG147" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH147" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI147" s="13" t="str">
@@ -48181,18 +47284,11 @@
         <v>935</v>
       </c>
       <c r="R148" s="9" t="str">
-        <f>IF(
-  AND(
-    $A148&lt;&gt;"",
-    COUNTIF(C:C,$A148)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S148" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T148" s="13" t="str">
@@ -48315,7 +47411,7 @@
         <v>123</v>
       </c>
       <c r="AC148" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD148" s="13" t="str">
@@ -48349,11 +47445,11 @@
         <v/>
       </c>
       <c r="AG148" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH148" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI148" s="13" t="str">
@@ -48427,18 +47523,11 @@
         <v>935</v>
       </c>
       <c r="R149" s="9" t="str">
-        <f>IF(
-  AND(
-    $A149&lt;&gt;"",
-    COUNTIF(C:C,$A149)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S149" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T149" s="13" t="str">
@@ -48561,7 +47650,7 @@
         <v>161</v>
       </c>
       <c r="AC149" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD149" s="13" t="str">
@@ -48595,11 +47684,11 @@
         <v/>
       </c>
       <c r="AG149" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH149" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI149" s="13" t="str">
@@ -48673,18 +47762,11 @@
         <v>935</v>
       </c>
       <c r="R150" s="9" t="str">
-        <f>IF(
-  AND(
-    $A150&lt;&gt;"",
-    COUNTIF(C:C,$A150)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S150" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T150" s="13" t="str">
@@ -48807,7 +47889,7 @@
         <v>153</v>
       </c>
       <c r="AC150" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD150" s="13" t="str">
@@ -48841,11 +47923,11 @@
         <v/>
       </c>
       <c r="AG150" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH150" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI150" s="13" t="str">
@@ -48919,18 +48001,11 @@
         <v>935</v>
       </c>
       <c r="R151" s="9" t="str">
-        <f>IF(
-  AND(
-    $A151&lt;&gt;"",
-    COUNTIF(C:C,$A151)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S151" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T151" s="13" t="str">
@@ -49053,7 +48128,7 @@
         <v>122</v>
       </c>
       <c r="AC151" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD151" s="13" t="str">
@@ -49087,11 +48162,11 @@
         <v/>
       </c>
       <c r="AG151" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH151" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI151" s="13" t="str">
@@ -49165,18 +48240,11 @@
         <v>935</v>
       </c>
       <c r="R152" s="9" t="str">
-        <f>IF(
-  AND(
-    $A152&lt;&gt;"",
-    COUNTIF(C:C,$A152)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S152" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="T152" s="13" t="str">
@@ -49299,7 +48367,7 @@
         <v>161</v>
       </c>
       <c r="AC152" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD152" s="13" t="str">
@@ -49333,11 +48401,11 @@
         <v/>
       </c>
       <c r="AG152" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH152" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AI152" s="13" t="str">
@@ -49411,14 +48479,7 @@
         <v>1430</v>
       </c>
       <c r="R153" s="9" t="str">
-        <f>IF(
-  AND(
-    $A153&lt;&gt;"",
-    COUNTIF(C:C,$A153)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S153" s="9" t="str">
@@ -49677,18 +48738,11 @@
         <v>935</v>
       </c>
       <c r="R154" s="9" t="str">
-        <f>IF(
-  AND(
-    $A154&lt;&gt;"",
-    COUNTIF(C:C,$A154)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S154" s="9" t="str">
-        <f t="shared" ref="S154:S186" si="24">IF(
+        <f t="shared" ref="S154:S186" si="27">IF(
   OR(
     $H154="",
     $H154="-",
@@ -49819,7 +48873,7 @@
         <v>161</v>
       </c>
       <c r="AC154" s="20" t="str">
-        <f t="shared" ref="AC154:AC186" si="25">IF(AND($M154&lt;&gt;"",$M154&lt;&gt;"-")," (&amp;"&amp;$M154&amp;")","")</f>
+        <f t="shared" ref="AC154:AC186" si="28">IF(AND($M154&lt;&gt;"",$M154&lt;&gt;"-")," (&amp;"&amp;$M154&amp;")","")</f>
         <v/>
       </c>
       <c r="AD154" s="13" t="str">
@@ -49853,7 +48907,7 @@
         <v/>
       </c>
       <c r="AG154" s="13" t="str">
-        <f t="shared" ref="AG154:AG186" si="26">IF(
+        <f t="shared" ref="AG154:AG186" si="29">IF(
   AND($A154&lt;&gt;"",$O154&lt;&gt;"-",$O154&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O154&amp;""" /tr """&amp;$C154&amp;""" /sc daily /st "&amp;$P154&amp;" /rl highest"
@@ -49863,7 +48917,7 @@
         <v/>
       </c>
       <c r="AH154" s="13" t="str">
-        <f t="shared" ref="AH154:AH186" si="27">IF(
+        <f t="shared" ref="AH154:AH186" si="30">IF(
   AND($A154&lt;&gt;"",$O154&lt;&gt;"-",$O154&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O154&amp;""""
@@ -49943,18 +48997,11 @@
         <v>39</v>
       </c>
       <c r="R155" s="9" t="str">
-        <f>IF(
-  AND(
-    $A155&lt;&gt;"",
-    COUNTIF(C:C,$A155)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S155" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T155" s="13" t="str">
@@ -50077,7 +49124,7 @@
         <v>172</v>
       </c>
       <c r="AC155" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD155" s="13" t="str">
@@ -50111,11 +49158,11 @@
         <v/>
       </c>
       <c r="AG155" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH155" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI155" s="13" t="str">
@@ -50189,18 +49236,11 @@
         <v>39</v>
       </c>
       <c r="R156" s="9" t="str">
-        <f>IF(
-  AND(
-    $A156&lt;&gt;"",
-    COUNTIF(C:C,$A156)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S156" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T156" s="13" t="str">
@@ -50323,7 +49363,7 @@
         <v>172</v>
       </c>
       <c r="AC156" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD156" s="13" t="str">
@@ -50357,11 +49397,11 @@
         <v/>
       </c>
       <c r="AG156" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH156" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI156" s="13" t="str">
@@ -50435,18 +49475,11 @@
         <v>39</v>
       </c>
       <c r="R157" s="9" t="str">
-        <f>IF(
-  AND(
-    $A157&lt;&gt;"",
-    COUNTIF(C:C,$A157)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S157" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T157" s="13" t="str">
@@ -50569,7 +49602,7 @@
         <v>200</v>
       </c>
       <c r="AC157" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD157" s="13" t="str">
@@ -50603,11 +49636,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\UserDefHotKey2.bat（ホットキー）.lnk</v>
       </c>
       <c r="AG157" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH157" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI157" s="13" t="str">
@@ -50681,14 +49714,7 @@
         <v>1498</v>
       </c>
       <c r="R158" s="9" t="str">
-        <f>IF(
-  AND(
-    $A158&lt;&gt;"",
-    COUNTIF(C:C,$A158)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S158" s="9" t="str">
@@ -50947,18 +49973,11 @@
         <v>935</v>
       </c>
       <c r="R159" s="9" t="str">
-        <f>IF(
-  AND(
-    $A159&lt;&gt;"",
-    COUNTIF(C:C,$A159)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S159" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T159" s="13" t="str">
@@ -51081,7 +50100,7 @@
         <v>200</v>
       </c>
       <c r="AC159" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD159" s="13" t="str">
@@ -51115,11 +50134,11 @@
         <v/>
       </c>
       <c r="AG159" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH159" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI159" s="13" t="str">
@@ -51193,18 +50212,11 @@
         <v>935</v>
       </c>
       <c r="R160" s="9" t="str">
-        <f>IF(
-  AND(
-    $A160&lt;&gt;"",
-    COUNTIF(C:C,$A160)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S160" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T160" s="13" t="str">
@@ -51327,7 +50339,7 @@
         <v>200</v>
       </c>
       <c r="AC160" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD160" s="13" t="str">
@@ -51361,11 +50373,11 @@
         <v/>
       </c>
       <c r="AG160" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH160" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI160" s="13" t="str">
@@ -51439,18 +50451,11 @@
         <v>935</v>
       </c>
       <c r="R161" s="9" t="str">
-        <f>IF(
-  AND(
-    $A161&lt;&gt;"",
-    COUNTIF(C:C,$A161)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S161" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T161" s="13" t="str">
@@ -51573,7 +50578,7 @@
         <v>200</v>
       </c>
       <c r="AC161" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD161" s="13" t="str">
@@ -51607,11 +50612,11 @@
         <v/>
       </c>
       <c r="AG161" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH161" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI161" s="13" t="str">
@@ -51685,18 +50690,11 @@
         <v>935</v>
       </c>
       <c r="R162" s="9" t="str">
-        <f>IF(
-  AND(
-    $A162&lt;&gt;"",
-    COUNTIF(C:C,$A162)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S162" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T162" s="13" t="str">
@@ -51819,7 +50817,7 @@
         <v>200</v>
       </c>
       <c r="AC162" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD162" s="13" t="str">
@@ -51853,11 +50851,11 @@
         <v/>
       </c>
       <c r="AG162" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH162" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI162" s="13" t="str">
@@ -51931,18 +50929,11 @@
         <v>935</v>
       </c>
       <c r="R163" s="9" t="str">
-        <f>IF(
-  AND(
-    $A163&lt;&gt;"",
-    COUNTIF(C:C,$A163)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S163" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T163" s="13" t="str">
@@ -52065,7 +51056,7 @@
         <v>200</v>
       </c>
       <c r="AC163" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD163" s="13" t="str">
@@ -52099,11 +51090,11 @@
         <v/>
       </c>
       <c r="AG163" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH163" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI163" s="13" t="str">
@@ -52177,18 +51168,11 @@
         <v>935</v>
       </c>
       <c r="R164" s="9" t="str">
-        <f>IF(
-  AND(
-    $A164&lt;&gt;"",
-    COUNTIF(C:C,$A164)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S164" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T164" s="13" t="str">
@@ -52311,7 +51295,7 @@
         <v>200</v>
       </c>
       <c r="AC164" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD164" s="13" t="str">
@@ -52345,11 +51329,11 @@
         <v/>
       </c>
       <c r="AG164" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH164" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI164" s="13" t="str">
@@ -52423,18 +51407,11 @@
         <v>935</v>
       </c>
       <c r="R165" s="9" t="str">
-        <f>IF(
-  AND(
-    $A165&lt;&gt;"",
-    COUNTIF(C:C,$A165)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S165" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T165" s="13" t="str">
@@ -52557,7 +51534,7 @@
         <v>200</v>
       </c>
       <c r="AC165" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD165" s="13" t="str">
@@ -52591,11 +51568,11 @@
         <v/>
       </c>
       <c r="AG165" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH165" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI165" s="13" t="str">
@@ -52669,18 +51646,11 @@
         <v>935</v>
       </c>
       <c r="R166" s="9" t="str">
-        <f>IF(
-  AND(
-    $A166&lt;&gt;"",
-    COUNTIF(C:C,$A166)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S166" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T166" s="13" t="str">
@@ -52803,7 +51773,7 @@
         <v>200</v>
       </c>
       <c r="AC166" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD166" s="13" t="str">
@@ -52837,11 +51807,11 @@
         <v/>
       </c>
       <c r="AG166" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH166" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI166" s="13" t="str">
@@ -52915,18 +51885,11 @@
         <v>935</v>
       </c>
       <c r="R167" s="9" t="str">
-        <f>IF(
-  AND(
-    $A167&lt;&gt;"",
-    COUNTIF(C:C,$A167)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S167" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T167" s="13" t="str">
@@ -53049,7 +52012,7 @@
         <v>200</v>
       </c>
       <c r="AC167" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD167" s="13" t="str">
@@ -53083,11 +52046,11 @@
         <v/>
       </c>
       <c r="AG167" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH167" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI167" s="13" t="str">
@@ -53161,18 +52124,11 @@
         <v>935</v>
       </c>
       <c r="R168" s="9" t="str">
-        <f>IF(
-  AND(
-    $A168&lt;&gt;"",
-    COUNTIF(C:C,$A168)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S168" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T168" s="13" t="str">
@@ -53295,7 +52251,7 @@
         <v>200</v>
       </c>
       <c r="AC168" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD168" s="13" t="str">
@@ -53329,11 +52285,11 @@
         <v/>
       </c>
       <c r="AG168" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH168" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI168" s="13" t="str">
@@ -53407,18 +52363,11 @@
         <v>935</v>
       </c>
       <c r="R169" s="9" t="str">
-        <f>IF(
-  AND(
-    $A169&lt;&gt;"",
-    COUNTIF(C:C,$A169)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S169" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T169" s="13" t="str">
@@ -53541,7 +52490,7 @@
         <v>200</v>
       </c>
       <c r="AC169" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD169" s="13" t="str">
@@ -53575,11 +52524,11 @@
         <v/>
       </c>
       <c r="AG169" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH169" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI169" s="13" t="str">
@@ -53653,18 +52602,11 @@
         <v>935</v>
       </c>
       <c r="R170" s="9" t="str">
-        <f>IF(
-  AND(
-    $A170&lt;&gt;"",
-    COUNTIF(C:C,$A170)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S170" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T170" s="13" t="str">
@@ -53787,7 +52729,7 @@
         <v>200</v>
       </c>
       <c r="AC170" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD170" s="13" t="str">
@@ -53821,11 +52763,11 @@
         <v/>
       </c>
       <c r="AG170" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH170" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI170" s="13" t="str">
@@ -53899,18 +52841,11 @@
         <v>935</v>
       </c>
       <c r="R171" s="9" t="str">
-        <f>IF(
-  AND(
-    $A171&lt;&gt;"",
-    COUNTIF(C:C,$A171)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S171" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T171" s="13" t="str">
@@ -54033,7 +52968,7 @@
         <v>200</v>
       </c>
       <c r="AC171" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD171" s="13" t="str">
@@ -54067,11 +53002,11 @@
         <v/>
       </c>
       <c r="AG171" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH171" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI171" s="13" t="str">
@@ -54145,18 +53080,11 @@
         <v>935</v>
       </c>
       <c r="R172" s="9" t="str">
-        <f>IF(
-  AND(
-    $A172&lt;&gt;"",
-    COUNTIF(C:C,$A172)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S172" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T172" s="13" t="str">
@@ -54279,7 +53207,7 @@
         <v>200</v>
       </c>
       <c r="AC172" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD172" s="13" t="str">
@@ -54313,11 +53241,11 @@
         <v/>
       </c>
       <c r="AG172" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH172" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI172" s="13" t="str">
@@ -54391,18 +53319,11 @@
         <v>935</v>
       </c>
       <c r="R173" s="9" t="str">
-        <f>IF(
-  AND(
-    $A173&lt;&gt;"",
-    COUNTIF(C:C,$A173)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S173" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T173" s="13" t="str">
@@ -54525,7 +53446,7 @@
         <v>200</v>
       </c>
       <c r="AC173" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD173" s="13" t="str">
@@ -54559,11 +53480,11 @@
         <v/>
       </c>
       <c r="AG173" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH173" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI173" s="13" t="str">
@@ -54637,18 +53558,11 @@
         <v>935</v>
       </c>
       <c r="R174" s="9" t="str">
-        <f>IF(
-  AND(
-    $A174&lt;&gt;"",
-    COUNTIF(C:C,$A174)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S174" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T174" s="13" t="str">
@@ -54771,7 +53685,7 @@
         <v>200</v>
       </c>
       <c r="AC174" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD174" s="13" t="str">
@@ -54805,11 +53719,11 @@
         <v/>
       </c>
       <c r="AG174" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH174" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI174" s="13" t="str">
@@ -54883,18 +53797,11 @@
         <v>935</v>
       </c>
       <c r="R175" s="9" t="str">
-        <f>IF(
-  AND(
-    $A175&lt;&gt;"",
-    COUNTIF(C:C,$A175)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S175" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T175" s="13" t="str">
@@ -55017,7 +53924,7 @@
         <v>200</v>
       </c>
       <c r="AC175" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD175" s="13" t="str">
@@ -55051,11 +53958,11 @@
         <v/>
       </c>
       <c r="AG175" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH175" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI175" s="13" t="str">
@@ -55129,18 +54036,11 @@
         <v>935</v>
       </c>
       <c r="R176" s="9" t="str">
-        <f>IF(
-  AND(
-    $A176&lt;&gt;"",
-    COUNTIF(C:C,$A176)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S176" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T176" s="13" t="str">
@@ -55263,7 +54163,7 @@
         <v>200</v>
       </c>
       <c r="AC176" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD176" s="13" t="str">
@@ -55297,11 +54197,11 @@
         <v/>
       </c>
       <c r="AG176" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH176" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI176" s="13" t="str">
@@ -55375,18 +54275,11 @@
         <v>935</v>
       </c>
       <c r="R177" s="9" t="str">
-        <f>IF(
-  AND(
-    $A177&lt;&gt;"",
-    COUNTIF(C:C,$A177)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S177" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T177" s="13" t="str">
@@ -55509,7 +54402,7 @@
         <v>200</v>
       </c>
       <c r="AC177" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD177" s="13" t="str">
@@ -55543,11 +54436,11 @@
         <v/>
       </c>
       <c r="AG177" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH177" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI177" s="13" t="str">
@@ -55621,18 +54514,11 @@
         <v>935</v>
       </c>
       <c r="R178" s="9" t="str">
-        <f>IF(
-  AND(
-    $A178&lt;&gt;"",
-    COUNTIF(C:C,$A178)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S178" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T178" s="13" t="str">
@@ -55755,7 +54641,7 @@
         <v>200</v>
       </c>
       <c r="AC178" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD178" s="13" t="str">
@@ -55789,11 +54675,11 @@
         <v/>
       </c>
       <c r="AG178" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH178" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI178" s="13" t="str">
@@ -55867,18 +54753,11 @@
         <v>935</v>
       </c>
       <c r="R179" s="9" t="str">
-        <f>IF(
-  AND(
-    $A179&lt;&gt;"",
-    COUNTIF(C:C,$A179)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S179" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T179" s="13" t="str">
@@ -56001,7 +54880,7 @@
         <v>200</v>
       </c>
       <c r="AC179" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD179" s="13" t="str">
@@ -56035,11 +54914,11 @@
         <v/>
       </c>
       <c r="AG179" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH179" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI179" s="13" t="str">
@@ -56113,18 +54992,11 @@
         <v>935</v>
       </c>
       <c r="R180" s="9" t="str">
-        <f>IF(
-  AND(
-    $A180&lt;&gt;"",
-    COUNTIF(C:C,$A180)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S180" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T180" s="13" t="str">
@@ -56247,7 +55119,7 @@
         <v>200</v>
       </c>
       <c r="AC180" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD180" s="13" t="str">
@@ -56281,11 +55153,11 @@
         <v/>
       </c>
       <c r="AG180" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH180" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI180" s="13" t="str">
@@ -56359,18 +55231,11 @@
         <v>935</v>
       </c>
       <c r="R181" s="9" t="str">
-        <f>IF(
-  AND(
-    $A181&lt;&gt;"",
-    COUNTIF(C:C,$A181)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S181" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T181" s="13" t="str">
@@ -56493,7 +55358,7 @@
         <v>200</v>
       </c>
       <c r="AC181" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD181" s="13" t="str">
@@ -56527,11 +55392,11 @@
         <v/>
       </c>
       <c r="AG181" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH181" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI181" s="13" t="str">
@@ -56605,18 +55470,11 @@
         <v>935</v>
       </c>
       <c r="R182" s="9" t="str">
-        <f>IF(
-  AND(
-    $A182&lt;&gt;"",
-    COUNTIF(C:C,$A182)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S182" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T182" s="13" t="str">
@@ -56739,7 +55597,7 @@
         <v>200</v>
       </c>
       <c r="AC182" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD182" s="13" t="str">
@@ -56773,11 +55631,11 @@
         <v/>
       </c>
       <c r="AG182" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH182" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI182" s="13" t="str">
@@ -56851,18 +55709,11 @@
         <v>935</v>
       </c>
       <c r="R183" s="9" t="str">
-        <f>IF(
-  AND(
-    $A183&lt;&gt;"",
-    COUNTIF(C:C,$A183)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S183" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T183" s="13" t="str">
@@ -56985,7 +55836,7 @@
         <v>200</v>
       </c>
       <c r="AC183" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD183" s="13" t="str">
@@ -57019,11 +55870,11 @@
         <v/>
       </c>
       <c r="AG183" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH183" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI183" s="13" t="str">
@@ -57097,18 +55948,11 @@
         <v>935</v>
       </c>
       <c r="R184" s="9" t="str">
-        <f>IF(
-  AND(
-    $A184&lt;&gt;"",
-    COUNTIF(C:C,$A184)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S184" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T184" s="13" t="str">
@@ -57231,7 +56075,7 @@
         <v>200</v>
       </c>
       <c r="AC184" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD184" s="13" t="str">
@@ -57265,11 +56109,11 @@
         <v/>
       </c>
       <c r="AG184" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH184" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI184" s="13" t="str">
@@ -57343,18 +56187,11 @@
         <v>935</v>
       </c>
       <c r="R185" s="9" t="str">
-        <f>IF(
-  AND(
-    $A185&lt;&gt;"",
-    COUNTIF(C:C,$A185)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S185" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T185" s="13" t="str">
@@ -57477,7 +56314,7 @@
         <v>200</v>
       </c>
       <c r="AC185" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD185" s="13" t="str">
@@ -57511,11 +56348,11 @@
         <v/>
       </c>
       <c r="AG185" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH185" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI185" s="13" t="str">
@@ -57589,18 +56426,11 @@
         <v>935</v>
       </c>
       <c r="R186" s="9" t="str">
-        <f>IF(
-  AND(
-    $A186&lt;&gt;"",
-    COUNTIF(C:C,$A186)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S186" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T186" s="13" t="str">
@@ -57723,7 +56553,7 @@
         <v>200</v>
       </c>
       <c r="AC186" s="20" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD186" s="13" t="str">
@@ -57757,11 +56587,11 @@
         <v/>
       </c>
       <c r="AG186" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH186" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AI186" s="13" t="str">
@@ -57835,18 +56665,11 @@
         <v>935</v>
       </c>
       <c r="R187" s="9" t="str">
-        <f>IF(
-  AND(
-    $A187&lt;&gt;"",
-    COUNTIF(C:C,$A187)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S187" s="9" t="str">
-        <f t="shared" ref="S187:S225" si="28">IF(
+        <f t="shared" ref="S187:S225" si="31">IF(
   OR(
     $H187="",
     $H187="-",
@@ -57977,7 +56800,7 @@
         <v>200</v>
       </c>
       <c r="AC187" s="20" t="str">
-        <f t="shared" ref="AC187:AC225" si="29">IF(AND($M187&lt;&gt;"",$M187&lt;&gt;"-")," (&amp;"&amp;$M187&amp;")","")</f>
+        <f t="shared" ref="AC187:AC225" si="32">IF(AND($M187&lt;&gt;"",$M187&lt;&gt;"-")," (&amp;"&amp;$M187&amp;")","")</f>
         <v/>
       </c>
       <c r="AD187" s="13" t="str">
@@ -58011,7 +56834,7 @@
         <v/>
       </c>
       <c r="AG187" s="13" t="str">
-        <f t="shared" ref="AG187:AG225" si="30">IF(
+        <f t="shared" ref="AG187:AG225" si="33">IF(
   AND($A187&lt;&gt;"",$O187&lt;&gt;"-",$O187&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O187&amp;""" /tr """&amp;$C187&amp;""" /sc daily /st "&amp;$P187&amp;" /rl highest"
@@ -58021,7 +56844,7 @@
         <v/>
       </c>
       <c r="AH187" s="13" t="str">
-        <f t="shared" ref="AH187:AH225" si="31">IF(
+        <f t="shared" ref="AH187:AH225" si="34">IF(
   AND($A187&lt;&gt;"",$O187&lt;&gt;"-",$O187&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O187&amp;""""
@@ -58101,18 +56924,11 @@
         <v>935</v>
       </c>
       <c r="R188" s="9" t="str">
-        <f>IF(
-  AND(
-    $A188&lt;&gt;"",
-    COUNTIF(C:C,$A188)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S188" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T188" s="13" t="str">
@@ -58235,7 +57051,7 @@
         <v>200</v>
       </c>
       <c r="AC188" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;D)</v>
       </c>
       <c r="AD188" s="13" t="str">
@@ -58269,11 +57085,11 @@
         <v/>
       </c>
       <c r="AG188" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH188" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI188" s="13" t="str">
@@ -58347,18 +57163,11 @@
         <v>935</v>
       </c>
       <c r="R189" s="9" t="str">
-        <f>IF(
-  AND(
-    $A189&lt;&gt;"",
-    COUNTIF(C:C,$A189)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S189" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T189" s="13" t="str">
@@ -58481,7 +57290,7 @@
         <v>200</v>
       </c>
       <c r="AC189" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD189" s="13" t="str">
@@ -58515,11 +57324,11 @@
         <v/>
       </c>
       <c r="AG189" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH189" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI189" s="13" t="str">
@@ -58593,18 +57402,11 @@
         <v>935</v>
       </c>
       <c r="R190" s="9" t="str">
-        <f>IF(
-  AND(
-    $A190&lt;&gt;"",
-    COUNTIF(C:C,$A190)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S190" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T190" s="13" t="str">
@@ -58727,7 +57529,7 @@
         <v>200</v>
       </c>
       <c r="AC190" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD190" s="13" t="str">
@@ -58761,11 +57563,11 @@
         <v/>
       </c>
       <c r="AG190" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH190" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI190" s="13" t="str">
@@ -58839,18 +57641,11 @@
         <v>935</v>
       </c>
       <c r="R191" s="9" t="str">
-        <f>IF(
-  AND(
-    $A191&lt;&gt;"",
-    COUNTIF(C:C,$A191)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S191" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T191" s="13" t="str">
@@ -58973,7 +57768,7 @@
         <v>200</v>
       </c>
       <c r="AC191" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;U)</v>
       </c>
       <c r="AD191" s="13" t="str">
@@ -59007,11 +57802,11 @@
         <v/>
       </c>
       <c r="AG191" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH191" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI191" s="13" t="str">
@@ -59085,18 +57880,11 @@
         <v>935</v>
       </c>
       <c r="R192" s="9" t="str">
-        <f>IF(
-  AND(
-    $A192&lt;&gt;"",
-    COUNTIF(C:C,$A192)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S192" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T192" s="13" t="str">
@@ -59219,7 +58007,7 @@
         <v>200</v>
       </c>
       <c r="AC192" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;Z)</v>
       </c>
       <c r="AD192" s="13" t="str">
@@ -59253,11 +58041,11 @@
         <v/>
       </c>
       <c r="AG192" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH192" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI192" s="13" t="str">
@@ -59331,18 +58119,11 @@
         <v>935</v>
       </c>
       <c r="R193" s="9" t="str">
-        <f>IF(
-  AND(
-    $A193&lt;&gt;"",
-    COUNTIF(C:C,$A193)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S193" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T193" s="13" t="str">
@@ -59465,7 +58246,7 @@
         <v>200</v>
       </c>
       <c r="AC193" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD193" s="13" t="str">
@@ -59499,11 +58280,11 @@
         <v/>
       </c>
       <c r="AG193" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH193" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI193" s="13" t="str">
@@ -59577,18 +58358,11 @@
         <v>935</v>
       </c>
       <c r="R194" s="9" t="str">
-        <f>IF(
-  AND(
-    $A194&lt;&gt;"",
-    COUNTIF(C:C,$A194)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S194" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T194" s="13" t="str">
@@ -59711,7 +58485,7 @@
         <v>200</v>
       </c>
       <c r="AC194" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD194" s="13" t="str">
@@ -59745,11 +58519,11 @@
         <v/>
       </c>
       <c r="AG194" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH194" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI194" s="13" t="str">
@@ -59823,18 +58597,11 @@
         <v>935</v>
       </c>
       <c r="R195" s="9" t="str">
-        <f>IF(
-  AND(
-    $A195&lt;&gt;"",
-    COUNTIF(C:C,$A195)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S195" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T195" s="13" t="str">
@@ -59957,7 +58724,7 @@
         <v>200</v>
       </c>
       <c r="AC195" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD195" s="13" t="str">
@@ -59991,11 +58758,11 @@
         <v/>
       </c>
       <c r="AG195" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH195" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI195" s="13" t="str">
@@ -60069,18 +58836,11 @@
         <v>935</v>
       </c>
       <c r="R196" s="9" t="str">
-        <f>IF(
-  AND(
-    $A196&lt;&gt;"",
-    COUNTIF(C:C,$A196)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S196" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T196" s="13" t="str">
@@ -60203,7 +58963,7 @@
         <v>200</v>
       </c>
       <c r="AC196" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD196" s="13" t="str">
@@ -60237,11 +58997,11 @@
         <v/>
       </c>
       <c r="AG196" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH196" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI196" s="13" t="str">
@@ -60315,18 +59075,11 @@
         <v>39</v>
       </c>
       <c r="R197" s="9" t="str">
-        <f>IF(
-  AND(
-    $A197&lt;&gt;"",
-    COUNTIF(C:C,$A197)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S197" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T197" s="13" t="str">
@@ -60449,7 +59202,7 @@
         <v>200</v>
       </c>
       <c r="AC197" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD197" s="13" t="str">
@@ -60483,11 +59236,11 @@
         <v/>
       </c>
       <c r="AG197" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH197" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI197" s="13" t="str">
@@ -60561,18 +59314,11 @@
         <v>935</v>
       </c>
       <c r="R198" s="9" t="str">
-        <f>IF(
-  AND(
-    $A198&lt;&gt;"",
-    COUNTIF(C:C,$A198)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S198" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T198" s="13" t="str">
@@ -60695,7 +59441,7 @@
         <v>200</v>
       </c>
       <c r="AC198" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD198" s="13" t="str">
@@ -60729,11 +59475,11 @@
         <v/>
       </c>
       <c r="AG198" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH198" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI198" s="13" t="str">
@@ -60807,18 +59553,11 @@
         <v>935</v>
       </c>
       <c r="R199" s="9" t="str">
-        <f>IF(
-  AND(
-    $A199&lt;&gt;"",
-    COUNTIF(C:C,$A199)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S199" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T199" s="13" t="str">
@@ -60941,7 +59680,7 @@
         <v>200</v>
       </c>
       <c r="AC199" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD199" s="13" t="str">
@@ -60975,11 +59714,11 @@
         <v/>
       </c>
       <c r="AG199" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH199" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI199" s="13" t="str">
@@ -61053,18 +59792,11 @@
         <v>935</v>
       </c>
       <c r="R200" s="9" t="str">
-        <f>IF(
-  AND(
-    $A200&lt;&gt;"",
-    COUNTIF(C:C,$A200)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S200" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T200" s="13" t="str">
@@ -61187,7 +59919,7 @@
         <v>200</v>
       </c>
       <c r="AC200" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD200" s="13" t="str">
@@ -61221,11 +59953,11 @@
         <v/>
       </c>
       <c r="AG200" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH200" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI200" s="13" t="str">
@@ -61299,18 +60031,11 @@
         <v>935</v>
       </c>
       <c r="R201" s="9" t="str">
-        <f>IF(
-  AND(
-    $A201&lt;&gt;"",
-    COUNTIF(C:C,$A201)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S201" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T201" s="13" t="str">
@@ -61433,7 +60158,7 @@
         <v>200</v>
       </c>
       <c r="AC201" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD201" s="13" t="str">
@@ -61467,11 +60192,11 @@
         <v/>
       </c>
       <c r="AG201" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH201" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI201" s="13" t="str">
@@ -61545,18 +60270,11 @@
         <v>935</v>
       </c>
       <c r="R202" s="9" t="str">
-        <f>IF(
-  AND(
-    $A202&lt;&gt;"",
-    COUNTIF(C:C,$A202)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S202" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T202" s="13" t="str">
@@ -61679,7 +60397,7 @@
         <v>200</v>
       </c>
       <c r="AC202" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD202" s="13" t="str">
@@ -61713,11 +60431,11 @@
         <v/>
       </c>
       <c r="AG202" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH202" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI202" s="13" t="str">
@@ -61791,7 +60509,7 @@
         <v>935</v>
       </c>
       <c r="R203" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R203:R226" si="35">IF(
   AND(
     $A203&lt;&gt;"",
     COUNTIF(C:C,$A203)&gt;1
@@ -61802,7 +60520,7 @@
         <v/>
       </c>
       <c r="S203" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T203" s="13" t="str">
@@ -61925,7 +60643,7 @@
         <v>200</v>
       </c>
       <c r="AC203" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD203" s="13" t="str">
@@ -61959,11 +60677,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\XF_BackupIniToTabbak.bat（X-Finder.iniタブバックアップ）.lnk</v>
       </c>
       <c r="AG203" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH203" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI203" s="13" t="str">
@@ -62037,14 +60755,7 @@
         <v>39</v>
       </c>
       <c r="R204" s="9" t="str">
-        <f>IF(
-  AND(
-    $A204&lt;&gt;"",
-    COUNTIF(C:C,$A204)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S204" s="9" t="str">
@@ -62303,18 +61014,11 @@
         <v>935</v>
       </c>
       <c r="R205" s="9" t="str">
-        <f>IF(
-  AND(
-    $A205&lt;&gt;"",
-    COUNTIF(C:C,$A205)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S205" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T205" s="13" t="str">
@@ -62437,7 +61141,7 @@
         <v>200</v>
       </c>
       <c r="AC205" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD205" s="13" t="str">
@@ -62471,11 +61175,11 @@
         <v/>
       </c>
       <c r="AG205" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH205" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI205" s="13" t="str">
@@ -62549,18 +61253,11 @@
         <v>935</v>
       </c>
       <c r="R206" s="9" t="str">
-        <f>IF(
-  AND(
-    $A206&lt;&gt;"",
-    COUNTIF(C:C,$A206)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S206" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T206" s="13" t="str">
@@ -62683,7 +61380,7 @@
         <v>200</v>
       </c>
       <c r="AC206" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD206" s="13" t="str">
@@ -62717,11 +61414,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\ScheduledBackup.bat（定期ファイルバックアップ）.lnk</v>
       </c>
       <c r="AG206" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH206" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI206" s="13" t="str">
@@ -62795,18 +61492,11 @@
         <v>935</v>
       </c>
       <c r="R207" s="9" t="str">
-        <f>IF(
-  AND(
-    $A207&lt;&gt;"",
-    COUNTIF(C:C,$A207)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S207" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T207" s="13" t="str">
@@ -62929,7 +61619,7 @@
         <v>200</v>
       </c>
       <c r="AC207" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD207" s="13" t="str">
@@ -62963,11 +61653,11 @@
         <v/>
       </c>
       <c r="AG207" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH207" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI207" s="13" t="str">
@@ -63041,18 +61731,11 @@
         <v>935</v>
       </c>
       <c r="R208" s="9" t="str">
-        <f>IF(
-  AND(
-    $A208&lt;&gt;"",
-    COUNTIF(C:C,$A208)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S208" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T208" s="13" t="str">
@@ -63175,7 +61858,7 @@
         <v>200</v>
       </c>
       <c r="AC208" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD208" s="13" t="str">
@@ -63209,11 +61892,11 @@
         <v/>
       </c>
       <c r="AG208" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH208" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI208" s="13" t="str">
@@ -63287,14 +61970,7 @@
         <v>39</v>
       </c>
       <c r="R209" s="9" t="str">
-        <f>IF(
-  AND(
-    $A209&lt;&gt;"",
-    COUNTIF(C:C,$A209)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S209" s="9" t="str">
@@ -63553,18 +62229,11 @@
         <v>935</v>
       </c>
       <c r="R210" s="9" t="str">
-        <f>IF(
-  AND(
-    $A210&lt;&gt;"",
-    COUNTIF(C:C,$A210)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S210" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T210" s="13" t="str">
@@ -63687,7 +62356,7 @@
         <v>200</v>
       </c>
       <c r="AC210" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD210" s="13" t="str">
@@ -63721,11 +62390,11 @@
         <v/>
       </c>
       <c r="AG210" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH210" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI210" s="13" t="str">
@@ -63799,14 +62468,7 @@
         <v>1446</v>
       </c>
       <c r="R211" s="9" t="str">
-        <f>IF(
-  AND(
-    $A211&lt;&gt;"",
-    COUNTIF(C:C,$A211)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S211" s="9" t="str">
@@ -64065,18 +62727,11 @@
         <v>934</v>
       </c>
       <c r="R212" s="9" t="str">
-        <f>IF(
-  AND(
-    $A212&lt;&gt;"",
-    COUNTIF(C:C,$A212)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S212" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T212" s="13" t="str">
@@ -64199,7 +62854,7 @@
         <v>200</v>
       </c>
       <c r="AC212" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v xml:space="preserve"> (&amp;R)</v>
       </c>
       <c r="AD212" s="13" t="str">
@@ -64233,11 +62888,11 @@
         <v/>
       </c>
       <c r="AG212" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH212" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI212" s="13" t="str">
@@ -64311,18 +62966,11 @@
         <v>934</v>
       </c>
       <c r="R213" s="9" t="str">
-        <f>IF(
-  AND(
-    $A213&lt;&gt;"",
-    COUNTIF(C:C,$A213)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S213" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T213" s="13" t="str">
@@ -64445,7 +63093,7 @@
         <v>200</v>
       </c>
       <c r="AC213" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD213" s="13" t="str">
@@ -64479,11 +63127,11 @@
         <v/>
       </c>
       <c r="AG213" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH213" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI213" s="13" t="str">
@@ -64557,14 +63205,7 @@
         <v>1427</v>
       </c>
       <c r="R214" s="9" t="str">
-        <f>IF(
-  AND(
-    $A214&lt;&gt;"",
-    COUNTIF(C:C,$A214)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S214" s="9" t="str">
@@ -64823,18 +63464,11 @@
         <v>39</v>
       </c>
       <c r="R215" s="9" t="str">
-        <f>IF(
-  AND(
-    $A215&lt;&gt;"",
-    COUNTIF(C:C,$A215)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S215" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T215" s="13" t="str">
@@ -64957,7 +63591,7 @@
         <v>200</v>
       </c>
       <c r="AC215" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD215" s="13" t="str">
@@ -64991,11 +63625,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\CreateProgramList.bat（インストールプログラム一覧作成）.lnk</v>
       </c>
       <c r="AG215" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH215" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI215" s="13" t="str">
@@ -65069,18 +63703,11 @@
         <v>39</v>
       </c>
       <c r="R216" s="9" t="str">
-        <f>IF(
-  AND(
-    $A216&lt;&gt;"",
-    COUNTIF(C:C,$A216)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S216" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T216" s="13" t="str">
@@ -65203,7 +63830,7 @@
         <v>200</v>
       </c>
       <c r="AC216" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD216" s="13" t="str">
@@ -65237,11 +63864,11 @@
         <v/>
       </c>
       <c r="AG216" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH216" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI216" s="13" t="str">
@@ -65315,18 +63942,11 @@
         <v>39</v>
       </c>
       <c r="R217" s="9" t="str">
-        <f>IF(
-  AND(
-    $A217&lt;&gt;"",
-    COUNTIF(C:C,$A217)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S217" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T217" s="13" t="str">
@@ -65449,7 +64069,7 @@
         <v>200</v>
       </c>
       <c r="AC217" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD217" s="13" t="str">
@@ -65483,11 +64103,11 @@
         <v/>
       </c>
       <c r="AG217" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH217" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI217" s="13" t="str">
@@ -65561,18 +64181,11 @@
         <v>39</v>
       </c>
       <c r="R218" s="9" t="str">
-        <f>IF(
-  AND(
-    $A218&lt;&gt;"",
-    COUNTIF(C:C,$A218)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S218" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T218" s="13" t="str">
@@ -65695,7 +64308,7 @@
         <v>200</v>
       </c>
       <c r="AC218" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD218" s="13" t="str">
@@ -65729,11 +64342,11 @@
         <v/>
       </c>
       <c r="AG218" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH218" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI218" s="13" t="str">
@@ -65807,18 +64420,11 @@
         <v>39</v>
       </c>
       <c r="R219" s="9" t="str">
-        <f>IF(
-  AND(
-    $A219&lt;&gt;"",
-    COUNTIF(C:C,$A219)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S219" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T219" s="13" t="str">
@@ -65941,7 +64547,7 @@
         <v>200</v>
       </c>
       <c r="AC219" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD219" s="13" t="str">
@@ -65975,11 +64581,11 @@
         <v/>
       </c>
       <c r="AG219" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH219" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI219" s="13" t="str">
@@ -66053,18 +64659,11 @@
         <v>39</v>
       </c>
       <c r="R220" s="9" t="str">
-        <f>IF(
-  AND(
-    $A220&lt;&gt;"",
-    COUNTIF(C:C,$A220)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S220" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T220" s="13" t="str">
@@ -66187,7 +64786,7 @@
         <v>200</v>
       </c>
       <c r="AC220" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD220" s="13" t="str">
@@ -66221,11 +64820,11 @@
         <v/>
       </c>
       <c r="AG220" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>schtasks /create /tn "_scheduled_backup_root" /tr "C:\codes\bat\tools\other\BackupRoot.bat" /sc daily /st 17:56 /rl highest</v>
       </c>
       <c r="AH220" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>schtasks /delete /tn "_scheduled_backup_root"</v>
       </c>
       <c r="AI220" s="13" t="str">
@@ -66299,18 +64898,11 @@
         <v>1252</v>
       </c>
       <c r="R221" s="9" t="str">
-        <f>IF(
-  AND(
-    $A221&lt;&gt;"",
-    COUNTIF(C:C,$A221)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S221" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T221" s="13" t="str">
@@ -66433,7 +65025,7 @@
         <v>200</v>
       </c>
       <c r="AC221" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD221" s="13" t="str">
@@ -66467,11 +65059,11 @@
         <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\Startup\BackupOtherPrgSettings.bat（各種プログラム設定バックアップ）.lnk</v>
       </c>
       <c r="AG221" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH221" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI221" s="13" t="str">
@@ -66545,14 +65137,7 @@
         <v>1419</v>
       </c>
       <c r="R222" s="9" t="str">
-        <f>IF(
-  AND(
-    $A222&lt;&gt;"",
-    COUNTIF(C:C,$A222)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S222" s="9" t="str">
@@ -66811,18 +65396,11 @@
         <v>1381</v>
       </c>
       <c r="R223" s="9" t="str">
-        <f>IF(
-  AND(
-    $A223&lt;&gt;"",
-    COUNTIF(C:C,$A223)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S223" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T223" s="13" t="str">
@@ -66945,7 +65523,7 @@
         <v>200</v>
       </c>
       <c r="AC223" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD223" s="13" t="str">
@@ -66979,11 +65557,11 @@
         <v/>
       </c>
       <c r="AG223" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH223" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI223" s="13" t="str">
@@ -67005,36 +65583,63 @@
       </c>
     </row>
     <row r="224" spans="1:36">
-      <c r="A224" s="9"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="15"/>
-      <c r="E224" s="26"/>
-      <c r="F224" s="15"/>
-      <c r="G224" s="15"/>
-      <c r="H224" s="9"/>
-      <c r="I224" s="15"/>
-      <c r="J224" s="15"/>
-      <c r="K224" s="15"/>
-      <c r="L224" s="93"/>
-      <c r="M224" s="94"/>
-      <c r="N224" s="15"/>
-      <c r="O224" s="26"/>
-      <c r="P224" s="157"/>
-      <c r="Q224" s="26"/>
+      <c r="A224" s="176" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B224" s="176" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C224" s="176" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D224" s="177" t="s">
+        <v>934</v>
+      </c>
+      <c r="E224" s="178" t="s">
+        <v>934</v>
+      </c>
+      <c r="F224" s="177" t="s">
+        <v>0</v>
+      </c>
+      <c r="G224" s="177" t="s">
+        <v>0</v>
+      </c>
+      <c r="H224" s="176" t="s">
+        <v>521</v>
+      </c>
+      <c r="I224" s="177" t="s">
+        <v>934</v>
+      </c>
+      <c r="J224" s="177" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K224" s="177" t="s">
+        <v>934</v>
+      </c>
+      <c r="L224" s="179" t="s">
+        <v>934</v>
+      </c>
+      <c r="M224" s="180" t="s">
+        <v>934</v>
+      </c>
+      <c r="N224" s="177" t="s">
+        <v>934</v>
+      </c>
+      <c r="O224" s="178" t="s">
+        <v>934</v>
+      </c>
+      <c r="P224" s="181" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q224" s="178" t="s">
+        <v>934</v>
+      </c>
       <c r="R224" s="9" t="str">
-        <f>IF(
-  AND(
-    $A224&lt;&gt;"",
-    COUNTIF(C:C,$A224)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S224" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T224" s="13" t="str">
@@ -67054,7 +65659,7 @@
         <v/>
       </c>
       <c r="U224" s="9" t="str">
-        <f>IFERROR(
+        <f ca="1">IFERROR(
   VLOOKUP(
     $H224,
     shortcut設定!$F:$J,
@@ -67067,7 +65672,7 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="V224" s="13" t="str">
         <f>IF(
@@ -67091,7 +65696,7 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess\sht（時刻指定シャットダウン）.lnk" "C:\codes\vbs\tools\win\other\Shutdown.vbs" "" ""</v>
       </c>
       <c r="X224" s="14" t="str">
         <f>IF(
@@ -67099,7 +65704,7 @@
   shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J224&amp;"（"&amp;$B224&amp;"）.lnk",
   ""
 )</f>
-        <v/>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess\sht（時刻指定シャットダウン）.lnk</v>
       </c>
       <c r="Y224" s="13" t="str">
         <f>IF(
@@ -67141,7 +65746,7 @@
         <v/>
       </c>
       <c r="AB224" s="9" t="str">
-        <f>IFERROR(
+        <f ca="1">IFERROR(
   VLOOKUP(
     $H224,
     shortcut設定!$F:$J,
@@ -67154,10 +65759,10 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="AC224" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD224" s="13" t="str">
@@ -67191,11 +65796,11 @@
         <v/>
       </c>
       <c r="AG224" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH224" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI224" s="13" t="str">
@@ -67235,18 +65840,11 @@
       <c r="P225" s="157"/>
       <c r="Q225" s="26"/>
       <c r="R225" s="9" t="str">
-        <f>IF(
-  AND(
-    $A225&lt;&gt;"",
-    COUNTIF(C:C,$A225)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S225" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T225" s="13" t="str">
@@ -67369,7 +65967,7 @@
         <v/>
       </c>
       <c r="AC225" s="20" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD225" s="13" t="str">
@@ -67403,11 +66001,11 @@
         <v/>
       </c>
       <c r="AG225" s="13" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH225" s="13" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI225" s="13" t="str">
@@ -67447,18 +66045,11 @@
       <c r="P226" s="157"/>
       <c r="Q226" s="26"/>
       <c r="R226" s="9" t="str">
-        <f>IF(
-  AND(
-    $A226&lt;&gt;"",
-    COUNTIF(C:C,$A226)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S226" s="9" t="str">
-        <f t="shared" ref="S226" si="32">IF(
+        <f t="shared" ref="S226" si="36">IF(
   OR(
     $H226="",
     $H226="-",
@@ -67589,7 +66180,7 @@
         <v/>
       </c>
       <c r="AC226" s="20" t="str">
-        <f t="shared" ref="AC226" si="33">IF(AND($M226&lt;&gt;"",$M226&lt;&gt;"-")," (&amp;"&amp;$M226&amp;")","")</f>
+        <f t="shared" ref="AC226" si="37">IF(AND($M226&lt;&gt;"",$M226&lt;&gt;"-")," (&amp;"&amp;$M226&amp;")","")</f>
         <v/>
       </c>
       <c r="AD226" s="13" t="str">
@@ -67623,7 +66214,7 @@
         <v/>
       </c>
       <c r="AG226" s="13" t="str">
-        <f t="shared" ref="AG226" si="34">IF(
+        <f t="shared" ref="AG226" si="38">IF(
   AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O226&amp;""" /tr """&amp;$C226&amp;""" /sc daily /st "&amp;$P226&amp;" /rl highest"
@@ -67633,7 +66224,7 @@
         <v/>
       </c>
       <c r="AH226" s="13" t="str">
-        <f t="shared" ref="AH226" si="35">IF(
+        <f t="shared" ref="AH226" si="39">IF(
   AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O226&amp;""""
@@ -67753,7 +66344,7 @@
         <v>935</v>
       </c>
       <c r="R229" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="R229:R234" si="40">IF(
   AND(
     $A229&lt;&gt;"",
     COUNTIF(C:C,$A229)&gt;1
@@ -67764,7 +66355,7 @@
         <v/>
       </c>
       <c r="S229" s="9" t="str">
-        <f t="shared" ref="S229:S234" si="36">IF(
+        <f t="shared" ref="S229:S234" si="41">IF(
   OR(
     $H229="",
     $H229="-",
@@ -67895,7 +66486,7 @@
         <v>153</v>
       </c>
       <c r="AC229" s="20" t="str">
-        <f t="shared" ref="AC229:AC234" si="37">IF(AND($M229&lt;&gt;"",$M229&lt;&gt;"-")," (&amp;"&amp;$M229&amp;")","")</f>
+        <f t="shared" ref="AC229:AC234" si="42">IF(AND($M229&lt;&gt;"",$M229&lt;&gt;"-")," (&amp;"&amp;$M229&amp;")","")</f>
         <v/>
       </c>
       <c r="AD229" s="13" t="str">
@@ -67929,7 +66520,7 @@
         <v/>
       </c>
       <c r="AG229" s="13" t="str">
-        <f t="shared" ref="AG229:AG234" si="38">IF(
+        <f t="shared" ref="AG229:AG234" si="43">IF(
   AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O229&amp;""" /tr """&amp;$C229&amp;""" /sc daily /st "&amp;$P229&amp;" /rl highest"
@@ -67939,7 +66530,7 @@
         <v/>
       </c>
       <c r="AH229" s="13" t="str">
-        <f t="shared" ref="AH229:AH234" si="39">IF(
+        <f t="shared" ref="AH229:AH234" si="44">IF(
   AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O229&amp;""""
@@ -68019,18 +66610,11 @@
         <v>935</v>
       </c>
       <c r="R230" s="9" t="str">
-        <f>IF(
-  AND(
-    $A230&lt;&gt;"",
-    COUNTIF(C:C,$A230)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S230" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T230" s="13" t="str">
@@ -68153,7 +66737,7 @@
         <v>161</v>
       </c>
       <c r="AC230" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD230" s="13" t="str">
@@ -68187,11 +66771,11 @@
         <v/>
       </c>
       <c r="AG230" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH230" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI230" s="13" t="str">
@@ -68265,18 +66849,11 @@
         <v>39</v>
       </c>
       <c r="R231" s="9" t="str">
-        <f>IF(
-  AND(
-    $A231&lt;&gt;"",
-    COUNTIF(C:C,$A231)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S231" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T231" s="13" t="str">
@@ -68399,7 +66976,7 @@
         <v>172</v>
       </c>
       <c r="AC231" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD231" s="13" t="str">
@@ -68433,11 +67010,11 @@
         <v/>
       </c>
       <c r="AG231" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH231" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI231" s="13" t="str">
@@ -68511,18 +67088,11 @@
         <v>935</v>
       </c>
       <c r="R232" s="9" t="str">
-        <f>IF(
-  AND(
-    $A232&lt;&gt;"",
-    COUNTIF(C:C,$A232)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S232" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T232" s="13" t="str">
@@ -68645,7 +67215,7 @@
         <v>143</v>
       </c>
       <c r="AC232" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD232" s="13" t="str">
@@ -68679,11 +67249,11 @@
         <v/>
       </c>
       <c r="AG232" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH232" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI232" s="13" t="str">
@@ -68757,18 +67327,11 @@
         <v>935</v>
       </c>
       <c r="R233" s="9" t="str">
-        <f>IF(
-  AND(
-    $A233&lt;&gt;"",
-    COUNTIF(C:C,$A233)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S233" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T233" s="13" t="str">
@@ -68891,7 +67454,7 @@
         <v>162</v>
       </c>
       <c r="AC233" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD233" s="13" t="str">
@@ -68925,11 +67488,11 @@
         <v/>
       </c>
       <c r="AG233" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH233" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI233" s="13" t="str">
@@ -69003,18 +67566,11 @@
         <v>39</v>
       </c>
       <c r="R234" s="9" t="str">
-        <f>IF(
-  AND(
-    $A234&lt;&gt;"",
-    COUNTIF(C:C,$A234)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="S234" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T234" s="13" t="str">
@@ -69137,7 +67693,7 @@
         <v>161</v>
       </c>
       <c r="AC234" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD234" s="13" t="str">
@@ -69171,11 +67727,11 @@
         <v/>
       </c>
       <c r="AG234" s="13" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH234" s="13" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AI234" s="13" t="str">
@@ -69199,7 +67755,7 @@
   </sheetData>
   <autoFilter ref="A9:AJ227" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H229:H234 H224:H226 H11:H223" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>カテゴリ</formula1>
     </dataValidation>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://robocip20-my.sharepoint.com/personal/endo_tatsuya_robocip_or_jp/Documents/ドキュメント/_repos/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D85E81-9CAE-40EC-909B-DB71E4614BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{62D85E81-9CAE-40EC-909B-DB71E4614BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B0B0EE-EB24-47D4-99F8-EB30F689D5A5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="42720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="42720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
@@ -33,21 +33,32 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">linux環境構築!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">shortcut!$A$9:$AJ$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">symlink!$A$11:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">セットアップ事項!$A$2:$M$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">linux環境構築!$A$6:$H$116</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$227</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">shortcut!$A$8:$AI$228</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">shortcut設定!$A$1:$O$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">symlink!$A$10:$L$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">セットアップ事項!$A$1:$H$83</definedName>
     <definedName name="カテゴリ" localSheetId="7">[1]shortcut設定!$F$13:$F$37</definedName>
     <definedName name="カテゴリ">shortcut設定!$F$13:$F$37</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -775,14 +786,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -797,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6478" uniqueCount="1576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6496" uniqueCount="1580">
   <si>
     <t>○</t>
   </si>
@@ -8299,6 +8310,25 @@
   </si>
   <si>
     <t>sht</t>
+  </si>
+  <si>
+    <t>ScheduleClockOut.vbs</t>
+  </si>
+  <si>
+    <t>遅延退勤</t>
+    <rPh sb="0" eb="2">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイキン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>C:\codes\vbs\tools\win\other\ScheduleClockOut.vbs</t>
+  </si>
+  <si>
+    <t>sco</t>
   </si>
 </sst>
 </file>
@@ -8864,7 +8894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9393,24 +9423,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
@@ -9664,12 +9676,10 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="setting"/>
-      <sheetName val="MyExcelAddin"/>
     </sheetNames>
     <definedNames>
       <definedName name="getdirpath"/>
@@ -9677,16 +9687,19 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9724,7 +9737,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9830,7 +9843,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9972,7 +9985,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -13748,7 +13761,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AN234"/>
+  <dimension ref="A1:AN235"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="11.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="42" style="7" bestFit="1" customWidth="1"/>
@@ -15300,9 +15313,9 @@
       <c r="D16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="26" t="e" cm="1">
-        <f t="array" aca="1" ref="E16" ca="1">[2]!getdirpath(C16)</f>
-        <v>#NAME?</v>
+      <c r="E16" s="26" t="str" cm="1">
+        <f t="array" ref="E16">[2]!getdirpath(C16)</f>
+        <v>C:\prg_exe\AiperEditex</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>149</v>
@@ -15348,7 +15361,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T16" s="13" t="e">
+      <c r="T16" s="13" t="str">
         <f ca="1">IF(
   AND($A16&lt;&gt;"",$I16="○"),
   (
@@ -15362,7 +15375,7 @@
   ),
   ""
 )</f>
-        <v>#NAME?</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\121_Doc_Analyze" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\121_Doc_Analyze\AiperEditex（OfficeファイルGrep）.lnk" "C:\prg_exe\AiperEditex\AiperEditex.exe" "" "C:\prg_exe\AiperEditex"</v>
       </c>
       <c r="U16" s="9" t="str">
         <f ca="1">IFERROR(
@@ -31859,9 +31872,9 @@
       <c r="D85" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E85" s="26" t="e" cm="1">
-        <f t="array" aca="1" ref="E85" ca="1">[2]!getdirpath(C85)</f>
-        <v>#NAME?</v>
+      <c r="E85" s="26" t="str" cm="1">
+        <f t="array" ref="E85">[2]!getdirpath(C85)</f>
+        <v>C:\prg_exe\Rapture</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>149</v>
@@ -31907,7 +31920,7 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="T85" s="13" t="e">
+      <c r="T85" s="13" t="str">
         <f ca="1">IF(
   AND($A85&lt;&gt;"",$I85="○"),
   (
@@ -31921,7 +31934,7 @@
   ),
   ""
 )</f>
-        <v>#NAME?</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\Rapture（スクリーンショット）.lnk" "C:\prg_exe\Rapture\rapture.exe" "" "C:\prg_exe\Rapture"</v>
       </c>
       <c r="U85" s="9" t="str">
         <f ca="1">IFERROR(
@@ -56669,7 +56682,7 @@
         <v/>
       </c>
       <c r="S187" s="9" t="str">
-        <f t="shared" ref="S187:S225" si="31">IF(
+        <f t="shared" ref="S187:S226" si="31">IF(
   OR(
     $H187="",
     $H187="-",
@@ -56800,7 +56813,7 @@
         <v>200</v>
       </c>
       <c r="AC187" s="20" t="str">
-        <f t="shared" ref="AC187:AC225" si="32">IF(AND($M187&lt;&gt;"",$M187&lt;&gt;"-")," (&amp;"&amp;$M187&amp;")","")</f>
+        <f t="shared" ref="AC187:AC226" si="32">IF(AND($M187&lt;&gt;"",$M187&lt;&gt;"-")," (&amp;"&amp;$M187&amp;")","")</f>
         <v/>
       </c>
       <c r="AD187" s="13" t="str">
@@ -56834,7 +56847,7 @@
         <v/>
       </c>
       <c r="AG187" s="13" t="str">
-        <f t="shared" ref="AG187:AG225" si="33">IF(
+        <f t="shared" ref="AG187:AG226" si="33">IF(
   AND($A187&lt;&gt;"",$O187&lt;&gt;"-",$O187&lt;&gt;""),
   (
     "schtasks /create /tn """&amp;$O187&amp;""" /tr """&amp;$C187&amp;""" /sc daily /st "&amp;$P187&amp;" /rl highest"
@@ -56844,7 +56857,7 @@
         <v/>
       </c>
       <c r="AH187" s="13" t="str">
-        <f t="shared" ref="AH187:AH225" si="34">IF(
+        <f t="shared" ref="AH187:AH226" si="34">IF(
   AND($A187&lt;&gt;"",$O187&lt;&gt;"-",$O187&lt;&gt;""),
   (
     "schtasks /delete /tn """&amp;$O187&amp;""""
@@ -60509,7 +60522,7 @@
         <v>935</v>
       </c>
       <c r="R203" s="9" t="str">
-        <f t="shared" ref="R203:R226" si="35">IF(
+        <f t="shared" ref="R203:R227" si="35">IF(
   AND(
     $A203&lt;&gt;"",
     COUNTIF(C:C,$A203)&gt;1
@@ -65583,55 +65596,55 @@
       </c>
     </row>
     <row r="224" spans="1:36">
-      <c r="A224" s="176" t="s">
+      <c r="A224" s="9" t="s">
         <v>1572</v>
       </c>
-      <c r="B224" s="176" t="s">
+      <c r="B224" s="9" t="s">
         <v>1573</v>
       </c>
-      <c r="C224" s="176" t="s">
+      <c r="C224" s="9" t="s">
         <v>1574</v>
       </c>
-      <c r="D224" s="177" t="s">
+      <c r="D224" s="15" t="s">
         <v>934</v>
       </c>
-      <c r="E224" s="178" t="s">
+      <c r="E224" s="26" t="s">
         <v>934</v>
       </c>
-      <c r="F224" s="177" t="s">
+      <c r="F224" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="G224" s="177" t="s">
+      <c r="G224" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="H224" s="176" t="s">
+      <c r="H224" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="I224" s="177" t="s">
+      <c r="I224" s="15" t="s">
         <v>934</v>
       </c>
-      <c r="J224" s="177" t="s">
+      <c r="J224" s="15" t="s">
         <v>1575</v>
       </c>
-      <c r="K224" s="177" t="s">
+      <c r="K224" s="15" t="s">
         <v>934</v>
       </c>
-      <c r="L224" s="179" t="s">
+      <c r="L224" s="93" t="s">
         <v>934</v>
       </c>
-      <c r="M224" s="180" t="s">
+      <c r="M224" s="94" t="s">
         <v>934</v>
       </c>
-      <c r="N224" s="177" t="s">
+      <c r="N224" s="15" t="s">
         <v>934</v>
       </c>
-      <c r="O224" s="178" t="s">
+      <c r="O224" s="26" t="s">
         <v>934</v>
       </c>
-      <c r="P224" s="181" t="s">
+      <c r="P224" s="157" t="s">
         <v>934</v>
       </c>
-      <c r="Q224" s="178" t="s">
+      <c r="Q224" s="26" t="s">
         <v>934</v>
       </c>
       <c r="R224" s="9" t="str">
@@ -65822,23 +65835,57 @@
       </c>
     </row>
     <row r="225" spans="1:36">
-      <c r="A225" s="9"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="15"/>
-      <c r="E225" s="26"/>
-      <c r="F225" s="15"/>
-      <c r="G225" s="15"/>
-      <c r="H225" s="9"/>
-      <c r="I225" s="15"/>
-      <c r="J225" s="15"/>
-      <c r="K225" s="15"/>
-      <c r="L225" s="93"/>
-      <c r="M225" s="94"/>
-      <c r="N225" s="15"/>
-      <c r="O225" s="26"/>
-      <c r="P225" s="157"/>
-      <c r="Q225" s="26"/>
+      <c r="A225" s="9" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D225" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="E225" s="26" t="s">
+        <v>934</v>
+      </c>
+      <c r="F225" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G225" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="I225" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="J225" s="15" t="s">
+        <v>1579</v>
+      </c>
+      <c r="K225" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="L225" s="93" t="s">
+        <v>934</v>
+      </c>
+      <c r="M225" s="94" t="s">
+        <v>934</v>
+      </c>
+      <c r="N225" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="O225" s="26" t="s">
+        <v>934</v>
+      </c>
+      <c r="P225" s="157" t="s">
+        <v>934</v>
+      </c>
+      <c r="Q225" s="26" t="s">
+        <v>934</v>
+      </c>
       <c r="R225" s="9" t="str">
         <f t="shared" si="35"/>
         <v/>
@@ -65864,7 +65911,7 @@
         <v/>
       </c>
       <c r="U225" s="9" t="str">
-        <f>IFERROR(
+        <f ca="1">IFERROR(
   VLOOKUP(
     $H225,
     shortcut設定!$F:$J,
@@ -65877,7 +65924,7 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="V225" s="13" t="str">
         <f>IF(
@@ -65901,7 +65948,7 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess\sco（遅延退勤）.lnk" "C:\codes\vbs\tools\win\other\ScheduleClockOut.vbs" "" ""</v>
       </c>
       <c r="X225" s="14" t="str">
         <f>IF(
@@ -65909,7 +65956,7 @@
   shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J225&amp;"（"&amp;$B225&amp;"）.lnk",
   ""
 )</f>
-        <v/>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\$QuickAccess\sco（遅延退勤）.lnk</v>
       </c>
       <c r="Y225" s="13" t="str">
         <f>IF(
@@ -65951,7 +65998,7 @@
         <v/>
       </c>
       <c r="AB225" s="9" t="str">
-        <f>IFERROR(
+        <f ca="1">IFERROR(
   VLOOKUP(
     $H225,
     shortcut設定!$F:$J,
@@ -65964,7 +66011,7 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="AC225" s="20" t="str">
         <f t="shared" si="32"/>
@@ -66049,15 +66096,7 @@
         <v/>
       </c>
       <c r="S226" s="9" t="str">
-        <f t="shared" ref="S226" si="36">IF(
-  OR(
-    $H226="",
-    $H226="-",
-    COUNTIF(カテゴリ,$H226)&gt;0
-  ),
-  "",
-  "★NG★"
-)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T226" s="13" t="str">
@@ -66180,7 +66219,7 @@
         <v/>
       </c>
       <c r="AC226" s="20" t="str">
-        <f t="shared" ref="AC226" si="37">IF(AND($M226&lt;&gt;"",$M226&lt;&gt;"-")," (&amp;"&amp;$M226&amp;")","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD226" s="13" t="str">
@@ -66214,23 +66253,11 @@
         <v/>
       </c>
       <c r="AG226" s="13" t="str">
-        <f t="shared" ref="AG226" si="38">IF(
-  AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
-  (
-    "schtasks /create /tn """&amp;$O226&amp;""" /tr """&amp;$C226&amp;""" /sc daily /st "&amp;$P226&amp;" /rl highest"
-  ),
-  ""
-)</f>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH226" s="13" t="str">
-        <f t="shared" ref="AH226" si="39">IF(
-  AND($A226&lt;&gt;"",$O226&lt;&gt;"-",$O226&lt;&gt;""),
-  (
-    "schtasks /delete /tn """&amp;$O226&amp;""""
-  ),
-  ""
-)</f>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AI226" s="13" t="str">
@@ -66251,141 +66278,60 @@
         <v>174</v>
       </c>
     </row>
-    <row r="227" spans="1:36" ht="1.5" customHeight="1">
-      <c r="A227" s="16"/>
-      <c r="B227" s="16"/>
-      <c r="C227" s="16"/>
-      <c r="D227" s="16"/>
-      <c r="E227" s="16"/>
-      <c r="F227" s="16"/>
-      <c r="G227" s="16"/>
-      <c r="H227" s="16"/>
-      <c r="I227" s="16"/>
-      <c r="J227" s="16"/>
-      <c r="K227" s="16"/>
-      <c r="L227" s="17"/>
-      <c r="M227" s="18"/>
-      <c r="N227" s="16"/>
-      <c r="O227" s="16"/>
-      <c r="P227" s="158"/>
-      <c r="Q227" s="96"/>
-      <c r="R227" s="16"/>
-      <c r="S227" s="16"/>
-      <c r="T227" s="17"/>
-      <c r="U227" s="16"/>
-      <c r="V227" s="17"/>
-      <c r="W227" s="17"/>
-      <c r="X227" s="18"/>
-      <c r="Y227" s="17"/>
-      <c r="Z227" s="18"/>
-      <c r="AA227" s="17"/>
-      <c r="AB227" s="16"/>
-      <c r="AC227" s="90"/>
-      <c r="AD227" s="17"/>
-      <c r="AE227" s="17"/>
-      <c r="AF227" s="16"/>
-      <c r="AG227" s="17"/>
-      <c r="AH227" s="17"/>
-      <c r="AI227" s="17"/>
-      <c r="AJ227" s="91" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="229" spans="1:36">
-      <c r="A229" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>785</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D229" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E229" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F229" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="G229" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H229" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I229" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="J229" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K229" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="L229" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="M229" s="94" t="s">
-        <v>545</v>
-      </c>
-      <c r="N229" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="O229" s="26" t="s">
-        <v>1230</v>
-      </c>
-      <c r="P229" s="157" t="s">
-        <v>1230</v>
-      </c>
-      <c r="Q229" s="26" t="s">
-        <v>935</v>
-      </c>
-      <c r="R229" s="9" t="str">
-        <f t="shared" ref="R229:R234" si="40">IF(
-  AND(
-    $A229&lt;&gt;"",
-    COUNTIF(C:C,$A229)&gt;1
-  ),
-  "★NG★",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="S229" s="9" t="str">
-        <f t="shared" ref="S229:S234" si="41">IF(
+    <row r="227" spans="1:36">
+      <c r="A227" s="9"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="15"/>
+      <c r="E227" s="26"/>
+      <c r="F227" s="15"/>
+      <c r="G227" s="15"/>
+      <c r="H227" s="9"/>
+      <c r="I227" s="15"/>
+      <c r="J227" s="15"/>
+      <c r="K227" s="15"/>
+      <c r="L227" s="93"/>
+      <c r="M227" s="94"/>
+      <c r="N227" s="15"/>
+      <c r="O227" s="26"/>
+      <c r="P227" s="157"/>
+      <c r="Q227" s="26"/>
+      <c r="R227" s="9" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="S227" s="9" t="str">
+        <f t="shared" ref="S227" si="36">IF(
   OR(
-    $H229="",
-    $H229="-",
-    COUNTIF(カテゴリ,$H229)&gt;0
+    $H227="",
+    $H227="-",
+    COUNTIF(カテゴリ,$H227)&gt;0
   ),
   "",
   "★NG★"
 )</f>
         <v/>
       </c>
-      <c r="T229" s="13" t="str">
-        <f ca="1">IF(
-  AND($A229&lt;&gt;"",$I229="○"),
-  (
-    "mkdir """&amp;V229&amp;""" &amp; "
+      <c r="T227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$I227="○"),
+  (
+    "mkdir """&amp;V227&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;V229&amp;"\"&amp;$A229&amp;"（"&amp;$B229&amp;"）.lnk"""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")
-  ),
-  ""
-)</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit\iMazingConverter（HEIC→JPG変換）.lnk" "C:\prg\DigiDNA\iMazing Converter\iMazing Converter.exe" "" ""</v>
-      </c>
-      <c r="U229" s="9" t="str">
-        <f ca="1">IFERROR(
+    " """&amp;V227&amp;"\"&amp;$A227&amp;"（"&amp;$B227&amp;"）.lnk"""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="U227" s="9" t="str">
+        <f>IFERROR(
   VLOOKUP(
-    $H229,
+    $H227,
     shortcut設定!$F:$J,
     MATCH(
       "ProgramsIndex",
@@ -66396,83 +66342,83 @@
   ),
   ""
 )</f>
-        <v>153</v>
-      </c>
-      <c r="V229" s="13" t="str">
-        <f ca="1">IF(
-  AND($A229&lt;&gt;"",$I229="○"),
-  shortcut設定!$F$4&amp;"\"&amp;U229&amp;"_"&amp;H229,
-  ""
-)</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit</v>
-      </c>
-      <c r="W229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$J229&lt;&gt;"-",$J229&lt;&gt;""),
+        <v/>
+      </c>
+      <c r="V227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$I227="○"),
+  shortcut設定!$F$4&amp;"\"&amp;U227&amp;"_"&amp;H227,
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="W227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$J227&lt;&gt;"-",$J227&lt;&gt;""),
   (
     "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$X229&amp;""""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="X229" s="14" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$J229&lt;&gt;"-",$J229&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J229&amp;"（"&amp;$B229&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Y229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$K229&lt;&gt;"-",$K229&lt;&gt;""),
+    " """&amp;$X227&amp;""""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="X227" s="14" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$J227&lt;&gt;"-",$J227&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J227&amp;"（"&amp;$B227&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Y227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$K227&lt;&gt;"-",$K227&lt;&gt;""),
   (
     "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;""" &amp; "
   )&amp;(
     """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Z229&amp;""""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")&amp;
-    IF($K229="-"," """""," """&amp;$K229&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="Z229" s="14" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$K229&lt;&gt;"-",$K229&lt;&gt;""),
-  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A229&amp;"（"&amp;$B229&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AA229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$L229&lt;&gt;"-",$L229&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AD229&amp;""""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AB229" s="9" t="str">
-        <f ca="1">IFERROR(
+    " """&amp;$Z227&amp;""""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")&amp;
+    IF($K227="-"," """""," """&amp;$K227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Z227" s="14" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$K227&lt;&gt;"-",$K227&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A227&amp;"（"&amp;$B227&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AA227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$L227&lt;&gt;"-",$L227&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AD227&amp;""""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AB227" s="9" t="str">
+        <f>IFERROR(
   VLOOKUP(
-    $H229,
+    $H227,
     shortcut設定!$F:$J,
     MATCH(
       "ProgramsIndex",
@@ -66483,89 +66429,129 @@
   ),
   ""
 )</f>
-        <v>153</v>
-      </c>
-      <c r="AC229" s="20" t="str">
-        <f t="shared" ref="AC229:AC234" si="42">IF(AND($M229&lt;&gt;"",$M229&lt;&gt;"-")," (&amp;"&amp;$M229&amp;")","")</f>
-        <v/>
-      </c>
-      <c r="AD229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$L229="○"),
-  shortcut設定!$F$5&amp;"\"&amp;AB229&amp;"_"&amp;A229&amp;"（"&amp;B229&amp;"）"&amp;AC229&amp;".lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AE229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$N229="○"),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$AF229&amp;""""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AF229" s="9" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$N229="○"),
-  shortcut設定!$F$6&amp;"\"&amp;A229&amp;"（"&amp;B229&amp;"）.lnk",
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AG229" s="13" t="str">
-        <f t="shared" ref="AG229:AG234" si="43">IF(
-  AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
-  (
-    "schtasks /create /tn """&amp;$O229&amp;""" /tr """&amp;$C229&amp;""" /sc daily /st "&amp;$P229&amp;" /rl highest"
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AH229" s="13" t="str">
-        <f t="shared" ref="AH229:AH234" si="44">IF(
-  AND($A229&lt;&gt;"",$O229&lt;&gt;"-",$O229&lt;&gt;""),
-  (
-    "schtasks /delete /tn """&amp;$O229&amp;""""
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AI229" s="13" t="str">
-        <f>IF(
-  AND($A229&lt;&gt;"",$Q229&lt;&gt;"-",$Q229&lt;&gt;""),
-  (
-    """"&amp;shortcut設定!$F$7&amp;""""&amp;
-    " """&amp;$Q229&amp;".lnk"""&amp;
-    " """&amp;$C229&amp;""""&amp;
-    IF($D229="-"," """""," """&amp;$D229&amp;"""")&amp;
-    IF($E229="-"," """""," """&amp;$E229&amp;"""")
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="AJ229" s="91" t="s">
+        <v/>
+      </c>
+      <c r="AC227" s="20" t="str">
+        <f t="shared" ref="AC227" si="37">IF(AND($M227&lt;&gt;"",$M227&lt;&gt;"-")," (&amp;"&amp;$M227&amp;")","")</f>
+        <v/>
+      </c>
+      <c r="AD227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$L227="○"),
+  shortcut設定!$F$5&amp;"\"&amp;AB227&amp;"_"&amp;A227&amp;"（"&amp;B227&amp;"）"&amp;AC227&amp;".lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AE227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$N227="○"),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AF227&amp;""""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AF227" s="9" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$N227="○"),
+  shortcut設定!$F$6&amp;"\"&amp;A227&amp;"（"&amp;B227&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AG227" s="13" t="str">
+        <f t="shared" ref="AG227" si="38">IF(
+  AND($A227&lt;&gt;"",$O227&lt;&gt;"-",$O227&lt;&gt;""),
+  (
+    "schtasks /create /tn """&amp;$O227&amp;""" /tr """&amp;$C227&amp;""" /sc daily /st "&amp;$P227&amp;" /rl highest"
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AH227" s="13" t="str">
+        <f t="shared" ref="AH227" si="39">IF(
+  AND($A227&lt;&gt;"",$O227&lt;&gt;"-",$O227&lt;&gt;""),
+  (
+    "schtasks /delete /tn """&amp;$O227&amp;""""
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AI227" s="13" t="str">
+        <f>IF(
+  AND($A227&lt;&gt;"",$Q227&lt;&gt;"-",$Q227&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$Q227&amp;".lnk"""&amp;
+    " """&amp;$C227&amp;""""&amp;
+    IF($D227="-"," """""," """&amp;$D227&amp;"""")&amp;
+    IF($E227="-"," """""," """&amp;$E227&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AJ227" s="91" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="228" spans="1:36" ht="1.5" customHeight="1">
+      <c r="A228" s="16"/>
+      <c r="B228" s="16"/>
+      <c r="C228" s="16"/>
+      <c r="D228" s="16"/>
+      <c r="E228" s="16"/>
+      <c r="F228" s="16"/>
+      <c r="G228" s="16"/>
+      <c r="H228" s="16"/>
+      <c r="I228" s="16"/>
+      <c r="J228" s="16"/>
+      <c r="K228" s="16"/>
+      <c r="L228" s="17"/>
+      <c r="M228" s="18"/>
+      <c r="N228" s="16"/>
+      <c r="O228" s="16"/>
+      <c r="P228" s="158"/>
+      <c r="Q228" s="96"/>
+      <c r="R228" s="16"/>
+      <c r="S228" s="16"/>
+      <c r="T228" s="17"/>
+      <c r="U228" s="16"/>
+      <c r="V228" s="17"/>
+      <c r="W228" s="17"/>
+      <c r="X228" s="18"/>
+      <c r="Y228" s="17"/>
+      <c r="Z228" s="18"/>
+      <c r="AA228" s="17"/>
+      <c r="AB228" s="16"/>
+      <c r="AC228" s="90"/>
+      <c r="AD228" s="17"/>
+      <c r="AE228" s="17"/>
+      <c r="AF228" s="16"/>
+      <c r="AG228" s="17"/>
+      <c r="AH228" s="17"/>
+      <c r="AI228" s="17"/>
+      <c r="AJ228" s="91" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="230" spans="1:36">
       <c r="A230" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>39</v>
@@ -66574,13 +66560,13 @@
         <v>39</v>
       </c>
       <c r="F230" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G230" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G230" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="H230" s="9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I230" s="15" t="s">
         <v>841</v>
@@ -66610,11 +66596,26 @@
         <v>935</v>
       </c>
       <c r="R230" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="R230:R235" si="40">IF(
+  AND(
+    $A230&lt;&gt;"",
+    COUNTIF(C:C,$A230)&gt;1
+  ),
+  "★NG★",
+  ""
+)</f>
         <v/>
       </c>
       <c r="S230" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="S230:S235" si="41">IF(
+  OR(
+    $H230="",
+    $H230="-",
+    COUNTIF(カテゴリ,$H230)&gt;0
+  ),
+  "",
+  "★NG★"
+)</f>
         <v/>
       </c>
       <c r="T230" s="13" t="str">
@@ -66631,7 +66632,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\VcXsrv（X11サーバー）.lnk" "C:\prg\VcXsrv\xlaunch.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit\iMazingConverter（HEIC→JPG変換）.lnk" "C:\prg\DigiDNA\iMazing Converter\iMazing Converter.exe" "" ""</v>
       </c>
       <c r="U230" s="9" t="str">
         <f ca="1">IFERROR(
@@ -66647,7 +66648,7 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="V230" s="13" t="str">
         <f ca="1">IF(
@@ -66655,7 +66656,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U230&amp;"_"&amp;H230,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\153_Picture_Edit</v>
       </c>
       <c r="W230" s="13" t="str">
         <f>IF(
@@ -66734,10 +66735,10 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="AC230" s="20" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="AC230:AC235" si="42">IF(AND($M230&lt;&gt;"",$M230&lt;&gt;"-")," (&amp;"&amp;$M230&amp;")","")</f>
         <v/>
       </c>
       <c r="AD230" s="13" t="str">
@@ -66771,11 +66772,23 @@
         <v/>
       </c>
       <c r="AG230" s="13" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="AG230:AG235" si="43">IF(
+  AND($A230&lt;&gt;"",$O230&lt;&gt;"-",$O230&lt;&gt;""),
+  (
+    "schtasks /create /tn """&amp;$O230&amp;""" /tr """&amp;$C230&amp;""" /sc daily /st "&amp;$P230&amp;" /rl highest"
+  ),
+  ""
+)</f>
         <v/>
       </c>
       <c r="AH230" s="13" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="AH230:AH235" si="44">IF(
+  AND($A230&lt;&gt;"",$O230&lt;&gt;"-",$O230&lt;&gt;""),
+  (
+    "schtasks /delete /tn """&amp;$O230&amp;""""
+  ),
+  ""
+)</f>
         <v/>
       </c>
       <c r="AI230" s="13" t="str">
@@ -66798,55 +66811,55 @@
     </row>
     <row r="231" spans="1:36">
       <c r="A231" s="9" t="s">
-        <v>1267</v>
+        <v>649</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>1268</v>
+        <v>786</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>1266</v>
+        <v>162</v>
       </c>
       <c r="D231" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E231" s="26" t="s">
-        <v>1269</v>
+        <v>39</v>
       </c>
       <c r="F231" s="15" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="G231" s="15" t="s">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="H231" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I231" s="15" t="s">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="J231" s="15" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="K231" s="15" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="L231" s="93" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="M231" s="94" t="s">
-        <v>39</v>
+        <v>545</v>
       </c>
       <c r="N231" s="15" t="s">
-        <v>934</v>
+        <v>64</v>
       </c>
       <c r="O231" s="26" t="s">
-        <v>39</v>
+        <v>1230</v>
       </c>
       <c r="P231" s="157" t="s">
-        <v>39</v>
+        <v>1230</v>
       </c>
       <c r="Q231" s="26" t="s">
-        <v>39</v>
+        <v>935</v>
       </c>
       <c r="R231" s="9" t="str">
         <f t="shared" si="40"/>
@@ -66870,7 +66883,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\壁カレ４（デスクトップカレンダー）.lnk" "C:\prg\KABE4\KABE4.exe" "" "C:\prg\KABE4"</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\VcXsrv（X11サーバー）.lnk" "C:\prg\VcXsrv\xlaunch.exe" "" ""</v>
       </c>
       <c r="U231" s="9" t="str">
         <f ca="1">IFERROR(
@@ -66886,7 +66899,7 @@
   ),
   ""
 )</f>
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="V231" s="13" t="str">
         <f ca="1">IF(
@@ -66894,7 +66907,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U231&amp;"_"&amp;H231,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
       </c>
       <c r="W231" s="13" t="str">
         <f>IF(
@@ -66973,7 +66986,7 @@
   ),
   ""
 )</f>
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AC231" s="20" t="str">
         <f t="shared" si="42"/>
@@ -67037,55 +67050,55 @@
     </row>
     <row r="232" spans="1:36">
       <c r="A232" s="9" t="s">
-        <v>54</v>
+        <v>1267</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>783</v>
+        <v>1268</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>93</v>
+        <v>1266</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E232" s="26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G232" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I232" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J232" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F232" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="G232" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H232" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I232" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="J232" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="K232" s="15" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L232" s="93" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="M232" s="94" t="s">
-        <v>545</v>
+        <v>39</v>
       </c>
       <c r="N232" s="15" t="s">
-        <v>64</v>
+        <v>934</v>
       </c>
       <c r="O232" s="26" t="s">
-        <v>1230</v>
+        <v>39</v>
       </c>
       <c r="P232" s="157" t="s">
-        <v>1230</v>
+        <v>39</v>
       </c>
       <c r="Q232" s="26" t="s">
-        <v>935</v>
+        <v>39</v>
       </c>
       <c r="R232" s="9" t="str">
         <f t="shared" si="40"/>
@@ -67109,7 +67122,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit\DVD Shrink（DVDリッピング）.lnk" "C:\prg\DVD Shrink\DVD Shrink 3.2.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other\壁カレ４（デスクトップカレンダー）.lnk" "C:\prg\KABE4\KABE4.exe" "" "C:\prg\KABE4"</v>
       </c>
       <c r="U232" s="9" t="str">
         <f ca="1">IFERROR(
@@ -67125,7 +67138,7 @@
   ),
   ""
 )</f>
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="V232" s="13" t="str">
         <f ca="1">IF(
@@ -67133,7 +67146,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U232&amp;"_"&amp;H232,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\172_Utility_Other</v>
       </c>
       <c r="W232" s="13" t="str">
         <f>IF(
@@ -67212,7 +67225,7 @@
   ),
   ""
 )</f>
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="AC232" s="20" t="str">
         <f t="shared" si="42"/>
@@ -67276,13 +67289,13 @@
     </row>
     <row r="233" spans="1:36">
       <c r="A233" s="9" t="s">
-        <v>646</v>
+        <v>54</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="D233" s="15" t="s">
         <v>39</v>
@@ -67297,7 +67310,7 @@
         <v>149</v>
       </c>
       <c r="H233" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I233" s="15" t="s">
         <v>841</v>
@@ -67348,7 +67361,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local\UltraVNC Viewer（RDP-Mac）.lnk" "C:\prg\uvnc bvba\UltraVNC\vncviewer.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit\DVD Shrink（DVDリッピング）.lnk" "C:\prg\DVD Shrink\DVD Shrink 3.2.exe" "" ""</v>
       </c>
       <c r="U233" s="9" t="str">
         <f ca="1">IFERROR(
@@ -67364,7 +67377,7 @@
   ),
   ""
 )</f>
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="V233" s="13" t="str">
         <f ca="1">IF(
@@ -67372,7 +67385,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U233&amp;"_"&amp;H233,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\143_Movie_Edit</v>
       </c>
       <c r="W233" s="13" t="str">
         <f>IF(
@@ -67451,7 +67464,7 @@
   ),
   ""
 )</f>
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="AC233" s="20" t="str">
         <f t="shared" si="42"/>
@@ -67515,46 +67528,46 @@
     </row>
     <row r="234" spans="1:36">
       <c r="A234" s="9" t="s">
-        <v>1153</v>
+        <v>646</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>1154</v>
+        <v>781</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>1152</v>
+        <v>156</v>
       </c>
       <c r="D234" s="15" t="s">
-        <v>934</v>
+        <v>39</v>
       </c>
       <c r="E234" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F234" s="15" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H234" s="9" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I234" s="15" t="s">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="J234" s="15" t="s">
-        <v>934</v>
+        <v>64</v>
       </c>
       <c r="K234" s="15" t="s">
-        <v>934</v>
+        <v>64</v>
       </c>
       <c r="L234" s="93" t="s">
-        <v>934</v>
+        <v>64</v>
       </c>
       <c r="M234" s="94" t="s">
-        <v>934</v>
+        <v>545</v>
       </c>
       <c r="N234" s="15" t="s">
-        <v>934</v>
+        <v>64</v>
       </c>
       <c r="O234" s="26" t="s">
         <v>1230</v>
@@ -67563,7 +67576,7 @@
         <v>1230</v>
       </c>
       <c r="Q234" s="26" t="s">
-        <v>39</v>
+        <v>935</v>
       </c>
       <c r="R234" s="9" t="str">
         <f t="shared" si="40"/>
@@ -67587,7 +67600,7 @@
   ),
   ""
 )</f>
-        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\Steam（ゲーム）.lnk" "C:\prg\Steam\steam.exe" "" ""</v>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local\UltraVNC Viewer（RDP-Mac）.lnk" "C:\prg\uvnc bvba\UltraVNC\vncviewer.exe" "" ""</v>
       </c>
       <c r="U234" s="9" t="str">
         <f ca="1">IFERROR(
@@ -67603,7 +67616,7 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="V234" s="13" t="str">
         <f ca="1">IF(
@@ -67611,7 +67624,7 @@
   shortcut設定!$F$4&amp;"\"&amp;U234&amp;"_"&amp;H234,
   ""
 )</f>
-        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\162_Network_Local</v>
       </c>
       <c r="W234" s="13" t="str">
         <f>IF(
@@ -67690,7 +67703,7 @@
   ),
   ""
 )</f>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AC234" s="20" t="str">
         <f t="shared" si="42"/>
@@ -67752,17 +67765,256 @@
         <v>174</v>
       </c>
     </row>
+    <row r="235" spans="1:36">
+      <c r="A235" s="9" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D235" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="E235" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G235" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I235" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J235" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="K235" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="L235" s="93" t="s">
+        <v>934</v>
+      </c>
+      <c r="M235" s="94" t="s">
+        <v>934</v>
+      </c>
+      <c r="N235" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="O235" s="26" t="s">
+        <v>1230</v>
+      </c>
+      <c r="P235" s="157" t="s">
+        <v>1230</v>
+      </c>
+      <c r="Q235" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="R235" s="9" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="S235" s="9" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="T235" s="13" t="str">
+        <f ca="1">IF(
+  AND($A235&lt;&gt;"",$I235="○"),
+  (
+    "mkdir """&amp;V235&amp;""" &amp; "
+  )&amp;(
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;V235&amp;"\"&amp;$A235&amp;"（"&amp;$B235&amp;"）.lnk"""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")
+  ),
+  ""
+)</f>
+        <v>mkdir "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global" &amp; "C:\codes\vbs\command\CreateShortcutFile.vbs" "%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global\Steam（ゲーム）.lnk" "C:\prg\Steam\steam.exe" "" ""</v>
+      </c>
+      <c r="U235" s="9" t="str">
+        <f ca="1">IFERROR(
+  VLOOKUP(
+    $H235,
+    shortcut設定!$F:$J,
+    MATCH(
+      "ProgramsIndex",
+      shortcut設定!$F$12:$J$12,
+      0
+    ),
+    FALSE
+  ),
+  ""
+)</f>
+        <v>161</v>
+      </c>
+      <c r="V235" s="13" t="str">
+        <f ca="1">IF(
+  AND($A235&lt;&gt;"",$I235="○"),
+  shortcut設定!$F$4&amp;"\"&amp;U235&amp;"_"&amp;H235,
+  ""
+)</f>
+        <v>%USERPROFILE%\AppData\Roaming\Microsoft\Windows\Start Menu\Programs\161_Network_Global</v>
+      </c>
+      <c r="W235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$J235&lt;&gt;"-",$J235&lt;&gt;""),
+  (
+    "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;""" &amp; "
+  )&amp;(
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$X235&amp;""""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="X235" s="14" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$J235&lt;&gt;"-",$J235&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$8&amp;"\"&amp;$J235&amp;"（"&amp;$B235&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Y235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$K235&lt;&gt;"-",$K235&lt;&gt;""),
+  (
+    "mkdir """&amp;shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;""" &amp; "
+  )&amp;(
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$Z235&amp;""""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")&amp;
+    IF($K235="-"," """""," """&amp;$K235&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="Z235" s="14" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$K235&lt;&gt;"-",$K235&lt;&gt;""),
+  shortcut設定!$F$4&amp;"\"&amp;shortcut設定!$F$9&amp;"\"&amp;$A235&amp;"（"&amp;$B235&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AA235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$L235&lt;&gt;"-",$L235&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AD235&amp;""""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AB235" s="9" t="str">
+        <f ca="1">IFERROR(
+  VLOOKUP(
+    $H235,
+    shortcut設定!$F:$J,
+    MATCH(
+      "ProgramsIndex",
+      shortcut設定!$F$12:$J$12,
+      0
+    ),
+    FALSE
+  ),
+  ""
+)</f>
+        <v>161</v>
+      </c>
+      <c r="AC235" s="20" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AD235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$L235="○"),
+  shortcut設定!$F$5&amp;"\"&amp;AB235&amp;"_"&amp;A235&amp;"（"&amp;B235&amp;"）"&amp;AC235&amp;".lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AE235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$N235="○"),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$AF235&amp;""""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AF235" s="9" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$N235="○"),
+  shortcut設定!$F$6&amp;"\"&amp;A235&amp;"（"&amp;B235&amp;"）.lnk",
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AG235" s="13" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AH235" s="13" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AI235" s="13" t="str">
+        <f>IF(
+  AND($A235&lt;&gt;"",$Q235&lt;&gt;"-",$Q235&lt;&gt;""),
+  (
+    """"&amp;shortcut設定!$F$7&amp;""""&amp;
+    " """&amp;$Q235&amp;".lnk"""&amp;
+    " """&amp;$C235&amp;""""&amp;
+    IF($D235="-"," """""," """&amp;$D235&amp;"""")&amp;
+    IF($E235="-"," """""," """&amp;$E235&amp;"""")
+  ),
+  ""
+)</f>
+        <v/>
+      </c>
+      <c r="AJ235" s="91" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:AJ227" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A9:AJ228" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H229:H234 H224:H226 H11:H223" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H230:H235 H11:H227" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>カテゴリ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F229:G234 F224:G226 F11:G223" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F230:G235 F11:G227" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"○,×"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I229:I234 L229:L234 N229:N234 I224:I226 I11:I223 L224:L226 L11:L223 N224:N226 N11:N223" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I230:I235 L230:L235 N230:N235 N11:N227 L11:L227 I11:I227" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"○,-"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PC移行時チェックリスト.xlsx
+++ b/PC移行時チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D618488-AEA8-4FCA-A47E-C859CB668499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C8FCBB-E73C-40B4-AE91-113E0F2A2356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="38385" windowHeight="42465" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="42720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="セットアップ事項" sheetId="21" r:id="rId1"/>
